--- a/exports/daily-games.xlsx
+++ b/exports/daily-games.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="R54bb49ae13584e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="Rbed25c0477c346aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -332,7 +332,7 @@
         <x:v>q2_borough</x:v>
       </x:c>
       <x:c r="F1" s="4" t="str">
-        <x:v>q3_medium</x:v>
+        <x:v>q3_easy</x:v>
       </x:c>
       <x:c r="G1" s="4" t="str">
         <x:v>q3_borough</x:v>
@@ -367,28 +367,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>B &amp; B Carousell</x:v>
+        <x:v>Forest Park Carousel</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Beth Olam Cemetery</x:v>
+        <x:v>Rainey Memorial Gates</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H2" s="7" t="str">
-        <x:v>Middletown Plaza</x:v>
+        <x:v>Jacques Marchais Center of Tibetan Art</x:v>
       </x:c>
       <x:c r="I2" s="7" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J2" s="7" t="str">
-        <x:v>Gardiner-Tyler House</x:v>
+        <x:v>Old Stone House of Brooklyn</x:v>
       </x:c>
       <x:c r="K2" s="7" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L2" s="15" t="str">
         <x:v>scheduled</x:v>
@@ -406,28 +406,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>Forest Park Carousel</x:v>
+        <x:v>Litchfield Villa</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>Boys' High School</x:v>
+        <x:v>Alice Austen House</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H3" s="9" t="str">
-        <x:v>United Workers' Cooperatives</x:v>
+        <x:v>Astoria Center of Israel</x:v>
       </x:c>
       <x:c r="I3" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J3" s="9" t="str">
-        <x:v>Billou-Stillwell-Perine House</x:v>
+        <x:v>St. James' Episcopal Church and Parish House</x:v>
       </x:c>
       <x:c r="K3" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L3" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -445,28 +445,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>Ridgewood Reservoir</x:v>
+        <x:v>Brooklyn Public Library</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>Staten Island Light</x:v>
+        <x:v>Williamsbridge Oval Park</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H4" s="9" t="str">
-        <x:v>Jamaica Chamber of Commerce Building</x:v>
+        <x:v>Richmond Terrace Cemeteries</x:v>
       </x:c>
       <x:c r="I4" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J4" s="9" t="str">
-        <x:v>St. James' Episcopal Church and Parish House</x:v>
+        <x:v>New York Architectural Terra Cotta Company Office Building</x:v>
       </x:c>
       <x:c r="K4" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L4" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -484,28 +484,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>Garibaldi Memorial</x:v>
+        <x:v>Brooklyn Borough Hall</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str">
-        <x:v>Manhattan Beach Jewish Center</x:v>
+        <x:v>Conference House</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
-        <x:v>Kurtz, J., and Sons Store Building</x:v>
+        <x:v>Bronx Borough Courthouse</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J5" s="9" t="str">
-        <x:v>Hall of Fame Complex</x:v>
+        <x:v>Allen-Beville House</x:v>
       </x:c>
       <x:c r="K5" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L5" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -523,25 +523,25 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
+        <x:v>Federal Hall National Memorial</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str">
         <x:v>Jerome Park Reservoir</x:v>
       </x:c>
-      <x:c r="E6" s="9" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="str">
-        <x:v>University Settlement House</x:v>
-      </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>Sylvan Grove Cemetery</x:v>
+        <x:v>Staten Island Light</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>New York Architectural Terra Cotta Company Office Building</x:v>
+        <x:v>Flushing Armory</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
         <x:v>Queens</x:v>
@@ -562,25 +562,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
+        <x:v>Marine Air Terminal, La Guardia Airport</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="str">
         <x:v>Bartow-Pell Mansion and Carriage House</x:v>
       </x:c>
-      <x:c r="E7" s="9" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="str">
-        <x:v>Quarters A</x:v>
-      </x:c>
       <x:c r="G7" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H7" s="9" t="str">
-        <x:v>Office of the Register</x:v>
+        <x:v>Erasmus Hall Academy</x:v>
       </x:c>
       <x:c r="I7" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J7" s="9" t="str">
-        <x:v>Frederick Law Olmsted Sr. Farmhouse</x:v>
+        <x:v>Gardiner-Tyler House</x:v>
       </x:c>
       <x:c r="K7" s="9" t="str">
         <x:v>Staten Island</x:v>
@@ -601,28 +601,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Loew's Kameo Theater</x:v>
+        <x:v>Washington Bridge</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>Saxe Embroidery Company Building</x:v>
+        <x:v>Battery Weed</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>Kingsland Homestead</x:v>
+        <x:v>Jewish Center of Coney Island</x:v>
       </x:c>
       <x:c r="I8" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>Moore-McMillen House</x:v>
+        <x:v>Spear &amp; Company Factory</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L8" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -640,28 +640,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>Old Town of Flushing Burial Ground</x:v>
+        <x:v>Port Morris Ferry Bridges</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F9" s="9" t="str">
-        <x:v>Wyckoff-Bennett Homestead</x:v>
+        <x:v>Ridgewood Reservoir</x:v>
       </x:c>
       <x:c r="G9" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H9" s="9" t="str">
-        <x:v>Fire Fighter</x:v>
+        <x:v>Beth Olam Cemetery</x:v>
       </x:c>
       <x:c r="I9" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J9" s="9" t="str">
-        <x:v>Hertlein and Schlatter Silk Trimmings Factory</x:v>
+        <x:v>Billou-Stillwell-Perine House</x:v>
       </x:c>
       <x:c r="K9" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L9" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -679,28 +679,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>Conference House</x:v>
+        <x:v>Woodlawn Cemetery</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>Gage and Tollner Restaurant</x:v>
+        <x:v>Sailors' Snug Harbor</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H10" s="9" t="str">
-        <x:v>Fort Totten Officers' Club</x:v>
+        <x:v>Kurtz, J., and Sons Store Building</x:v>
       </x:c>
       <x:c r="I10" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>Dodge, William E., House</x:v>
+        <x:v>Lincoln Club</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L10" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -718,25 +718,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>Battery Weed</x:v>
+        <x:v>Old Quaker Meetinghouse</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>New Lots Reformed Church and Cemetery</x:v>
+        <x:v>Floyd Bennett Field</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H11" s="9" t="str">
-        <x:v>Kent Manor</x:v>
+        <x:v>New Dorp Light</x:v>
       </x:c>
       <x:c r="I11" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J11" s="9" t="str">
-        <x:v>Valentine-Varian House</x:v>
+        <x:v>Hall of Fame Complex</x:v>
       </x:c>
       <x:c r="K11" s="9" t="str">
         <x:v>The Bronx</x:v>
@@ -757,28 +757,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>Theodore Roosevelt Birthplace</x:v>
+        <x:v>Biltmore Theater</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>Sage, Russell, Memorial Church</x:v>
+        <x:v>King Manor</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="H12" s="9" t="str">
-        <x:v>Eighth Regiment Armory (Kingsbridge Armory)</x:v>
+        <x:v>Silver Lake Cemetery</x:v>
       </x:c>
       <x:c r="I12" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J12" s="9" t="str">
-        <x:v>Kreischer House</x:v>
+        <x:v>Hertlein and Schlatter Silk Trimmings Factory</x:v>
       </x:c>
       <x:c r="K12" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L12" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -796,28 +796,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>African Burial Ground</x:v>
+        <x:v>New Amsterdam Theater</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>Trinity Chapel</x:v>
+        <x:v>Edgar Allan Poe Cottage</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H13" s="9" t="str">
-        <x:v>Edgewater Village Hall and Tappen Park</x:v>
+        <x:v>Benevolent and Protective Order of Elks, Lodge #878</x:v>
       </x:c>
       <x:c r="I13" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J13" s="9" t="str">
-        <x:v>Grace Episcopal Church</x:v>
+        <x:v>Frederick Law Olmsted Sr. Farmhouse</x:v>
       </x:c>
       <x:c r="K13" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L13" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -835,28 +835,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>Fort Wadsworth</x:v>
+        <x:v>Green-Wood Cemetery</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>Beth-El Jewish Center of Flatbush</x:v>
+        <x:v>Garibaldi Memorial</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H14" s="9" t="str">
-        <x:v>Maple Grove Cemetery</x:v>
+        <x:v>Casita Rincon Criollo</x:v>
       </x:c>
       <x:c r="I14" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J14" s="9" t="str">
-        <x:v>Riverdale Presbyterian Church Complex</x:v>
+        <x:v>Cornell Farmhouse</x:v>
       </x:c>
       <x:c r="K14" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L14" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -874,25 +874,25 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>Alice Austen House</x:v>
+        <x:v>Morris–Jumel Mansion</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F15" s="9" t="str">
-        <x:v>Riverside Park and Drive</x:v>
+        <x:v>Fort Tompkins Quadrangle</x:v>
       </x:c>
       <x:c r="G15" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H15" s="9" t="str">
-        <x:v>Rockaway Courthouse</x:v>
+        <x:v>Trinity Chapel</x:v>
       </x:c>
       <x:c r="I15" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J15" s="9" t="str">
-        <x:v>C. Rieger's Sons Factory</x:v>
+        <x:v>Dodge, William E., House</x:v>
       </x:c>
       <x:c r="K15" s="9" t="str">
         <x:v>The Bronx</x:v>
@@ -913,28 +913,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>Old Orchard Shoal Light Station</x:v>
+        <x:v>Ocean Parkway</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
-        <x:v>Alku &amp; Alku Toinen</x:v>
+        <x:v>Wave Hill</x:v>
       </x:c>
       <x:c r="G16" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
-        <x:v>BOHEMIAN HALL AND PARK</x:v>
+        <x:v>First Reformed Church of College Point</x:v>
       </x:c>
       <x:c r="I16" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J16" s="9" t="str">
-        <x:v>Reformed Church of Melrose</x:v>
+        <x:v>Moore-McMillen House</x:v>
       </x:c>
       <x:c r="K16" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L16" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -958,22 +958,22 @@
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F17" s="9" t="str">
-        <x:v>Old Brooklyn Fire Headquarters</x:v>
+        <x:v>Prospect Park Boathouse</x:v>
       </x:c>
       <x:c r="G17" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H17" s="9" t="str">
-        <x:v>Silver Lake Cemetery</x:v>
+        <x:v>Flushing High School</x:v>
       </x:c>
       <x:c r="I17" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J17" s="9" t="str">
-        <x:v>Allen-Beville House</x:v>
+        <x:v>Kreischer House</x:v>
       </x:c>
       <x:c r="K17" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L17" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -991,25 +991,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>Floyd Bennett Field</x:v>
+        <x:v>Fort Wadsworth</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>Wyckoff-Snediker Family Cemetery</x:v>
+        <x:v>Steinway House</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="H18" s="9" t="str">
-        <x:v>St. Paul's Memorial Church and Rectory</x:v>
+        <x:v>Nassau Brewery</x:v>
       </x:c>
       <x:c r="I18" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J18" s="9" t="str">
-        <x:v>St. Anselm's Roman Catholic Church Complex</x:v>
+        <x:v>Valentine-Varian House</x:v>
       </x:c>
       <x:c r="K18" s="9" t="str">
         <x:v>The Bronx</x:v>
@@ -1030,28 +1030,28 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>Port Morris Ferry Bridges</x:v>
+        <x:v>The Public Theater</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>Park Row Building</x:v>
+        <x:v>Ward, Caleb T., Mansion</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
-        <x:v>Talmud Torah Atereth Israel</x:v>
+        <x:v>Brooklyn Trust Company</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J19" s="9" t="str">
-        <x:v>LaTourette House</x:v>
+        <x:v>Grace Episcopal Church</x:v>
       </x:c>
       <x:c r="K19" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L19" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1069,28 +1069,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Fort Tompkins Quadrangle</x:v>
+        <x:v>Gracie Mansion</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>Whitney Museum of American Art</x:v>
+        <x:v>Rego Park Jewish Center</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H20" s="9" t="str">
-        <x:v>The Church-in-the-Gardens</x:v>
+        <x:v>United Workers' Cooperatives</x:v>
       </x:c>
       <x:c r="I20" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J20" s="9" t="str">
-        <x:v>Spaulding, Henry F., Coachman's House</x:v>
+        <x:v>LaTourette House</x:v>
       </x:c>
       <x:c r="K20" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L20" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1108,28 +1108,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>King Manor</x:v>
+        <x:v>Riverside Park and Drive</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>Verdi, Giuseppe, Monument</x:v>
+        <x:v>Voorlezer's House</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H21" s="9" t="str">
-        <x:v>St. Peter's Church, Chapel and Cemetery Complex</x:v>
+        <x:v>Bronx County Courthouse</x:v>
       </x:c>
       <x:c r="I21" s="9" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J21" s="9" t="str">
-        <x:v>Boardman- Mitchell House</x:v>
+        <x:v>Trinity Lutheran Church</x:v>
       </x:c>
       <x:c r="K21" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L21" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1147,25 +1147,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>Flushing Town Hall</x:v>
+        <x:v>Loew's Kameo Theater</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
-        <x:v>Young Israel of Flatbush</x:v>
+        <x:v>Parkway Village</x:v>
       </x:c>
       <x:c r="G22" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
-        <x:v>Riverdale, Spuyten Duyvil, Kingsbridge Memorial Bell Tower</x:v>
+        <x:v>St. Peter's Church, Chapel and Cemetery Complex</x:v>
       </x:c>
       <x:c r="I22" s="9" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J22" s="9" t="str">
-        <x:v>McFarlane-Bredt House</x:v>
+        <x:v>Boardman- Mitchell House</x:v>
       </x:c>
       <x:c r="K22" s="9" t="str">
         <x:v>Staten Island</x:v>
@@ -1186,28 +1186,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>Ocean Parkway Jewish Center</x:v>
+        <x:v>McGolrick, Monsignor, Park and Shelter Pavilion</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F23" s="9" t="str">
-        <x:v>Richmond Terrace Cemeteries</x:v>
+        <x:v>Old Town of Flushing Burial Ground</x:v>
       </x:c>
       <x:c r="G23" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H23" s="9" t="str">
-        <x:v>Casa Amadeo, antigua Casa Hernandez</x:v>
+        <x:v>West Bank Light Station</x:v>
       </x:c>
       <x:c r="I23" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J23" s="9" t="str">
-        <x:v>Flushing Armory</x:v>
+        <x:v>Riverdale Presbyterian Church Complex</x:v>
       </x:c>
       <x:c r="K23" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L23" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1225,28 +1225,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Woodlawn Cemetery</x:v>
+        <x:v>Eastern Parkway</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>Prospect Park Boathouse</x:v>
+        <x:v>RKO Keith's Theater</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H24" s="9" t="str">
-        <x:v>West Bank Light Station</x:v>
+        <x:v>Keeper's House, Williamsbridge Reservoir</x:v>
       </x:c>
       <x:c r="I24" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J24" s="9" t="str">
-        <x:v>Spear &amp; Company Factory</x:v>
+        <x:v>McFarlane-Bredt House</x:v>
       </x:c>
       <x:c r="K24" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L24" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1264,28 +1264,28 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>New York Public Library</x:v>
+        <x:v>Theodore Roosevelt Birthplace</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F25" s="9" t="str">
-        <x:v>Joralemon Street Tunnel (IRT)</x:v>
+        <x:v>Loew's King Theatre</x:v>
       </x:c>
       <x:c r="G25" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H25" s="9" t="str">
-        <x:v>Bronx Borough Courthouse</x:v>
+        <x:v>Ward's Point Conservation Area</x:v>
       </x:c>
       <x:c r="I25" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J25" s="9" t="str">
-        <x:v>Kreuzer-Pelton House</x:v>
+        <x:v>C. Rieger's Sons Factory</x:v>
       </x:c>
       <x:c r="K25" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L25" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1303,28 +1303,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Old Quaker Meetinghouse</x:v>
+        <x:v>Crotona Play Center</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>Friends Meetinghouse and School</x:v>
+        <x:v>Parkway Theater</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H26" s="9" t="str">
-        <x:v>Vanderbilt Family Cemetery and Mausoleum</x:v>
+        <x:v>Maple Grove Cemetery</x:v>
       </x:c>
       <x:c r="I26" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J26" s="9" t="str">
-        <x:v>St. Ann's Church Complex</x:v>
+        <x:v>Kreuzer-Pelton House</x:v>
       </x:c>
       <x:c r="K26" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L26" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1342,22 +1342,22 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>Washington Bridge</x:v>
+        <x:v>Jeffrey's Hook Lighthouse</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F27" s="9" t="str">
-        <x:v>Charlie Parker Residence</x:v>
+        <x:v>Flushing Town Hall</x:v>
       </x:c>
       <x:c r="G27" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H27" s="9" t="str">
-        <x:v>La Casina</x:v>
+        <x:v>Boston Road Plaza</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J27" s="9" t="str">
         <x:v>Immanuel Union Church</x:v>
@@ -1381,19 +1381,19 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>Rainey Memorial Gates</x:v>
+        <x:v>B &amp; B Carousell</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F28" s="9" t="str">
-        <x:v>Old Gravesend Cemetery</x:v>
+        <x:v>Fort Schuyler</x:v>
       </x:c>
       <x:c r="G28" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H28" s="9" t="str">
-        <x:v>Benevolent and Protective Order of Elks, Lodge #878</x:v>
+        <x:v>Queens County Savings Bank, Kew Gardens Hills Branch</x:v>
       </x:c>
       <x:c r="I28" s="9" t="str">
         <x:v>Queens</x:v>
@@ -1420,28 +1420,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>Steinway House</x:v>
+        <x:v>U.S. Army Military Ocean Terminal</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F29" s="9" t="str">
-        <x:v>Erasmus Hall Academy</x:v>
+        <x:v>Old Orchard Shoal Light Station</x:v>
       </x:c>
       <x:c r="G29" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H29" s="9" t="str">
-        <x:v>Bronx County Courthouse</x:v>
+        <x:v>Office of the Register</x:v>
       </x:c>
       <x:c r="I29" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J29" s="9" t="str">
-        <x:v>Louis A. and Laura Stirn House</x:v>
+        <x:v>Reformed Church of Melrose</x:v>
       </x:c>
       <x:c r="K29" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L29" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1459,28 +1459,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>Wave Hill</x:v>
+        <x:v>Ocean Parkway Jewish Center</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F30" s="9" t="str">
-        <x:v>Fiorentino Plaza</x:v>
+        <x:v>Staten Island Ferry Terminal</x:v>
       </x:c>
       <x:c r="G30" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H30" s="9" t="str">
-        <x:v>Astoria Center of Israel</x:v>
+        <x:v>Long Island City Courthouse Complex</x:v>
       </x:c>
       <x:c r="I30" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J30" s="9" t="str">
-        <x:v>Old Stone House of Brooklyn</x:v>
+        <x:v>St. Anselm's Roman Catholic Church Complex</x:v>
       </x:c>
       <x:c r="K30" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L30" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1498,28 +1498,28 @@
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Trinity Church and Graveyard</x:v>
+        <x:v>African Burial Ground</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v>Jewish Center of Kings Highway</x:v>
+        <x:v>Long Island Motor Parkway</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H31" s="9" t="str">
-        <x:v>Jacques Marchais Center of Tibetan Art</x:v>
+        <x:v>Mary A. Whalen</x:v>
       </x:c>
       <x:c r="I31" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J31" s="9" t="str">
-        <x:v>Cornell Farmhouse</x:v>
+        <x:v>Louis A. and Laura Stirn House</x:v>
       </x:c>
       <x:c r="K31" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L31" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1537,28 +1537,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>Brooklyn Public Library</x:v>
+        <x:v>Ed Sullivan Theater</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v>Flushing High School</x:v>
+        <x:v>Hamilton Grange National Memorial</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H32" s="9" t="str">
-        <x:v>Sunnyslope</x:v>
+        <x:v>Casemate Fort, Whiting Quadrangle</x:v>
       </x:c>
       <x:c r="I32" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J32" s="9" t="str">
-        <x:v>Circle Line X</x:v>
+        <x:v>Conrad Voelcker House</x:v>
       </x:c>
       <x:c r="K32" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L32" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1576,28 +1576,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>Fort Schuyler</x:v>
+        <x:v>New York Public Library</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F33" s="9" t="str">
-        <x:v>Public Bath No. 7</x:v>
+        <x:v>Morgan Library</x:v>
       </x:c>
       <x:c r="G33" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H33" s="9" t="str">
-        <x:v>First Reformed Church of College Point</x:v>
+        <x:v>Beth-El Jewish Center of Flatbush</x:v>
       </x:c>
       <x:c r="I33" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J33" s="9" t="str">
-        <x:v>Corbin Building</x:v>
+        <x:v>Sohmer Piano Factory</x:v>
       </x:c>
       <x:c r="K33" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L33" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1615,25 +1615,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>Loew's King Theatre</x:v>
+        <x:v>Trinity Church and Graveyard</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F34" s="9" t="str">
-        <x:v>Admiral David Glasgow Farragut Gravesite</x:v>
+        <x:v>Castle Clinton National Monument</x:v>
       </x:c>
       <x:c r="G34" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H34" s="9" t="str">
-        <x:v>Staten Island Borough Hall and Richmond County Courthouse</x:v>
+        <x:v>Gage and Tollner Restaurant</x:v>
       </x:c>
       <x:c r="I34" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J34" s="9" t="str">
-        <x:v>Trinity Lutheran Church</x:v>
+        <x:v>Saint James Church</x:v>
       </x:c>
       <x:c r="K34" s="9" t="str">
         <x:v>Queens</x:v>
@@ -1654,25 +1654,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>RKO Keith's Theater</x:v>
+        <x:v>Queensboro Bridge</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F35" s="9" t="str">
-        <x:v>Brooklyn Historical Society Building</x:v>
+        <x:v>American Stock Exchange</x:v>
       </x:c>
       <x:c r="G35" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H35" s="9" t="str">
-        <x:v>Ward's Point Conservation Area</x:v>
+        <x:v>Joralemon Street Tunnel (IRT)</x:v>
       </x:c>
       <x:c r="I35" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J35" s="9" t="str">
-        <x:v>Christ Church Complex</x:v>
+        <x:v>Spaulding, Henry F., Coachman's House</x:v>
       </x:c>
       <x:c r="K35" s="9" t="str">
         <x:v>The Bronx</x:v>
@@ -1693,28 +1693,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>McGolrick, Monsignor, Park and Shelter Pavilion</x:v>
+        <x:v>Whitney Museum of American Art</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>Queens County Savings Bank, Kew Gardens Hills Branch</x:v>
+        <x:v>College of the City of New York</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str">
-        <x:v>Lorillard Snuff Mill</x:v>
+        <x:v>Jewish Center of Kings Highway</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J36" s="11" t="str">
-        <x:v>Bayard Rustin Apartment</x:v>
+        <x:v>Jamaica Savings Bank</x:v>
       </x:c>
       <x:c r="K36" s="11" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L36" s="17" t="str">
         <x:v>scheduled</x:v>

--- a/exports/daily-games.xlsx
+++ b/exports/daily-games.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="Rbed25c0477c346aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="R01871f8d06cd49fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -320,31 +320,31 @@
         <x:v>date</x:v>
       </x:c>
       <x:c r="B1" s="4" t="str">
-        <x:v>q1_very_easy</x:v>
+        <x:v>q1_easy</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
         <x:v>q1_borough</x:v>
       </x:c>
       <x:c r="D1" s="4" t="str">
-        <x:v>q2_easy</x:v>
+        <x:v>q2_medium</x:v>
       </x:c>
       <x:c r="E1" s="4" t="str">
         <x:v>q2_borough</x:v>
       </x:c>
       <x:c r="F1" s="4" t="str">
-        <x:v>q3_easy</x:v>
+        <x:v>q3_medium</x:v>
       </x:c>
       <x:c r="G1" s="4" t="str">
         <x:v>q3_borough</x:v>
       </x:c>
       <x:c r="H1" s="4" t="str">
-        <x:v>q4_medium</x:v>
+        <x:v>q4_hard</x:v>
       </x:c>
       <x:c r="I1" s="4" t="str">
         <x:v>q4_borough</x:v>
       </x:c>
       <x:c r="J1" s="4" t="str">
-        <x:v>q5_hard</x:v>
+        <x:v>q5_im_walking_here</x:v>
       </x:c>
       <x:c r="K1" s="4" t="str">
         <x:v>q5_borough</x:v>
@@ -385,10 +385,10 @@
         <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J2" s="7" t="str">
-        <x:v>Old Stone House of Brooklyn</x:v>
+        <x:v>New York Architectural Terra Cotta Company Office Building</x:v>
       </x:c>
       <x:c r="K2" s="7" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L2" s="15" t="str">
         <x:v>scheduled</x:v>
@@ -406,16 +406,16 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>Litchfield Villa</x:v>
+        <x:v>Federal Hall National Memorial</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>Alice Austen House</x:v>
+        <x:v>Biltmore Theater</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H3" s="9" t="str">
         <x:v>Astoria Center of Israel</x:v>
@@ -424,10 +424,10 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J3" s="9" t="str">
-        <x:v>St. James' Episcopal Church and Parish House</x:v>
+        <x:v>Old Stone House of Brooklyn</x:v>
       </x:c>
       <x:c r="K3" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L3" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -445,28 +445,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>Brooklyn Public Library</x:v>
+        <x:v>Litchfield Villa</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>Williamsbridge Oval Park</x:v>
+        <x:v>Alice Austen House</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H4" s="9" t="str">
-        <x:v>Richmond Terrace Cemeteries</x:v>
+        <x:v>Bronx Borough Courthouse</x:v>
       </x:c>
       <x:c r="I4" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J4" s="9" t="str">
-        <x:v>New York Architectural Terra Cotta Company Office Building</x:v>
+        <x:v>Circle Line X</x:v>
       </x:c>
       <x:c r="K4" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L4" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -484,28 +484,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>Brooklyn Borough Hall</x:v>
+        <x:v>Brooklyn Public Library</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str">
-        <x:v>Conference House</x:v>
+        <x:v>Williamsbridge Oval Park</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
-        <x:v>Bronx Borough Courthouse</x:v>
+        <x:v>Richmond Terrace Cemeteries</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J5" s="9" t="str">
-        <x:v>Allen-Beville House</x:v>
+        <x:v>St. James' Episcopal Church and Parish House</x:v>
       </x:c>
       <x:c r="K5" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L5" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -523,28 +523,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>Federal Hall National Memorial</x:v>
+        <x:v>New Amsterdam Theater</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>Jerome Park Reservoir</x:v>
+        <x:v>Brooklyn Borough Hall</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>Staten Island Light</x:v>
+        <x:v>Erasmus Hall Academy</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J6" s="9" t="str">
-        <x:v>Flushing Armory</x:v>
+        <x:v>Gardiner-Tyler House</x:v>
       </x:c>
       <x:c r="K6" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L6" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -562,28 +562,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>Marine Air Terminal, La Guardia Airport</x:v>
+        <x:v>Conference House</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>Bartow-Pell Mansion and Carriage House</x:v>
+        <x:v>Jerome Park Reservoir</x:v>
       </x:c>
       <x:c r="G7" s="9" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H7" s="9" t="str">
-        <x:v>Erasmus Hall Academy</x:v>
+        <x:v>Staten Island Light</x:v>
       </x:c>
       <x:c r="I7" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J7" s="9" t="str">
-        <x:v>Gardiner-Tyler House</x:v>
+        <x:v>Allen-Beville House</x:v>
       </x:c>
       <x:c r="K7" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L7" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -601,16 +601,16 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Washington Bridge</x:v>
+        <x:v>Morris–Jumel Mansion</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>Battery Weed</x:v>
+        <x:v>Marine Air Terminal, La Guardia Airport</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
         <x:v>Jewish Center of Coney Island</x:v>
@@ -619,10 +619,10 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J8" s="9" t="str">
-        <x:v>Spear &amp; Company Factory</x:v>
+        <x:v>Billou-Stillwell-Perine House</x:v>
       </x:c>
       <x:c r="K8" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L8" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -640,16 +640,16 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>Port Morris Ferry Bridges</x:v>
+        <x:v>Bartow-Pell Mansion and Carriage House</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F9" s="9" t="str">
-        <x:v>Ridgewood Reservoir</x:v>
+        <x:v>Washington Bridge</x:v>
       </x:c>
       <x:c r="G9" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H9" s="9" t="str">
         <x:v>Beth Olam Cemetery</x:v>
@@ -658,10 +658,10 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J9" s="9" t="str">
-        <x:v>Billou-Stillwell-Perine House</x:v>
+        <x:v>Hall of Fame Complex</x:v>
       </x:c>
       <x:c r="K9" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L9" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -679,13 +679,13 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>Woodlawn Cemetery</x:v>
+        <x:v>Port Morris Ferry Bridges</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>Sailors' Snug Harbor</x:v>
+        <x:v>Battery Weed</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
         <x:v>Staten Island</x:v>
@@ -697,10 +697,10 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J10" s="9" t="str">
-        <x:v>Lincoln Club</x:v>
+        <x:v>Frederick Law Olmsted Sr. Farmhouse</x:v>
       </x:c>
       <x:c r="K10" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L10" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -718,28 +718,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>Old Quaker Meetinghouse</x:v>
+        <x:v>Ridgewood Reservoir</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>Floyd Bennett Field</x:v>
+        <x:v>Woodlawn Cemetery</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H11" s="9" t="str">
-        <x:v>New Dorp Light</x:v>
+        <x:v>Nassau Brewery</x:v>
       </x:c>
       <x:c r="I11" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J11" s="9" t="str">
-        <x:v>Hall of Fame Complex</x:v>
+        <x:v>Corbin Building</x:v>
       </x:c>
       <x:c r="K11" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L11" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -757,28 +757,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>Biltmore Theater</x:v>
+        <x:v>Sailors' Snug Harbor</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>King Manor</x:v>
+        <x:v>The Public Theater</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H12" s="9" t="str">
-        <x:v>Silver Lake Cemetery</x:v>
+        <x:v>Duke, James B., Mansion</x:v>
       </x:c>
       <x:c r="I12" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J12" s="9" t="str">
-        <x:v>Hertlein and Schlatter Silk Trimmings Factory</x:v>
+        <x:v>Bayard Rustin Apartment</x:v>
       </x:c>
       <x:c r="K12" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L12" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -796,16 +796,16 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>New Amsterdam Theater</x:v>
+        <x:v>Old Quaker Meetinghouse</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>Edgar Allan Poe Cottage</x:v>
+        <x:v>Floyd Bennett Field</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H13" s="9" t="str">
         <x:v>Benevolent and Protective Order of Elks, Lodge #878</x:v>
@@ -814,10 +814,10 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J13" s="9" t="str">
-        <x:v>Frederick Law Olmsted Sr. Farmhouse</x:v>
+        <x:v>Bell Telephone Laboratories</x:v>
       </x:c>
       <x:c r="K13" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L13" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -835,28 +835,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
+        <x:v>Gracie Mansion</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="F14" s="9" t="str">
         <x:v>Green-Wood Cemetery</x:v>
       </x:c>
-      <x:c r="E14" s="9" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="str">
-        <x:v>Garibaldi Memorial</x:v>
-      </x:c>
       <x:c r="G14" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H14" s="9" t="str">
-        <x:v>Casita Rincon Criollo</x:v>
+        <x:v>Harlem Courthouse</x:v>
       </x:c>
       <x:c r="I14" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J14" s="9" t="str">
-        <x:v>Cornell Farmhouse</x:v>
+        <x:v>Hertlein and Schlatter Silk Trimmings Factory</x:v>
       </x:c>
       <x:c r="K14" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L14" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -874,28 +874,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>Morris–Jumel Mansion</x:v>
+        <x:v>King Manor</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F15" s="9" t="str">
-        <x:v>Fort Tompkins Quadrangle</x:v>
+        <x:v>Edgar Allan Poe Cottage</x:v>
       </x:c>
       <x:c r="G15" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H15" s="9" t="str">
-        <x:v>Trinity Chapel</x:v>
+        <x:v>Brooklyn Trust Company</x:v>
       </x:c>
       <x:c r="I15" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J15" s="9" t="str">
-        <x:v>Dodge, William E., House</x:v>
+        <x:v>Daily News Building</x:v>
       </x:c>
       <x:c r="K15" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L15" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -913,28 +913,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>Ocean Parkway</x:v>
+        <x:v>Garibaldi Memorial</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
-        <x:v>Wave Hill</x:v>
+        <x:v>Riverside Park and Drive</x:v>
       </x:c>
       <x:c r="G16" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
-        <x:v>First Reformed Church of College Point</x:v>
+        <x:v>Whitney Museum of American Art (NY Studio School)</x:v>
       </x:c>
       <x:c r="I16" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J16" s="9" t="str">
-        <x:v>Moore-McMillen House</x:v>
+        <x:v>Flushing Armory</x:v>
       </x:c>
       <x:c r="K16" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L16" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -952,28 +952,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>High Bridge Aqueduct and Water Tower</x:v>
+        <x:v>Fort Tompkins Quadrangle</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F17" s="9" t="str">
-        <x:v>Prospect Park Boathouse</x:v>
+        <x:v>Ocean Parkway</x:v>
       </x:c>
       <x:c r="G17" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H17" s="9" t="str">
-        <x:v>Flushing High School</x:v>
+        <x:v>New Dorp Light</x:v>
       </x:c>
       <x:c r="I17" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J17" s="9" t="str">
-        <x:v>Kreischer House</x:v>
+        <x:v>Candler Building</x:v>
       </x:c>
       <x:c r="K17" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L17" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -991,28 +991,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>Fort Wadsworth</x:v>
+        <x:v>Theodore Roosevelt Birthplace</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>Steinway House</x:v>
+        <x:v>Wave Hill</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H18" s="9" t="str">
-        <x:v>Nassau Brewery</x:v>
+        <x:v>Mary A. Whalen</x:v>
       </x:c>
       <x:c r="I18" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J18" s="9" t="str">
-        <x:v>Valentine-Varian House</x:v>
+        <x:v>Moore-McMillen House</x:v>
       </x:c>
       <x:c r="K18" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L18" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1030,28 +1030,28 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>The Public Theater</x:v>
+        <x:v>High Bridge Aqueduct and Water Tower</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>Ward, Caleb T., Mansion</x:v>
+        <x:v>Prospect Park Boathouse</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H19" s="9" t="str">
-        <x:v>Brooklyn Trust Company</x:v>
+        <x:v>Columbus Monument</x:v>
       </x:c>
       <x:c r="I19" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J19" s="9" t="str">
-        <x:v>Grace Episcopal Church</x:v>
+        <x:v>Cary Building</x:v>
       </x:c>
       <x:c r="K19" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L19" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1069,28 +1069,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Gracie Mansion</x:v>
+        <x:v>Fort Wadsworth</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>Rego Park Jewish Center</x:v>
+        <x:v>Jeffrey's Hook Lighthouse</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H20" s="9" t="str">
-        <x:v>United Workers' Cooperatives</x:v>
+        <x:v>Casemate Fort, Whiting Quadrangle</x:v>
       </x:c>
       <x:c r="I20" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J20" s="9" t="str">
-        <x:v>LaTourette House</x:v>
+        <x:v>City &amp; Suburban Homes Company's York Avenue Estate</x:v>
       </x:c>
       <x:c r="K20" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L20" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1108,28 +1108,28 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>Riverside Park and Drive</x:v>
+        <x:v>Steinway House</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>Voorlezer's House</x:v>
+        <x:v>Ward, Caleb T., Mansion</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H21" s="9" t="str">
-        <x:v>Bronx County Courthouse</x:v>
+        <x:v>Silver Lake Cemetery</x:v>
       </x:c>
       <x:c r="I21" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="J21" s="9" t="str">
-        <x:v>Trinity Lutheran Church</x:v>
+        <x:v>Kreischer House</x:v>
       </x:c>
       <x:c r="K21" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L21" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1147,28 +1147,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>Loew's Kameo Theater</x:v>
+        <x:v>African Burial Ground</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
-        <x:v>Parkway Village</x:v>
+        <x:v>Rego Park Jewish Center</x:v>
       </x:c>
       <x:c r="G22" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="H22" s="9" t="str">
-        <x:v>St. Peter's Church, Chapel and Cemetery Complex</x:v>
+        <x:v>Appellate Division Courthouse of New York State</x:v>
       </x:c>
       <x:c r="I22" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J22" s="9" t="str">
-        <x:v>Boardman- Mitchell House</x:v>
+        <x:v>Lincoln Club</x:v>
       </x:c>
       <x:c r="K22" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L22" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1186,25 +1186,25 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>McGolrick, Monsignor, Park and Shelter Pavilion</x:v>
+        <x:v>Loew's Kameo Theater</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F23" s="9" t="str">
-        <x:v>Old Town of Flushing Burial Ground</x:v>
+        <x:v>Ed Sullivan Theater</x:v>
       </x:c>
       <x:c r="G23" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H23" s="9" t="str">
-        <x:v>West Bank Light Station</x:v>
+        <x:v>University Settlement House</x:v>
       </x:c>
       <x:c r="I23" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J23" s="9" t="str">
-        <x:v>Riverdale Presbyterian Church Complex</x:v>
+        <x:v>Dodge, William E., House</x:v>
       </x:c>
       <x:c r="K23" s="9" t="str">
         <x:v>The Bronx</x:v>
@@ -1225,28 +1225,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Eastern Parkway</x:v>
+        <x:v>Voorlezer's House</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>RKO Keith's Theater</x:v>
+        <x:v>Hamilton Grange National Memorial</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H24" s="9" t="str">
-        <x:v>Keeper's House, Williamsbridge Reservoir</x:v>
+        <x:v>Beth-El Jewish Center of Flatbush</x:v>
       </x:c>
       <x:c r="I24" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J24" s="9" t="str">
-        <x:v>McFarlane-Bredt House</x:v>
+        <x:v>Congregation Tifereth Israel</x:v>
       </x:c>
       <x:c r="K24" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L24" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1264,28 +1264,28 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>Theodore Roosevelt Birthplace</x:v>
+        <x:v>New York Public Library</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F25" s="9" t="str">
-        <x:v>Loew's King Theatre</x:v>
+        <x:v>Parkway Village</x:v>
       </x:c>
       <x:c r="G25" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H25" s="9" t="str">
-        <x:v>Ward's Point Conservation Area</x:v>
+        <x:v>Gage and Tollner Restaurant</x:v>
       </x:c>
       <x:c r="I25" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J25" s="9" t="str">
-        <x:v>C. Rieger's Sons Factory</x:v>
+        <x:v>Spear &amp; Company Factory</x:v>
       </x:c>
       <x:c r="K25" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L25" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1303,28 +1303,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Crotona Play Center</x:v>
+        <x:v>McGolrick, Monsignor, Park and Shelter Pavilion</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>Parkway Theater</x:v>
+        <x:v>Morgan Library</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H26" s="9" t="str">
-        <x:v>Maple Grove Cemetery</x:v>
+        <x:v>Lighthouse</x:v>
       </x:c>
       <x:c r="I26" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J26" s="9" t="str">
-        <x:v>Kreuzer-Pelton House</x:v>
+        <x:v>Cornell Farmhouse</x:v>
       </x:c>
       <x:c r="K26" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L26" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1342,25 +1342,25 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>Jeffrey's Hook Lighthouse</x:v>
+        <x:v>Old Town of Flushing Burial Ground</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F27" s="9" t="str">
-        <x:v>Flushing Town Hall</x:v>
+        <x:v>Eastern Parkway</x:v>
       </x:c>
       <x:c r="G27" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H27" s="9" t="str">
-        <x:v>Boston Road Plaza</x:v>
+        <x:v>DeLamar Mansion</x:v>
       </x:c>
       <x:c r="I27" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J27" s="9" t="str">
-        <x:v>Immanuel Union Church</x:v>
+        <x:v>LaTourette House</x:v>
       </x:c>
       <x:c r="K27" s="9" t="str">
         <x:v>Staten Island</x:v>
@@ -1381,28 +1381,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>B &amp; B Carousell</x:v>
+        <x:v>Trinity Church and Graveyard</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F28" s="9" t="str">
-        <x:v>Fort Schuyler</x:v>
+        <x:v>RKO Keith's Theater</x:v>
       </x:c>
       <x:c r="G28" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="H28" s="9" t="str">
-        <x:v>Queens County Savings Bank, Kew Gardens Hills Branch</x:v>
+        <x:v>Casita Rincon Criollo</x:v>
       </x:c>
       <x:c r="I28" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J28" s="9" t="str">
-        <x:v>Christ Church New Brighton</x:v>
+        <x:v>Bayard-Condict Building</x:v>
       </x:c>
       <x:c r="K28" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L28" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1420,28 +1420,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>U.S. Army Military Ocean Terminal</x:v>
+        <x:v>Loew's King Theatre</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F29" s="9" t="str">
-        <x:v>Old Orchard Shoal Light Station</x:v>
+        <x:v>Crotona Play Center</x:v>
       </x:c>
       <x:c r="G29" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H29" s="9" t="str">
-        <x:v>Office of the Register</x:v>
+        <x:v>Trinity Chapel</x:v>
       </x:c>
       <x:c r="I29" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J29" s="9" t="str">
-        <x:v>Reformed Church of Melrose</x:v>
+        <x:v>New York Congregational Home for the Aged</x:v>
       </x:c>
       <x:c r="K29" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L29" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1459,28 +1459,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>Ocean Parkway Jewish Center</x:v>
+        <x:v>Castle Clinton National Monument</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F30" s="9" t="str">
-        <x:v>Staten Island Ferry Terminal</x:v>
+        <x:v>Queensboro Bridge</x:v>
       </x:c>
       <x:c r="G30" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H30" s="9" t="str">
-        <x:v>Long Island City Courthouse Complex</x:v>
+        <x:v>First Reformed Church of College Point</x:v>
       </x:c>
       <x:c r="I30" s="9" t="str">
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="J30" s="9" t="str">
-        <x:v>St. Anselm's Roman Catholic Church Complex</x:v>
+        <x:v>Trinity Lutheran Church</x:v>
       </x:c>
       <x:c r="K30" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L30" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1498,28 +1498,28 @@
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>African Burial Ground</x:v>
+        <x:v>Parkway Theater</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v>Long Island Motor Parkway</x:v>
+        <x:v>B &amp; B Carousell</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H31" s="9" t="str">
-        <x:v>Mary A. Whalen</x:v>
+        <x:v>Joralemon Street Tunnel (IRT)</x:v>
       </x:c>
       <x:c r="I31" s="9" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J31" s="9" t="str">
-        <x:v>Louis A. and Laura Stirn House</x:v>
+        <x:v>Decker Building</x:v>
       </x:c>
       <x:c r="K31" s="9" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="L31" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1537,28 +1537,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>Ed Sullivan Theater</x:v>
+        <x:v>Flushing Town Hall</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v>Hamilton Grange National Memorial</x:v>
+        <x:v>U.S. Army Military Ocean Terminal</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="H32" s="9" t="str">
-        <x:v>Casemate Fort, Whiting Quadrangle</x:v>
+        <x:v>Ottendorfer Public Library and Stuyvesant Polyclinic Hospital</x:v>
       </x:c>
       <x:c r="I32" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J32" s="9" t="str">
-        <x:v>Conrad Voelcker House</x:v>
+        <x:v>English Evangelical Lutheran Church of the Reformation</x:v>
       </x:c>
       <x:c r="K32" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="L32" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1576,28 +1576,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>New York Public Library</x:v>
+        <x:v>American Stock Exchange</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F33" s="9" t="str">
-        <x:v>Morgan Library</x:v>
+        <x:v>Fort Schuyler</x:v>
       </x:c>
       <x:c r="G33" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="H33" s="9" t="str">
-        <x:v>Beth-El Jewish Center of Flatbush</x:v>
+        <x:v>Sheffield Farms Stable</x:v>
       </x:c>
       <x:c r="I33" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="J33" s="9" t="str">
-        <x:v>Sohmer Piano Factory</x:v>
+        <x:v>Boardman- Mitchell House</x:v>
       </x:c>
       <x:c r="K33" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L33" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1615,28 +1615,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>Trinity Church and Graveyard</x:v>
+        <x:v>Ocean Parkway Jewish Center</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="F34" s="9" t="str">
-        <x:v>Castle Clinton National Monument</x:v>
+        <x:v>Old Orchard Shoal Light Station</x:v>
       </x:c>
       <x:c r="G34" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H34" s="9" t="str">
-        <x:v>Gage and Tollner Restaurant</x:v>
+        <x:v>Flushing High School</x:v>
       </x:c>
       <x:c r="I34" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="J34" s="9" t="str">
-        <x:v>Saint James Church</x:v>
+        <x:v>Valentine-Varian House</x:v>
       </x:c>
       <x:c r="K34" s="9" t="str">
-        <x:v>Queens</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="L34" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1654,28 +1654,28 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>Queensboro Bridge</x:v>
+        <x:v>Whitney Museum of American Art</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="F35" s="9" t="str">
-        <x:v>American Stock Exchange</x:v>
+        <x:v>Staten Island Ferry Terminal</x:v>
       </x:c>
       <x:c r="G35" s="9" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="H35" s="9" t="str">
-        <x:v>Joralemon Street Tunnel (IRT)</x:v>
+        <x:v>United Workers' Cooperatives</x:v>
       </x:c>
       <x:c r="I35" s="9" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="J35" s="9" t="str">
-        <x:v>Spaulding, Henry F., Coachman's House</x:v>
+        <x:v>Conrad Voelcker House</x:v>
       </x:c>
       <x:c r="K35" s="9" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="L35" s="16" t="str">
         <x:v>scheduled</x:v>
@@ -1693,10 +1693,10 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>Whitney Museum of American Art</x:v>
+        <x:v>Long Island Motor Parkway</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
         <x:v>College of the City of New York</x:v>
@@ -1711,10 +1711,10 @@
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="J36" s="11" t="str">
-        <x:v>Jamaica Savings Bank</x:v>
+        <x:v>McFarlane-Bredt House</x:v>
       </x:c>
       <x:c r="K36" s="11" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="L36" s="17" t="str">
         <x:v>scheduled</x:v>

--- a/exports/daily-games.xlsx
+++ b/exports/daily-games.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="R27a0945120064f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Locations" sheetId="2" r:id="Rfc0846ec19494109"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog Summary" sheetId="3" r:id="Raad1979b850d4996"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dedupe Review" sheetId="4" r:id="Raf7a4a216f65409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="R466b08c82aff479a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Locations" sheetId="2" r:id="Rbaac8aed3c6b4409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog Summary" sheetId="3" r:id="R1a4046e0dd7a456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dedupe Review" sheetId="4" r:id="Rb3bfeb887b704569"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -893,10 +893,10 @@
         <x:v>Queens</x:v>
       </x:c>
       <x:c r="H2" s="85" t="str">
-        <x:v>loc-0452</x:v>
+        <x:v>loc-0469</x:v>
       </x:c>
       <x:c r="I2" s="85" t="str">
-        <x:v>Trump Tower</x:v>
+        <x:v>Bank of America Tower</x:v>
       </x:c>
       <x:c r="J2" s="85" t="str">
         <x:v>Manhattan</x:v>
@@ -1217,10 +1217,10 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="H8" s="85" t="str">
-        <x:v>loc-0469</x:v>
+        <x:v>loc-0452</x:v>
       </x:c>
       <x:c r="I8" s="85" t="str">
-        <x:v>Bank of America Tower</x:v>
+        <x:v>Trump Tower</x:v>
       </x:c>
       <x:c r="J8" s="85" t="str">
         <x:v>Manhattan</x:v>
@@ -4923,7 +4923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3faaed5333f4bf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55fe259df43046df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23803,7 +23803,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab095198ca0f4118"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1792a3ebb2734274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27445,7 +27445,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf657f4dec6ab4182"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66f6f4c860574a05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/exports/daily-games.xlsx
+++ b/exports/daily-games.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="R466b08c82aff479a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Locations" sheetId="2" r:id="Rbaac8aed3c6b4409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog Summary" sheetId="3" r:id="R1a4046e0dd7a456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dedupe Review" sheetId="4" r:id="Rb3bfeb887b704569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Games" sheetId="1" r:id="R23d79692eed64fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Locations" sheetId="2" r:id="Ra6527391da284bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog Summary" sheetId="3" r:id="R991f24cea0bd4dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dedupe Review" sheetId="4" r:id="R9fd6ee41fd1b46a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -128,6 +128,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF0B3C68"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0D426D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFCDEFFC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -296,7 +311,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="117">
+  <x:cellXfs count="143">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -490,6 +505,52 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="14" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="6" fillId="14" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="6" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="6" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="17" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="17" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -799,130 +860,165 @@
     <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="32" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="32" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="32" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="12" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="13" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="83" t="str">
+      <x:c r="A1" s="122" t="str">
         <x:v>date</x:v>
       </x:c>
-      <x:c r="B1" s="83" t="str">
-        <x:v>q1_easy_id</x:v>
-      </x:c>
-      <x:c r="C1" s="83" t="str">
-        <x:v>q1_easy</x:v>
-      </x:c>
-      <x:c r="D1" s="83" t="str">
+      <x:c r="B1" s="122" t="str">
+        <x:v>q1_id</x:v>
+      </x:c>
+      <x:c r="C1" s="122" t="str">
+        <x:v>q1_name</x:v>
+      </x:c>
+      <x:c r="D1" s="122" t="str">
         <x:v>q1_borough</x:v>
       </x:c>
-      <x:c r="E1" s="83" t="str">
-        <x:v>q2_easy_id</x:v>
-      </x:c>
-      <x:c r="F1" s="83" t="str">
-        <x:v>q2_easy</x:v>
-      </x:c>
-      <x:c r="G1" s="83" t="str">
+      <x:c r="E1" s="122" t="str">
+        <x:v>q1_difficulty</x:v>
+      </x:c>
+      <x:c r="F1" s="122" t="str">
+        <x:v>q2_id</x:v>
+      </x:c>
+      <x:c r="G1" s="122" t="str">
+        <x:v>q2_name</x:v>
+      </x:c>
+      <x:c r="H1" s="122" t="str">
         <x:v>q2_borough</x:v>
       </x:c>
-      <x:c r="H1" s="83" t="str">
-        <x:v>q3_medium_id</x:v>
-      </x:c>
-      <x:c r="I1" s="83" t="str">
-        <x:v>q3_medium</x:v>
-      </x:c>
-      <x:c r="J1" s="83" t="str">
+      <x:c r="I1" s="122" t="str">
+        <x:v>q2_difficulty</x:v>
+      </x:c>
+      <x:c r="J1" s="122" t="str">
+        <x:v>q3_id</x:v>
+      </x:c>
+      <x:c r="K1" s="122" t="str">
+        <x:v>q3_name</x:v>
+      </x:c>
+      <x:c r="L1" s="122" t="str">
         <x:v>q3_borough</x:v>
       </x:c>
-      <x:c r="K1" s="83" t="str">
-        <x:v>q4_medium_id</x:v>
-      </x:c>
-      <x:c r="L1" s="83" t="str">
-        <x:v>q4_medium</x:v>
-      </x:c>
-      <x:c r="M1" s="83" t="str">
+      <x:c r="M1" s="122" t="str">
+        <x:v>q3_difficulty</x:v>
+      </x:c>
+      <x:c r="N1" s="122" t="str">
+        <x:v>q4_id</x:v>
+      </x:c>
+      <x:c r="O1" s="122" t="str">
+        <x:v>q4_name</x:v>
+      </x:c>
+      <x:c r="P1" s="122" t="str">
         <x:v>q4_borough</x:v>
       </x:c>
-      <x:c r="N1" s="83" t="str">
-        <x:v>q5_hard_id</x:v>
-      </x:c>
-      <x:c r="O1" s="83" t="str">
-        <x:v>q5_hard</x:v>
-      </x:c>
-      <x:c r="P1" s="83" t="str">
+      <x:c r="Q1" s="122" t="str">
+        <x:v>q4_difficulty</x:v>
+      </x:c>
+      <x:c r="R1" s="122" t="str">
+        <x:v>q5_id</x:v>
+      </x:c>
+      <x:c r="S1" s="122" t="str">
+        <x:v>q5_name</x:v>
+      </x:c>
+      <x:c r="T1" s="122" t="str">
         <x:v>q5_borough</x:v>
       </x:c>
-      <x:c r="Q1" s="83" t="str">
+      <x:c r="U1" s="122" t="str">
+        <x:v>q5_difficulty</x:v>
+      </x:c>
+      <x:c r="V1" s="122" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="R1" s="83" t="str">
+      <x:c r="W1" s="122" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="84" t="n">
+      <x:c r="A2" s="123" t="n">
         <x:v>46246</x:v>
       </x:c>
-      <x:c r="B2" s="85" t="str">
+      <x:c r="B2" s="124" t="str">
         <x:v>loc-0385</x:v>
       </x:c>
-      <x:c r="C2" s="85" t="str">
+      <x:c r="C2" s="124" t="str">
         <x:v>Brighton Beach Station</x:v>
       </x:c>
-      <x:c r="D2" s="85" t="str">
+      <x:c r="D2" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="E2" s="85" t="str">
+      <x:c r="E2" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F2" s="124" t="str">
         <x:v>loc-0421</x:v>
       </x:c>
-      <x:c r="F2" s="85" t="str">
+      <x:c r="G2" s="124" t="str">
         <x:v>Diversity Plaza</x:v>
       </x:c>
-      <x:c r="G2" s="85" t="str">
+      <x:c r="H2" s="124" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="H2" s="85" t="str">
+      <x:c r="I2" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J2" s="124" t="str">
         <x:v>loc-0469</x:v>
       </x:c>
-      <x:c r="I2" s="85" t="str">
+      <x:c r="K2" s="124" t="str">
         <x:v>Bank of America Tower</x:v>
       </x:c>
-      <x:c r="J2" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K2" s="85" t="str">
+      <x:c r="L2" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M2" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="N2" s="124" t="str">
         <x:v>loc-0248</x:v>
       </x:c>
-      <x:c r="L2" s="85" t="str">
+      <x:c r="O2" s="124" t="str">
         <x:v>Crotona Park</x:v>
       </x:c>
-      <x:c r="M2" s="85" t="str">
+      <x:c r="P2" s="124" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
-      <x:c r="N2" s="85" t="str">
+      <x:c r="Q2" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R2" s="124" t="str">
         <x:v>loc-0162</x:v>
       </x:c>
-      <x:c r="O2" s="85" t="str">
+      <x:c r="S2" s="124" t="str">
         <x:v>George Washington at Valley Forge</x:v>
       </x:c>
-      <x:c r="P2" s="85" t="str">
+      <x:c r="T2" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="Q2" s="85" t="str">
+      <x:c r="U2" s="124" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V2" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R2" s="85" t="str"/>
+      <x:c r="W2" s="124" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="86" t="n">
@@ -938,3992 +1034,3877 @@
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E3" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F3" s="87" t="str">
         <x:v>loc-0035</x:v>
       </x:c>
-      <x:c r="F3" s="87" t="str">
+      <x:c r="G3" s="87" t="str">
         <x:v>Louis Armstrong House</x:v>
       </x:c>
-      <x:c r="G3" s="87" t="str">
+      <x:c r="H3" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="H3" s="87" t="str">
+      <x:c r="I3" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J3" s="87" t="str">
         <x:v>loc-0433</x:v>
       </x:c>
-      <x:c r="I3" s="87" t="str">
+      <x:c r="K3" s="87" t="str">
         <x:v>Brooklyn Plaza</x:v>
       </x:c>
-      <x:c r="J3" s="87" t="str">
+      <x:c r="L3" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="K3" s="87" t="str">
+      <x:c r="M3" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="N3" s="87" t="str">
         <x:v>loc-0251</x:v>
       </x:c>
-      <x:c r="L3" s="87" t="str">
+      <x:c r="O3" s="87" t="str">
         <x:v>Highbridge Park</x:v>
       </x:c>
-      <x:c r="M3" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N3" s="87" t="str">
+      <x:c r="P3" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q3" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R3" s="87" t="str">
         <x:v>loc-0237</x:v>
       </x:c>
-      <x:c r="O3" s="87" t="str">
+      <x:c r="S3" s="87" t="str">
         <x:v>Father Capodanno Memorial</x:v>
       </x:c>
-      <x:c r="P3" s="87" t="str">
+      <x:c r="T3" s="87" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
-      <x:c r="Q3" s="87" t="str">
+      <x:c r="U3" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V3" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R3" s="87" t="str"/>
+      <x:c r="W3" s="87" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="84" t="n">
+      <x:c r="A4" s="123" t="n">
         <x:v>46248</x:v>
       </x:c>
-      <x:c r="B4" s="85" t="str">
-        <x:v>loc-0262</x:v>
-      </x:c>
-      <x:c r="C4" s="85" t="str">
-        <x:v>Washington Square Park</x:v>
-      </x:c>
-      <x:c r="D4" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E4" s="85" t="str">
-        <x:v>loc-0477</x:v>
-      </x:c>
-      <x:c r="F4" s="85" t="str">
-        <x:v>Citi Field</x:v>
-      </x:c>
-      <x:c r="G4" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H4" s="85" t="str">
-        <x:v>loc-0132</x:v>
-      </x:c>
-      <x:c r="I4" s="85" t="str">
-        <x:v>Fort Totten Officers' Club</x:v>
-      </x:c>
-      <x:c r="J4" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="K4" s="85" t="str">
-        <x:v>loc-0127</x:v>
-      </x:c>
-      <x:c r="L4" s="85" t="str">
-        <x:v>Edgewater Village Hall and Tappen Park</x:v>
-      </x:c>
-      <x:c r="M4" s="85" t="str">
+      <x:c r="B4" s="124" t="str">
+        <x:v>loc-0155</x:v>
+      </x:c>
+      <x:c r="C4" s="124" t="str">
+        <x:v>Washington Square Arch</x:v>
+      </x:c>
+      <x:c r="D4" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E4" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F4" s="124" t="str">
+        <x:v>loc-0323</x:v>
+      </x:c>
+      <x:c r="G4" s="124" t="str">
+        <x:v>Tenement Museum</x:v>
+      </x:c>
+      <x:c r="H4" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I4" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J4" s="124" t="str">
+        <x:v>loc-0338</x:v>
+      </x:c>
+      <x:c r="K4" s="124" t="str">
+        <x:v>Metropolitan Opera House</x:v>
+      </x:c>
+      <x:c r="L4" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M4" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N4" s="124" t="str">
+        <x:v>loc-0371</x:v>
+      </x:c>
+      <x:c r="O4" s="124" t="str">
+        <x:v>Children's Museum of Manhattan</x:v>
+      </x:c>
+      <x:c r="P4" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q4" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R4" s="124" t="str">
+        <x:v>loc-0288</x:v>
+      </x:c>
+      <x:c r="S4" s="124" t="str">
+        <x:v>Freshkills Park</x:v>
+      </x:c>
+      <x:c r="T4" s="124" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
-      <x:c r="N4" s="85" t="str">
-        <x:v>loc-0234</x:v>
-      </x:c>
-      <x:c r="O4" s="85" t="str">
-        <x:v>Louis J. Heintz Memorial</x:v>
-      </x:c>
-      <x:c r="P4" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q4" s="85" t="str">
+      <x:c r="U4" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V4" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R4" s="85" t="str"/>
+      <x:c r="W4" s="124" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="86" t="n">
         <x:v>46249</x:v>
       </x:c>
       <x:c r="B5" s="87" t="str">
-        <x:v>loc-0264</x:v>
+        <x:v>loc-0439</x:v>
       </x:c>
       <x:c r="C5" s="87" t="str">
-        <x:v>Union Square Park</x:v>
+        <x:v>Industry City</x:v>
       </x:c>
       <x:c r="D5" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="E5" s="87" t="str">
-        <x:v>loc-0411</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F5" s="87" t="str">
-        <x:v>Times Square Plaza</x:v>
+        <x:v>loc-0014</x:v>
       </x:c>
       <x:c r="G5" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Fraunces Tavern</x:v>
       </x:c>
       <x:c r="H5" s="87" t="str">
-        <x:v>loc-0121</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I5" s="87" t="str">
-        <x:v>BOHEMIAN HALL AND PARK</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J5" s="87" t="str">
+        <x:v>loc-0075</x:v>
+      </x:c>
+      <x:c r="K5" s="87" t="str">
+        <x:v>Parkway Village</x:v>
+      </x:c>
+      <x:c r="L5" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="K5" s="87" t="str">
-        <x:v>loc-0087</x:v>
-      </x:c>
-      <x:c r="L5" s="87" t="str">
-        <x:v>American Stock Exchange</x:v>
-      </x:c>
       <x:c r="M5" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N5" s="87" t="str">
-        <x:v>loc-0242</x:v>
+        <x:v>loc-0494</x:v>
       </x:c>
       <x:c r="O5" s="87" t="str">
-        <x:v>College Point War Memorial</x:v>
+        <x:v>Bay Plaza Shopping Center</x:v>
       </x:c>
       <x:c r="P5" s="87" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Bronx</x:v>
       </x:c>
       <x:c r="Q5" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R5" s="87" t="str">
+        <x:v>loc-0234</x:v>
+      </x:c>
+      <x:c r="S5" s="87" t="str">
+        <x:v>Louis J. Heintz Memorial</x:v>
+      </x:c>
+      <x:c r="T5" s="87" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="U5" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V5" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R5" s="87" t="str"/>
+      <x:c r="W5" s="87" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="84" t="n">
+      <x:c r="A6" s="123" t="n">
         <x:v>46250</x:v>
       </x:c>
-      <x:c r="B6" s="85" t="str">
-        <x:v>loc-0440</x:v>
-      </x:c>
-      <x:c r="C6" s="85" t="str">
-        <x:v>Chelsea Market</x:v>
-      </x:c>
-      <x:c r="D6" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E6" s="85" t="str">
-        <x:v>loc-0100</x:v>
-      </x:c>
-      <x:c r="F6" s="85" t="str">
-        <x:v>Morgan Library</x:v>
-      </x:c>
-      <x:c r="G6" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H6" s="85" t="str">
-        <x:v>loc-0289</x:v>
-      </x:c>
-      <x:c r="I6" s="85" t="str">
-        <x:v>Great Kills Park</x:v>
-      </x:c>
-      <x:c r="J6" s="85" t="str">
+      <x:c r="B6" s="124" t="str">
+        <x:v>loc-0042</x:v>
+      </x:c>
+      <x:c r="C6" s="124" t="str">
+        <x:v>Fort Wadsworth</x:v>
+      </x:c>
+      <x:c r="D6" s="124" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
-      <x:c r="K6" s="85" t="str">
-        <x:v>loc-0019</x:v>
-      </x:c>
-      <x:c r="L6" s="85" t="str">
-        <x:v>Parachute Jump</x:v>
-      </x:c>
-      <x:c r="M6" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N6" s="85" t="str">
-        <x:v>loc-0183</x:v>
-      </x:c>
-      <x:c r="O6" s="85" t="str">
-        <x:v>Jenkins Fountain</x:v>
-      </x:c>
-      <x:c r="P6" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q6" s="85" t="str">
+      <x:c r="E6" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F6" s="124" t="str">
+        <x:v>loc-0470</x:v>
+      </x:c>
+      <x:c r="G6" s="124" t="str">
+        <x:v>One World Trade Center</x:v>
+      </x:c>
+      <x:c r="H6" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I6" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J6" s="124" t="str">
+        <x:v>loc-0468</x:v>
+      </x:c>
+      <x:c r="K6" s="124" t="str">
+        <x:v>Katz's Delicatessen</x:v>
+      </x:c>
+      <x:c r="L6" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M6" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N6" s="124" t="str">
+        <x:v>loc-0314</x:v>
+      </x:c>
+      <x:c r="O6" s="124" t="str">
+        <x:v>Willowbrook Park</x:v>
+      </x:c>
+      <x:c r="P6" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="Q6" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R6" s="124" t="str">
+        <x:v>loc-0344</x:v>
+      </x:c>
+      <x:c r="S6" s="124" t="str">
+        <x:v>Drawing Center</x:v>
+      </x:c>
+      <x:c r="T6" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U6" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V6" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R6" s="85" t="str"/>
+      <x:c r="W6" s="124" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="86" t="n">
         <x:v>46251</x:v>
       </x:c>
       <x:c r="B7" s="87" t="str">
-        <x:v>loc-0021</x:v>
+        <x:v>loc-0330</x:v>
       </x:c>
       <x:c r="C7" s="87" t="str">
-        <x:v>Chrysler Building</x:v>
+        <x:v>Museum of the City of New York</x:v>
       </x:c>
       <x:c r="D7" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E7" s="87" t="str">
-        <x:v>loc-0417</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F7" s="87" t="str">
-        <x:v>Corona Plaza</x:v>
+        <x:v>loc-0010</x:v>
       </x:c>
       <x:c r="G7" s="87" t="str">
+        <x:v>The Metropolitan Museum of Art</x:v>
+      </x:c>
+      <x:c r="H7" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I7" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J7" s="87" t="str">
+        <x:v>loc-0004</x:v>
+      </x:c>
+      <x:c r="K7" s="87" t="str">
+        <x:v>Brooklyn Academy of Music</x:v>
+      </x:c>
+      <x:c r="L7" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="M7" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N7" s="87" t="str">
+        <x:v>loc-0083</x:v>
+      </x:c>
+      <x:c r="O7" s="87" t="str">
+        <x:v>Williamsbridge Oval Park</x:v>
+      </x:c>
+      <x:c r="P7" s="87" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="Q7" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R7" s="87" t="str">
+        <x:v>loc-0050</x:v>
+      </x:c>
+      <x:c r="S7" s="87" t="str">
+        <x:v>Old Quaker Meetinghouse</x:v>
+      </x:c>
+      <x:c r="T7" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="H7" s="87" t="str">
-        <x:v>loc-0339</x:v>
-      </x:c>
-      <x:c r="I7" s="87" t="str">
-        <x:v>USS Growler</x:v>
-      </x:c>
-      <x:c r="J7" s="87" t="str">
-        <x:v>New York City</x:v>
-      </x:c>
-      <x:c r="K7" s="87" t="str">
-        <x:v>loc-0376</x:v>
-      </x:c>
-      <x:c r="L7" s="87" t="str">
-        <x:v>Museum of Reclaimed Urban Space</x:v>
-      </x:c>
-      <x:c r="M7" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N7" s="87" t="str">
-        <x:v>loc-0227</x:v>
-      </x:c>
-      <x:c r="O7" s="87" t="str">
-        <x:v>Holocaust Memorial Mall</x:v>
-      </x:c>
-      <x:c r="P7" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q7" s="87" t="str">
+      <x:c r="U7" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V7" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R7" s="87" t="str"/>
+      <x:c r="W7" s="87" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="84" t="n">
+      <x:c r="A8" s="123" t="n">
         <x:v>46252</x:v>
       </x:c>
-      <x:c r="B8" s="85" t="str">
-        <x:v>loc-0399</x:v>
-      </x:c>
-      <x:c r="C8" s="85" t="str">
-        <x:v>34 Street-Penn Station Station</x:v>
-      </x:c>
-      <x:c r="D8" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E8" s="85" t="str">
-        <x:v>loc-0338</x:v>
-      </x:c>
-      <x:c r="F8" s="85" t="str">
-        <x:v>Metropolitan Opera House</x:v>
-      </x:c>
-      <x:c r="G8" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H8" s="85" t="str">
-        <x:v>loc-0452</x:v>
-      </x:c>
-      <x:c r="I8" s="85" t="str">
-        <x:v>Trump Tower</x:v>
-      </x:c>
-      <x:c r="J8" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K8" s="85" t="str">
-        <x:v>loc-0319</x:v>
-      </x:c>
-      <x:c r="L8" s="85" t="str">
-        <x:v>Crocheron Park</x:v>
-      </x:c>
-      <x:c r="M8" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N8" s="85" t="str">
-        <x:v>loc-0065</x:v>
-      </x:c>
-      <x:c r="O8" s="85" t="str">
-        <x:v>Fort Tompkins Quadrangle</x:v>
-      </x:c>
-      <x:c r="P8" s="85" t="str">
+      <x:c r="B8" s="124" t="str">
+        <x:v>loc-0024</x:v>
+      </x:c>
+      <x:c r="C8" s="124" t="str">
+        <x:v>Stonewall Inn</x:v>
+      </x:c>
+      <x:c r="D8" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E8" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F8" s="124" t="str">
+        <x:v>loc-0444</x:v>
+      </x:c>
+      <x:c r="G8" s="124" t="str">
+        <x:v>Birdland</x:v>
+      </x:c>
+      <x:c r="H8" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I8" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J8" s="124" t="str">
+        <x:v>loc-0454</x:v>
+      </x:c>
+      <x:c r="K8" s="124" t="str">
+        <x:v>Hearst Tower</x:v>
+      </x:c>
+      <x:c r="L8" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M8" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N8" s="124" t="str">
+        <x:v>loc-0275</x:v>
+      </x:c>
+      <x:c r="O8" s="124" t="str">
+        <x:v>Bronx Park</x:v>
+      </x:c>
+      <x:c r="P8" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="Q8" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R8" s="124" t="str">
+        <x:v>loc-0383</x:v>
+      </x:c>
+      <x:c r="S8" s="124" t="str">
+        <x:v>New Dorp Station</x:v>
+      </x:c>
+      <x:c r="T8" s="124" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
-      <x:c r="Q8" s="85" t="str">
+      <x:c r="U8" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V8" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R8" s="85" t="str"/>
+      <x:c r="W8" s="124" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="86" t="n">
         <x:v>46253</x:v>
       </x:c>
       <x:c r="B9" s="87" t="str">
-        <x:v>loc-0099</x:v>
+        <x:v>loc-0262</x:v>
       </x:c>
       <x:c r="C9" s="87" t="str">
-        <x:v>Gracie Mansion</x:v>
+        <x:v>Washington Square Park</x:v>
       </x:c>
       <x:c r="D9" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E9" s="87" t="str">
-        <x:v>loc-0323</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F9" s="87" t="str">
-        <x:v>Tenement Museum</x:v>
+        <x:v>loc-0021</x:v>
       </x:c>
       <x:c r="G9" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Chrysler Building</x:v>
       </x:c>
       <x:c r="H9" s="87" t="str">
-        <x:v>loc-0491</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I9" s="87" t="str">
-        <x:v>Staten Island Zoo</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J9" s="87" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>loc-0033</x:v>
       </x:c>
       <x:c r="K9" s="87" t="str">
-        <x:v>loc-0041</x:v>
+        <x:v>Carnegie Hall</x:v>
       </x:c>
       <x:c r="L9" s="87" t="str">
-        <x:v>Forest Park Carousel</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="M9" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N9" s="87" t="str">
+        <x:v>loc-0054</x:v>
+      </x:c>
+      <x:c r="O9" s="87" t="str">
+        <x:v>Theodore Roosevelt Birthplace</x:v>
+      </x:c>
+      <x:c r="P9" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q9" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R9" s="87" t="str">
+        <x:v>loc-0216</x:v>
+      </x:c>
+      <x:c r="S9" s="87" t="str">
+        <x:v>Amorphophallus Titanum</x:v>
+      </x:c>
+      <x:c r="T9" s="87" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="U9" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V9" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W9" s="87" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="123" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="B10" s="124" t="str">
+        <x:v>loc-0034</x:v>
+      </x:c>
+      <x:c r="C10" s="124" t="str">
+        <x:v>Hotel Chelsea</x:v>
+      </x:c>
+      <x:c r="D10" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E10" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F10" s="124" t="str">
+        <x:v>loc-0030</x:v>
+      </x:c>
+      <x:c r="G10" s="124" t="str">
+        <x:v>USS Intrepid (CV-11)</x:v>
+      </x:c>
+      <x:c r="H10" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I10" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J10" s="124" t="str">
+        <x:v>loc-0038</x:v>
+      </x:c>
+      <x:c r="K10" s="124" t="str">
+        <x:v>Fort Schuyler</x:v>
+      </x:c>
+      <x:c r="L10" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="M10" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N10" s="124" t="str">
+        <x:v>loc-0311</x:v>
+      </x:c>
+      <x:c r="O10" s="124" t="str">
+        <x:v>Soundview Park</x:v>
+      </x:c>
+      <x:c r="P10" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="Q10" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R10" s="124" t="str">
+        <x:v>loc-0296</x:v>
+      </x:c>
+      <x:c r="S10" s="124" t="str">
+        <x:v>Juniper Valley Park</x:v>
+      </x:c>
+      <x:c r="T10" s="124" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="N9" s="87" t="str">
-        <x:v>loc-0240</x:v>
-      </x:c>
-      <x:c r="O9" s="87" t="str">
-        <x:v>Paul Rainey Memorial Gate</x:v>
-      </x:c>
-      <x:c r="P9" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q9" s="87" t="str">
+      <x:c r="U10" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V10" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R9" s="87" t="str"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="84" t="n">
-        <x:v>46254</x:v>
-      </x:c>
-      <x:c r="B10" s="85" t="str">
-        <x:v>loc-0106</x:v>
-      </x:c>
-      <x:c r="C10" s="85" t="str">
-        <x:v>Castle Williams</x:v>
-      </x:c>
-      <x:c r="D10" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E10" s="85" t="str">
-        <x:v>loc-0030</x:v>
-      </x:c>
-      <x:c r="F10" s="85" t="str">
-        <x:v>USS Intrepid (CV-11)</x:v>
-      </x:c>
-      <x:c r="G10" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H10" s="85" t="str">
-        <x:v>loc-0414</x:v>
-      </x:c>
-      <x:c r="I10" s="85" t="str">
-        <x:v>Gansevoort Plaza</x:v>
-      </x:c>
-      <x:c r="J10" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K10" s="85" t="str">
-        <x:v>loc-0392</x:v>
-      </x:c>
-      <x:c r="L10" s="85" t="str">
-        <x:v>57 Street-7 Avenue Station</x:v>
-      </x:c>
-      <x:c r="M10" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N10" s="85" t="str">
-        <x:v>loc-0223</x:v>
-      </x:c>
-      <x:c r="O10" s="85" t="str">
-        <x:v>Bound Hands Rising Free</x:v>
-      </x:c>
-      <x:c r="P10" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q10" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R10" s="85" t="str"/>
+      <x:c r="W10" s="124" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="86" t="n">
         <x:v>46255</x:v>
       </x:c>
       <x:c r="B11" s="87" t="str">
-        <x:v>loc-0074</x:v>
+        <x:v>loc-0020</x:v>
       </x:c>
       <x:c r="C11" s="87" t="str">
-        <x:v>Parkway Theater</x:v>
+        <x:v>Rockefeller Center</x:v>
       </x:c>
       <x:c r="D11" s="87" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E11" s="87" t="str">
-        <x:v>loc-0439</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F11" s="87" t="str">
-        <x:v>Industry City</x:v>
+        <x:v>loc-0051</x:v>
       </x:c>
       <x:c r="G11" s="87" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Wave Hill</x:v>
       </x:c>
       <x:c r="H11" s="87" t="str">
-        <x:v>loc-0295</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="I11" s="87" t="str">
-        <x:v>Jamaica Bay Park</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J11" s="87" t="str">
+        <x:v>loc-0110</x:v>
+      </x:c>
+      <x:c r="K11" s="87" t="str">
+        <x:v>Greenacre Park</x:v>
+      </x:c>
+      <x:c r="L11" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M11" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N11" s="87" t="str">
+        <x:v>loc-0432</x:v>
+      </x:c>
+      <x:c r="O11" s="87" t="str">
+        <x:v>Montefiore Plaza</x:v>
+      </x:c>
+      <x:c r="P11" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q11" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R11" s="87" t="str">
+        <x:v>loc-0245</x:v>
+      </x:c>
+      <x:c r="S11" s="87" t="str">
+        <x:v>Richmond Hill War Memorial</x:v>
+      </x:c>
+      <x:c r="T11" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="K11" s="87" t="str">
-        <x:v>loc-0435</x:v>
-      </x:c>
-      <x:c r="L11" s="87" t="str">
-        <x:v>James Cagney Plaza</x:v>
-      </x:c>
-      <x:c r="M11" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N11" s="87" t="str">
-        <x:v>loc-0286</x:v>
-      </x:c>
-      <x:c r="O11" s="87" t="str">
-        <x:v>Franklin D. Roosevelt Boardwalk and Beach</x:v>
-      </x:c>
-      <x:c r="P11" s="87" t="str">
+      <x:c r="U11" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V11" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W11" s="87" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="123" t="n">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="B12" s="124" t="str">
+        <x:v>loc-0022</x:v>
+      </x:c>
+      <x:c r="C12" s="124" t="str">
+        <x:v>Flatiron Building</x:v>
+      </x:c>
+      <x:c r="D12" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E12" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F12" s="124" t="str">
+        <x:v>loc-0012</x:v>
+      </x:c>
+      <x:c r="G12" s="124" t="str">
+        <x:v>New York Stock Exchange</x:v>
+      </x:c>
+      <x:c r="H12" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I12" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J12" s="124" t="str">
+        <x:v>loc-0093</x:v>
+      </x:c>
+      <x:c r="K12" s="124" t="str">
+        <x:v>New Amsterdam Theater</x:v>
+      </x:c>
+      <x:c r="L12" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M12" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N12" s="124" t="str">
+        <x:v>loc-0273</x:v>
+      </x:c>
+      <x:c r="O12" s="124" t="str">
+        <x:v>Bloomingdale Park</x:v>
+      </x:c>
+      <x:c r="P12" s="124" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
-      <x:c r="Q11" s="87" t="str">
+      <x:c r="Q12" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R12" s="124" t="str">
+        <x:v>loc-0491</x:v>
+      </x:c>
+      <x:c r="S12" s="124" t="str">
+        <x:v>Staten Island Zoo</x:v>
+      </x:c>
+      <x:c r="T12" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="U12" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V12" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R11" s="87" t="str"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="84" t="n">
-        <x:v>46256</x:v>
-      </x:c>
-      <x:c r="B12" s="85" t="str">
-        <x:v>loc-0016</x:v>
-      </x:c>
-      <x:c r="C12" s="85" t="str">
-        <x:v>Radio City Music Hall</x:v>
-      </x:c>
-      <x:c r="D12" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E12" s="85" t="str">
-        <x:v>loc-0250</x:v>
-      </x:c>
-      <x:c r="F12" s="85" t="str">
-        <x:v>Fort Tryon Park</x:v>
-      </x:c>
-      <x:c r="G12" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H12" s="85" t="str">
-        <x:v>loc-0448</x:v>
-      </x:c>
-      <x:c r="I12" s="85" t="str">
-        <x:v>Oyster Bar</x:v>
-      </x:c>
-      <x:c r="J12" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K12" s="85" t="str">
-        <x:v>loc-0044</x:v>
-      </x:c>
-      <x:c r="L12" s="85" t="str">
-        <x:v>Brooklyn Public Library</x:v>
-      </x:c>
-      <x:c r="M12" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N12" s="85" t="str">
-        <x:v>loc-0073</x:v>
-      </x:c>
-      <x:c r="O12" s="85" t="str">
-        <x:v>Old Town of Flushing Burial Ground</x:v>
-      </x:c>
-      <x:c r="P12" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q12" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R12" s="85" t="str"/>
+      <x:c r="W12" s="124" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="86" t="n">
         <x:v>46257</x:v>
       </x:c>
       <x:c r="B13" s="87" t="str">
-        <x:v>loc-0378</x:v>
+        <x:v>loc-0074</x:v>
       </x:c>
       <x:c r="C13" s="87" t="str">
-        <x:v>Intrepid Sea, Air &amp; Space Museum</x:v>
+        <x:v>Parkway Theater</x:v>
       </x:c>
       <x:c r="D13" s="87" t="str">
-        <x:v>New York City</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="E13" s="87" t="str">
-        <x:v>loc-0461</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F13" s="87" t="str">
-        <x:v>Citigroup Center</x:v>
+        <x:v>loc-0472</x:v>
       </x:c>
       <x:c r="G13" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Peter Luger Steak House</x:v>
       </x:c>
       <x:c r="H13" s="87" t="str">
-        <x:v>loc-0282</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="I13" s="87" t="str">
-        <x:v>Dyker Beach Park</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J13" s="87" t="str">
+        <x:v>loc-0060</x:v>
+      </x:c>
+      <x:c r="K13" s="87" t="str">
+        <x:v>Voorlezer's House</x:v>
+      </x:c>
+      <x:c r="L13" s="87" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="M13" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N13" s="87" t="str">
+        <x:v>loc-0104</x:v>
+      </x:c>
+      <x:c r="O13" s="87" t="str">
+        <x:v>Bowling Green Fence and Park</x:v>
+      </x:c>
+      <x:c r="P13" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q13" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R13" s="87" t="str">
+        <x:v>loc-0209</x:v>
+      </x:c>
+      <x:c r="S13" s="87" t="str">
+        <x:v>Bushwick War Memorial</x:v>
+      </x:c>
+      <x:c r="T13" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="K13" s="87" t="str">
-        <x:v>loc-0387</x:v>
-      </x:c>
-      <x:c r="L13" s="87" t="str">
-        <x:v>High Street Station</x:v>
-      </x:c>
-      <x:c r="M13" s="87" t="str">
+      <x:c r="U13" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V13" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W13" s="87" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="123" t="n">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="B14" s="124" t="str">
+        <x:v>loc-0436</x:v>
+      </x:c>
+      <x:c r="C14" s="124" t="str">
+        <x:v>Bronx Zoo</x:v>
+      </x:c>
+      <x:c r="D14" s="124" t="str">
+        <x:v>Bronx</x:v>
+      </x:c>
+      <x:c r="E14" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F14" s="124" t="str">
+        <x:v>loc-0269</x:v>
+      </x:c>
+      <x:c r="G14" s="124" t="str">
+        <x:v>Pelham Bay Park</x:v>
+      </x:c>
+      <x:c r="H14" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="I14" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J14" s="124" t="str">
+        <x:v>loc-0057</x:v>
+      </x:c>
+      <x:c r="K14" s="124" t="str">
+        <x:v>Steinway House</x:v>
+      </x:c>
+      <x:c r="L14" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="M14" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N14" s="124" t="str">
+        <x:v>loc-0044</x:v>
+      </x:c>
+      <x:c r="O14" s="124" t="str">
+        <x:v>Brooklyn Public Library</x:v>
+      </x:c>
+      <x:c r="P14" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="N13" s="87" t="str">
-        <x:v>loc-0373</x:v>
-      </x:c>
-      <x:c r="O13" s="87" t="str">
-        <x:v>National Museum of Mathematics</x:v>
-      </x:c>
-      <x:c r="P13" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q13" s="87" t="str">
+      <x:c r="Q14" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R14" s="124" t="str">
+        <x:v>loc-0425</x:v>
+      </x:c>
+      <x:c r="S14" s="124" t="str">
+        <x:v>Bogardus Plaza</x:v>
+      </x:c>
+      <x:c r="T14" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U14" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V14" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R13" s="87" t="str"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="84" t="n">
-        <x:v>46258</x:v>
-      </x:c>
-      <x:c r="B14" s="85" t="str">
-        <x:v>loc-0334</x:v>
-      </x:c>
-      <x:c r="C14" s="85" t="str">
-        <x:v>Beacon Theatre</x:v>
-      </x:c>
-      <x:c r="D14" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E14" s="85" t="str">
-        <x:v>loc-0155</x:v>
-      </x:c>
-      <x:c r="F14" s="85" t="str">
-        <x:v>Washington Square Arch</x:v>
-      </x:c>
-      <x:c r="G14" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H14" s="85" t="str">
-        <x:v>loc-0361</x:v>
-      </x:c>
-      <x:c r="I14" s="85" t="str">
-        <x:v>Mount Vernon Hotel Museum</x:v>
-      </x:c>
-      <x:c r="J14" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K14" s="85" t="str">
-        <x:v>loc-0389</x:v>
-      </x:c>
-      <x:c r="L14" s="85" t="str">
-        <x:v>125 Street Station</x:v>
-      </x:c>
-      <x:c r="M14" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N14" s="85" t="str">
-        <x:v>loc-0117</x:v>
-      </x:c>
-      <x:c r="O14" s="85" t="str">
-        <x:v>Sheffield Farms Stable</x:v>
-      </x:c>
-      <x:c r="P14" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q14" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R14" s="85" t="str"/>
+      <x:c r="W14" s="124" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="86" t="n">
         <x:v>46259</x:v>
       </x:c>
       <x:c r="B15" s="87" t="str">
-        <x:v>loc-0096</x:v>
+        <x:v>loc-0106</x:v>
       </x:c>
       <x:c r="C15" s="87" t="str">
-        <x:v>The Public Theater</x:v>
+        <x:v>Castle Williams</x:v>
       </x:c>
       <x:c r="D15" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E15" s="87" t="str">
-        <x:v>loc-0454</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F15" s="87" t="str">
-        <x:v>Hearst Tower</x:v>
+        <x:v>loc-0404</x:v>
       </x:c>
       <x:c r="G15" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Atlantic Avenue-Barclays Center Station</x:v>
       </x:c>
       <x:c r="H15" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="I15" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J15" s="87" t="str">
+        <x:v>loc-0327</x:v>
+      </x:c>
+      <x:c r="K15" s="87" t="str">
+        <x:v>New York Transit Museum</x:v>
+      </x:c>
+      <x:c r="L15" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="M15" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N15" s="87" t="str">
+        <x:v>loc-0402</x:v>
+      </x:c>
+      <x:c r="O15" s="87" t="str">
+        <x:v>86 Street Station</x:v>
+      </x:c>
+      <x:c r="P15" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q15" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R15" s="87" t="str">
+        <x:v>loc-0160</x:v>
+      </x:c>
+      <x:c r="S15" s="87" t="str">
+        <x:v>Christopher Columbus</x:v>
+      </x:c>
+      <x:c r="T15" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="U15" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V15" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W15" s="87" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="123" t="n">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="B16" s="124" t="str">
+        <x:v>loc-0053</x:v>
+      </x:c>
+      <x:c r="C16" s="124" t="str">
+        <x:v>King Manor</x:v>
+      </x:c>
+      <x:c r="D16" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="E16" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F16" s="124" t="str">
+        <x:v>loc-0395</x:v>
+      </x:c>
+      <x:c r="G16" s="124" t="str">
+        <x:v>Coney Island-Stillwell Avenue Station</x:v>
+      </x:c>
+      <x:c r="H16" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="I16" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J16" s="124" t="str">
+        <x:v>loc-0463</x:v>
+      </x:c>
+      <x:c r="K16" s="124" t="str">
+        <x:v>MetLife Building</x:v>
+      </x:c>
+      <x:c r="L16" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M16" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N16" s="124" t="str">
+        <x:v>loc-0300</x:v>
+      </x:c>
+      <x:c r="O16" s="124" t="str">
+        <x:v>Little Bay Park</x:v>
+      </x:c>
+      <x:c r="P16" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="Q16" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R16" s="124" t="str">
         <x:v>loc-0476</x:v>
       </x:c>
-      <x:c r="I15" s="87" t="str">
+      <x:c r="S16" s="124" t="str">
         <x:v>Sylvia's Restaurant of Harlem</x:v>
       </x:c>
-      <x:c r="J15" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K15" s="87" t="str">
-        <x:v>loc-0278</x:v>
-      </x:c>
-      <x:c r="L15" s="87" t="str">
-        <x:v>Calvert Vaux Park</x:v>
-      </x:c>
-      <x:c r="M15" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N15" s="87" t="str">
-        <x:v>loc-0148</x:v>
-      </x:c>
-      <x:c r="O15" s="87" t="str">
-        <x:v>Victory, Peace and Love of County</x:v>
-      </x:c>
-      <x:c r="P15" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q15" s="87" t="str">
+      <x:c r="T16" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U16" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V16" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R15" s="87" t="str"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="84" t="n">
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="B16" s="85" t="str">
-        <x:v>loc-0490</x:v>
-      </x:c>
-      <x:c r="C16" s="85" t="str">
-        <x:v>New York Aquarium</x:v>
-      </x:c>
-      <x:c r="D16" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="E16" s="85" t="str">
-        <x:v>loc-0249</x:v>
-      </x:c>
-      <x:c r="F16" s="85" t="str">
-        <x:v>Flushing Meadows Corona Park</x:v>
-      </x:c>
-      <x:c r="G16" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H16" s="85" t="str">
-        <x:v>loc-0246</x:v>
-      </x:c>
-      <x:c r="I16" s="85" t="str">
-        <x:v>Clove Lakes Park</x:v>
-      </x:c>
-      <x:c r="J16" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="K16" s="85" t="str">
-        <x:v>loc-0280</x:v>
-      </x:c>
-      <x:c r="L16" s="85" t="str">
-        <x:v>Crescent Beach Park</x:v>
-      </x:c>
-      <x:c r="M16" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="N16" s="85" t="str">
-        <x:v>loc-0111</x:v>
-      </x:c>
-      <x:c r="O16" s="85" t="str">
-        <x:v>Harlem Fire Watchtower</x:v>
-      </x:c>
-      <x:c r="P16" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q16" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R16" s="85" t="str"/>
+      <x:c r="W16" s="124" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="86" t="n">
         <x:v>46261</x:v>
       </x:c>
       <x:c r="B17" s="87" t="str">
-        <x:v>loc-0092</x:v>
+        <x:v>loc-0205</x:v>
       </x:c>
       <x:c r="C17" s="87" t="str">
-        <x:v>Morris–Jumel Mansion</x:v>
+        <x:v>Rockefeller Fountain</x:v>
       </x:c>
       <x:c r="D17" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="E17" s="87" t="str">
-        <x:v>loc-0332</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F17" s="87" t="str">
-        <x:v>Cooper Hewitt, Smithsonian Design Museum</x:v>
+        <x:v>loc-0457</x:v>
       </x:c>
       <x:c r="G17" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Algonquin Hotel</x:v>
       </x:c>
       <x:c r="H17" s="87" t="str">
-        <x:v>loc-0086</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I17" s="87" t="str">
-        <x:v>Ward, Caleb T., Mansion</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J17" s="87" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>loc-0018</x:v>
       </x:c>
       <x:c r="K17" s="87" t="str">
-        <x:v>loc-0424</x:v>
+        <x:v>Empire State Building</x:v>
       </x:c>
       <x:c r="L17" s="87" t="str">
-        <x:v>Astor Place Plaza</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="M17" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N17" s="87" t="str">
-        <x:v>loc-0263</x:v>
+        <x:v>loc-0297</x:v>
       </x:c>
       <x:c r="O17" s="87" t="str">
-        <x:v>Riverside Park South</x:v>
+        <x:v>Kissena Corridor Park</x:v>
       </x:c>
       <x:c r="P17" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="Q17" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R17" s="87" t="str">
+        <x:v>loc-0202</x:v>
+      </x:c>
+      <x:c r="S17" s="87" t="str">
+        <x:v>Happy Land Memorial</x:v>
+      </x:c>
+      <x:c r="T17" s="87" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="U17" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V17" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R17" s="87" t="str"/>
+      <x:c r="W17" s="87" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="84" t="n">
+      <x:c r="A18" s="123" t="n">
         <x:v>46262</x:v>
       </x:c>
-      <x:c r="B18" s="85" t="str">
-        <x:v>loc-0449</x:v>
-      </x:c>
-      <x:c r="C18" s="85" t="str">
-        <x:v>Joe's Pizza</x:v>
-      </x:c>
-      <x:c r="D18" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E18" s="85" t="str">
-        <x:v>loc-0034</x:v>
-      </x:c>
-      <x:c r="F18" s="85" t="str">
-        <x:v>Hotel Chelsea</x:v>
-      </x:c>
-      <x:c r="G18" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H18" s="85" t="str">
-        <x:v>loc-0386</x:v>
-      </x:c>
-      <x:c r="I18" s="85" t="str">
-        <x:v>Broadway Junction Station</x:v>
-      </x:c>
-      <x:c r="J18" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="K18" s="85" t="str">
-        <x:v>loc-0445</x:v>
-      </x:c>
-      <x:c r="L18" s="85" t="str">
-        <x:v>Studio 54</x:v>
-      </x:c>
-      <x:c r="M18" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N18" s="85" t="str">
-        <x:v>loc-0308</x:v>
-      </x:c>
-      <x:c r="O18" s="85" t="str">
-        <x:v>Reed's Basket Willow Swamp Park</x:v>
-      </x:c>
-      <x:c r="P18" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="Q18" s="85" t="str">
+      <x:c r="B18" s="124" t="str">
+        <x:v>loc-0480</x:v>
+      </x:c>
+      <x:c r="C18" s="124" t="str">
+        <x:v>Etihad Park</x:v>
+      </x:c>
+      <x:c r="D18" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="E18" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F18" s="124" t="str">
+        <x:v>loc-0112</x:v>
+      </x:c>
+      <x:c r="G18" s="124" t="str">
+        <x:v>Hudson Theater</x:v>
+      </x:c>
+      <x:c r="H18" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I18" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J18" s="124" t="str">
+        <x:v>loc-0261</x:v>
+      </x:c>
+      <x:c r="K18" s="124" t="str">
+        <x:v>Tompkins Square Park</x:v>
+      </x:c>
+      <x:c r="L18" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M18" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N18" s="124" t="str">
+        <x:v>loc-0283</x:v>
+      </x:c>
+      <x:c r="O18" s="124" t="str">
+        <x:v>Ferry Point Park</x:v>
+      </x:c>
+      <x:c r="P18" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="Q18" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R18" s="124" t="str">
+        <x:v>loc-0392</x:v>
+      </x:c>
+      <x:c r="S18" s="124" t="str">
+        <x:v>57 Street-7 Avenue Station</x:v>
+      </x:c>
+      <x:c r="T18" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U18" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V18" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R18" s="85" t="str"/>
+      <x:c r="W18" s="124" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="86" t="n">
         <x:v>46263</x:v>
       </x:c>
       <x:c r="B19" s="87" t="str">
-        <x:v>loc-0390</x:v>
+        <x:v>loc-0336</x:v>
       </x:c>
       <x:c r="C19" s="87" t="str">
-        <x:v>14 Street-Union Square Station</x:v>
+        <x:v>Village Vanguard</x:v>
       </x:c>
       <x:c r="D19" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E19" s="87" t="str">
-        <x:v>loc-0324</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F19" s="87" t="str">
-        <x:v>El Museo del Barrio</x:v>
+        <x:v>loc-0337</x:v>
       </x:c>
       <x:c r="G19" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Blue Note Jazz Club</x:v>
       </x:c>
       <x:c r="H19" s="87" t="str">
-        <x:v>loc-0267</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I19" s="87" t="str">
-        <x:v>Hunts Point Riverside Park</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J19" s="87" t="str">
+        <x:v>loc-0325</x:v>
+      </x:c>
+      <x:c r="K19" s="87" t="str">
+        <x:v>Museum of Modern Art</x:v>
+      </x:c>
+      <x:c r="L19" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M19" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N19" s="87" t="str">
+        <x:v>loc-0129</x:v>
+      </x:c>
+      <x:c r="O19" s="87" t="str">
+        <x:v>Erasmus Hall Academy</x:v>
+      </x:c>
+      <x:c r="P19" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="Q19" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R19" s="87" t="str">
+        <x:v>loc-0350</x:v>
+      </x:c>
+      <x:c r="S19" s="87" t="str">
+        <x:v>Microscope Gallery</x:v>
+      </x:c>
+      <x:c r="T19" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="U19" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V19" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W19" s="87" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="123" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="B20" s="124" t="str">
+        <x:v>loc-0442</x:v>
+      </x:c>
+      <x:c r="C20" s="124" t="str">
+        <x:v>Westfield World Trade Center</x:v>
+      </x:c>
+      <x:c r="D20" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E20" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F20" s="124" t="str">
+        <x:v>loc-0270</x:v>
+      </x:c>
+      <x:c r="G20" s="124" t="str">
+        <x:v>Van Cortlandt Park</x:v>
+      </x:c>
+      <x:c r="H20" s="124" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
-      <x:c r="K19" s="87" t="str">
-        <x:v>loc-0300</x:v>
-      </x:c>
-      <x:c r="L19" s="87" t="str">
-        <x:v>Little Bay Park</x:v>
-      </x:c>
-      <x:c r="M19" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N19" s="87" t="str">
-        <x:v>loc-0197</x:v>
-      </x:c>
-      <x:c r="O19" s="87" t="str">
-        <x:v>Sunnyside Memorial</x:v>
-      </x:c>
-      <x:c r="P19" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q19" s="87" t="str">
+      <x:c r="I20" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J20" s="124" t="str">
+        <x:v>loc-0456</x:v>
+      </x:c>
+      <x:c r="K20" s="124" t="str">
+        <x:v>One Vanderbilt</x:v>
+      </x:c>
+      <x:c r="L20" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M20" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N20" s="124" t="str">
+        <x:v>loc-0258</x:v>
+      </x:c>
+      <x:c r="O20" s="124" t="str">
+        <x:v>McCarren Park</x:v>
+      </x:c>
+      <x:c r="P20" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="Q20" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R20" s="124" t="str">
+        <x:v>loc-0475</x:v>
+      </x:c>
+      <x:c r="S20" s="124" t="str">
+        <x:v>Manhattan Municipal Building</x:v>
+      </x:c>
+      <x:c r="T20" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U20" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V20" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R19" s="87" t="str"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="84" t="n">
-        <x:v>46264</x:v>
-      </x:c>
-      <x:c r="B20" s="85" t="str">
-        <x:v>loc-0462</x:v>
-      </x:c>
-      <x:c r="C20" s="85" t="str">
-        <x:v>Keens Steakhouse</x:v>
-      </x:c>
-      <x:c r="D20" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E20" s="85" t="str">
-        <x:v>loc-0455</x:v>
-      </x:c>
-      <x:c r="F20" s="85" t="str">
-        <x:v>Le Bernardin</x:v>
-      </x:c>
-      <x:c r="G20" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H20" s="85" t="str">
-        <x:v>loc-0098</x:v>
-      </x:c>
-      <x:c r="I20" s="85" t="str">
-        <x:v>Ed Sullivan Theater</x:v>
-      </x:c>
-      <x:c r="J20" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K20" s="85" t="str">
-        <x:v>loc-0104</x:v>
-      </x:c>
-      <x:c r="L20" s="85" t="str">
-        <x:v>Bowling Green Fence and Park</x:v>
-      </x:c>
-      <x:c r="M20" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N20" s="85" t="str">
-        <x:v>loc-0150</x:v>
-      </x:c>
-      <x:c r="O20" s="85" t="str">
-        <x:v>Jackie Robinson and Pee Wee Reese Monument</x:v>
-      </x:c>
-      <x:c r="P20" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q20" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R20" s="85" t="str"/>
+      <x:c r="W20" s="124" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="86" t="n">
         <x:v>46265</x:v>
       </x:c>
       <x:c r="B21" s="87" t="str">
-        <x:v>loc-0468</x:v>
+        <x:v>loc-0028</x:v>
       </x:c>
       <x:c r="C21" s="87" t="str">
-        <x:v>Katz's Delicatessen</x:v>
+        <x:v>Grant’s Tomb</x:v>
       </x:c>
       <x:c r="D21" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E21" s="87" t="str">
-        <x:v>loc-0470</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F21" s="87" t="str">
-        <x:v>One World Trade Center</x:v>
+        <x:v>loc-0055</x:v>
       </x:c>
       <x:c r="G21" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Sailors' Snug Harbor</x:v>
       </x:c>
       <x:c r="H21" s="87" t="str">
-        <x:v>loc-0340</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="I21" s="87" t="str">
-        <x:v>Dyckman House</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J21" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>loc-0061</x:v>
       </x:c>
       <x:c r="K21" s="87" t="str">
-        <x:v>loc-0317</x:v>
+        <x:v>Alice Austen House</x:v>
       </x:c>
       <x:c r="L21" s="87" t="str">
-        <x:v>Harlem River Park</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="M21" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N21" s="87" t="str">
-        <x:v>loc-0175</x:v>
+        <x:v>loc-0290</x:v>
       </x:c>
       <x:c r="O21" s="87" t="str">
-        <x:v>Bailey Fountain</x:v>
+        <x:v>Hart Island</x:v>
       </x:c>
       <x:c r="P21" s="87" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="Q21" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R21" s="87" t="str">
+        <x:v>loc-0356</x:v>
+      </x:c>
+      <x:c r="S21" s="87" t="str">
+        <x:v>Nicholas Roerich Museum</x:v>
+      </x:c>
+      <x:c r="T21" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U21" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V21" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R21" s="87" t="str"/>
+      <x:c r="W21" s="87" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="84" t="n">
+      <x:c r="A22" s="123" t="n">
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="B22" s="85" t="str">
-        <x:v>loc-0444</x:v>
-      </x:c>
-      <x:c r="C22" s="85" t="str">
-        <x:v>Birdland</x:v>
-      </x:c>
-      <x:c r="D22" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E22" s="85" t="str">
-        <x:v>loc-0055</x:v>
-      </x:c>
-      <x:c r="F22" s="85" t="str">
-        <x:v>Sailors' Snug Harbor</x:v>
-      </x:c>
-      <x:c r="G22" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="H22" s="85" t="str">
-        <x:v>loc-0383</x:v>
-      </x:c>
-      <x:c r="I22" s="85" t="str">
-        <x:v>New Dorp Station</x:v>
-      </x:c>
-      <x:c r="J22" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="K22" s="85" t="str">
-        <x:v>loc-0288</x:v>
-      </x:c>
-      <x:c r="L22" s="85" t="str">
-        <x:v>Freshkills Park</x:v>
-      </x:c>
-      <x:c r="M22" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="N22" s="85" t="str">
-        <x:v>loc-0133</x:v>
-      </x:c>
-      <x:c r="O22" s="85" t="str">
-        <x:v>Friends Meetinghouse and School</x:v>
-      </x:c>
-      <x:c r="P22" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q22" s="85" t="str">
+      <x:c r="B22" s="124" t="str">
+        <x:v>loc-0397</x:v>
+      </x:c>
+      <x:c r="C22" s="124" t="str">
+        <x:v>Jackson Heights-Roosevelt Avenue Station</x:v>
+      </x:c>
+      <x:c r="D22" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="E22" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F22" s="124" t="str">
+        <x:v>loc-0478</x:v>
+      </x:c>
+      <x:c r="G22" s="124" t="str">
+        <x:v>Yankee Stadium</x:v>
+      </x:c>
+      <x:c r="H22" s="124" t="str">
+        <x:v>Bronx</x:v>
+      </x:c>
+      <x:c r="I22" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J22" s="124" t="str">
+        <x:v>loc-0477</x:v>
+      </x:c>
+      <x:c r="K22" s="124" t="str">
+        <x:v>Citi Field</x:v>
+      </x:c>
+      <x:c r="L22" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="M22" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N22" s="124" t="str">
+        <x:v>loc-0114</x:v>
+      </x:c>
+      <x:c r="O22" s="124" t="str">
+        <x:v>Mary McLeod Bethune Gardens</x:v>
+      </x:c>
+      <x:c r="P22" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q22" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R22" s="124" t="str">
+        <x:v>loc-0295</x:v>
+      </x:c>
+      <x:c r="S22" s="124" t="str">
+        <x:v>Jamaica Bay Park</x:v>
+      </x:c>
+      <x:c r="T22" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="U22" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V22" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R22" s="85" t="str"/>
+      <x:c r="W22" s="124" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="86" t="n">
         <x:v>46267</x:v>
       </x:c>
       <x:c r="B23" s="87" t="str">
-        <x:v>loc-0261</x:v>
+        <x:v>loc-0091</x:v>
       </x:c>
       <x:c r="C23" s="87" t="str">
-        <x:v>Tompkins Square Park</x:v>
+        <x:v>Hamilton Grange National Memorial</x:v>
       </x:c>
       <x:c r="D23" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E23" s="87" t="str">
-        <x:v>loc-0395</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F23" s="87" t="str">
-        <x:v>Coney Island-Stillwell Avenue Station</x:v>
+        <x:v>loc-0490</x:v>
       </x:c>
       <x:c r="G23" s="87" t="str">
+        <x:v>New York Aquarium</x:v>
+      </x:c>
+      <x:c r="H23" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="H23" s="87" t="str">
-        <x:v>loc-0277</x:v>
-      </x:c>
       <x:c r="I23" s="87" t="str">
-        <x:v>Brookville Park</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J23" s="87" t="str">
-        <x:v>Queens</x:v>
+        <x:v>loc-0391</x:v>
       </x:c>
       <x:c r="K23" s="87" t="str">
-        <x:v>loc-0432</x:v>
+        <x:v>34 Street-Herald Square Station</x:v>
       </x:c>
       <x:c r="L23" s="87" t="str">
-        <x:v>Montefiore Plaza</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="M23" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N23" s="87" t="str">
-        <x:v>loc-0228</x:v>
+        <x:v>loc-0361</x:v>
       </x:c>
       <x:c r="O23" s="87" t="str">
-        <x:v>The Song of Achievement</x:v>
+        <x:v>Mount Vernon Hotel Museum</x:v>
       </x:c>
       <x:c r="P23" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q23" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R23" s="87" t="str">
+        <x:v>loc-0123</x:v>
+      </x:c>
+      <x:c r="S23" s="87" t="str">
+        <x:v>Bronx County Courthouse</x:v>
+      </x:c>
+      <x:c r="T23" s="87" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
-      <x:c r="Q23" s="87" t="str">
+      <x:c r="U23" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V23" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R23" s="87" t="str"/>
+      <x:c r="W23" s="87" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="84" t="n">
+      <x:c r="A24" s="123" t="n">
         <x:v>46268</x:v>
       </x:c>
-      <x:c r="B24" s="85" t="str">
-        <x:v>loc-0018</x:v>
-      </x:c>
-      <x:c r="C24" s="85" t="str">
-        <x:v>Empire State Building</x:v>
-      </x:c>
-      <x:c r="D24" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E24" s="85" t="str">
-        <x:v>loc-0483</x:v>
-      </x:c>
-      <x:c r="F24" s="85" t="str">
-        <x:v>Empire Outlets</x:v>
-      </x:c>
-      <x:c r="G24" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="H24" s="85" t="str">
-        <x:v>loc-0370</x:v>
-      </x:c>
-      <x:c r="I24" s="85" t="str">
-        <x:v>Children's Museum of the Arts</x:v>
-      </x:c>
-      <x:c r="J24" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K24" s="85" t="str">
-        <x:v>loc-0346</x:v>
-      </x:c>
-      <x:c r="L24" s="85" t="str">
-        <x:v>Ukrainian Museum</x:v>
-      </x:c>
-      <x:c r="M24" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N24" s="85" t="str">
-        <x:v>loc-0212</x:v>
-      </x:c>
-      <x:c r="O24" s="85" t="str">
-        <x:v>Dover Patrol Monument</x:v>
-      </x:c>
-      <x:c r="P24" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q24" s="85" t="str">
+      <x:c r="B24" s="124" t="str">
+        <x:v>loc-0447</x:v>
+      </x:c>
+      <x:c r="C24" s="124" t="str">
+        <x:v>Film Forum</x:v>
+      </x:c>
+      <x:c r="D24" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E24" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F24" s="124" t="str">
+        <x:v>loc-0458</x:v>
+      </x:c>
+      <x:c r="G24" s="124" t="str">
+        <x:v>Gramercy Tavern</x:v>
+      </x:c>
+      <x:c r="H24" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I24" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J24" s="124" t="str">
+        <x:v>loc-0334</x:v>
+      </x:c>
+      <x:c r="K24" s="124" t="str">
+        <x:v>Beacon Theatre</x:v>
+      </x:c>
+      <x:c r="L24" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M24" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N24" s="124" t="str">
+        <x:v>loc-0474</x:v>
+      </x:c>
+      <x:c r="O24" s="124" t="str">
+        <x:v>John's of Bleecker Street</x:v>
+      </x:c>
+      <x:c r="P24" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q24" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R24" s="124" t="str">
+        <x:v>loc-0388</x:v>
+      </x:c>
+      <x:c r="S24" s="124" t="str">
+        <x:v>Woodlawn Station</x:v>
+      </x:c>
+      <x:c r="T24" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="U24" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V24" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R24" s="85" t="str"/>
+      <x:c r="W24" s="124" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="86" t="n">
         <x:v>46269</x:v>
       </x:c>
       <x:c r="B25" s="87" t="str">
-        <x:v>loc-0060</x:v>
+        <x:v>loc-0108</x:v>
       </x:c>
       <x:c r="C25" s="87" t="str">
-        <x:v>Voorlezer's House</x:v>
+        <x:v>DeLamar Mansion</x:v>
       </x:c>
       <x:c r="D25" s="87" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E25" s="87" t="str">
-        <x:v>loc-0011</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F25" s="87" t="str">
-        <x:v>New York Public Library and Bryant Park</x:v>
+        <x:v>loc-0116</x:v>
       </x:c>
       <x:c r="G25" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Park Row Building</x:v>
       </x:c>
       <x:c r="H25" s="87" t="str">
-        <x:v>loc-0403</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I25" s="87" t="str">
-        <x:v>96 Street Station</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J25" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>loc-0037</x:v>
       </x:c>
       <x:c r="K25" s="87" t="str">
-        <x:v>loc-0283</x:v>
+        <x:v>Ocean Parkway</x:v>
       </x:c>
       <x:c r="L25" s="87" t="str">
-        <x:v>Ferry Point Park</x:v>
+        <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="M25" s="87" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N25" s="87" t="str">
-        <x:v>loc-0179</x:v>
+        <x:v>loc-0253</x:v>
       </x:c>
       <x:c r="O25" s="87" t="str">
-        <x:v>John N. LaCorte</x:v>
+        <x:v>Marine Park</x:v>
       </x:c>
       <x:c r="P25" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="Q25" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R25" s="87" t="str">
+        <x:v>loc-0172</x:v>
+      </x:c>
+      <x:c r="S25" s="87" t="str">
+        <x:v>Doric Columns</x:v>
+      </x:c>
+      <x:c r="T25" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="U25" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V25" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R25" s="87" t="str"/>
+      <x:c r="W25" s="87" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="84" t="n">
+      <x:c r="A26" s="123" t="n">
         <x:v>46270</x:v>
       </x:c>
-      <x:c r="B26" s="85" t="str">
-        <x:v>loc-0458</x:v>
-      </x:c>
-      <x:c r="C26" s="85" t="str">
-        <x:v>Gramercy Tavern</x:v>
-      </x:c>
-      <x:c r="D26" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E26" s="85" t="str">
-        <x:v>loc-0091</x:v>
-      </x:c>
-      <x:c r="F26" s="85" t="str">
-        <x:v>Hamilton Grange National Memorial</x:v>
-      </x:c>
-      <x:c r="G26" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H26" s="85" t="str">
-        <x:v>loc-0420</x:v>
-      </x:c>
-      <x:c r="I26" s="85" t="str">
-        <x:v>Lou Gehrig Plaza</x:v>
-      </x:c>
-      <x:c r="J26" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="K26" s="85" t="str">
-        <x:v>loc-0126</x:v>
-      </x:c>
-      <x:c r="L26" s="85" t="str">
-        <x:v>Duke, James B., Mansion</x:v>
-      </x:c>
-      <x:c r="M26" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N26" s="85" t="str">
-        <x:v>loc-0239</x:v>
-      </x:c>
-      <x:c r="O26" s="85" t="str">
-        <x:v>Macombs Dam Park Fountain</x:v>
-      </x:c>
-      <x:c r="P26" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q26" s="85" t="str">
+      <x:c r="B26" s="124" t="str">
+        <x:v>loc-0315</x:v>
+      </x:c>
+      <x:c r="C26" s="124" t="str">
+        <x:v>Brooklyn Botanic Garden</x:v>
+      </x:c>
+      <x:c r="D26" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="E26" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F26" s="124" t="str">
+        <x:v>loc-0407</x:v>
+      </x:c>
+      <x:c r="G26" s="124" t="str">
+        <x:v>Grand Central-42 Street Station</x:v>
+      </x:c>
+      <x:c r="H26" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I26" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J26" s="124" t="str">
+        <x:v>loc-0016</x:v>
+      </x:c>
+      <x:c r="K26" s="124" t="str">
+        <x:v>Radio City Music Hall</x:v>
+      </x:c>
+      <x:c r="L26" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M26" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N26" s="124" t="str">
+        <x:v>loc-0313</x:v>
+      </x:c>
+      <x:c r="O26" s="124" t="str">
+        <x:v>Wards Island Park</x:v>
+      </x:c>
+      <x:c r="P26" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q26" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R26" s="124" t="str">
+        <x:v>loc-0102</x:v>
+      </x:c>
+      <x:c r="S26" s="124" t="str">
+        <x:v>Jeffrey's Hook Lighthouse</x:v>
+      </x:c>
+      <x:c r="T26" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U26" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V26" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R26" s="85" t="str"/>
+      <x:c r="W26" s="124" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="86" t="n">
         <x:v>46271</x:v>
       </x:c>
       <x:c r="B27" s="87" t="str">
-        <x:v>loc-0270</x:v>
+        <x:v>loc-0412</x:v>
       </x:c>
       <x:c r="C27" s="87" t="str">
-        <x:v>Van Cortlandt Park</x:v>
+        <x:v>Fordham Plaza</x:v>
       </x:c>
       <x:c r="D27" s="87" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="E27" s="87" t="str">
-        <x:v>loc-0486</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F27" s="87" t="str">
-        <x:v>Jane's Carousel</x:v>
+        <x:v>loc-0408</x:v>
       </x:c>
       <x:c r="G27" s="87" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>Jamaica Center-Parsons/Archer Station</x:v>
       </x:c>
       <x:c r="H27" s="87" t="str">
-        <x:v>loc-0080</x:v>
+        <x:v>Queens</x:v>
       </x:c>
       <x:c r="I27" s="87" t="str">
-        <x:v>RKO Keith's Theater</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J27" s="87" t="str">
+        <x:v>loc-0446</x:v>
+      </x:c>
+      <x:c r="K27" s="87" t="str">
+        <x:v>Dirt Candy</x:v>
+      </x:c>
+      <x:c r="L27" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M27" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N27" s="87" t="str">
+        <x:v>loc-0289</x:v>
+      </x:c>
+      <x:c r="O27" s="87" t="str">
+        <x:v>Great Kills Park</x:v>
+      </x:c>
+      <x:c r="P27" s="87" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="Q27" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R27" s="87" t="str">
+        <x:v>loc-0293</x:v>
+      </x:c>
+      <x:c r="S27" s="87" t="str">
+        <x:v>Hook Creek Park</x:v>
+      </x:c>
+      <x:c r="T27" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="K27" s="87" t="str">
-        <x:v>loc-0425</x:v>
-      </x:c>
-      <x:c r="L27" s="87" t="str">
-        <x:v>Bogardus Plaza</x:v>
-      </x:c>
-      <x:c r="M27" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N27" s="87" t="str">
-        <x:v>loc-0202</x:v>
-      </x:c>
-      <x:c r="O27" s="87" t="str">
-        <x:v>Happy Land Memorial</x:v>
-      </x:c>
-      <x:c r="P27" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q27" s="87" t="str">
+      <x:c r="U27" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V27" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R27" s="87" t="str"/>
+      <x:c r="W27" s="87" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="84" t="n">
+      <x:c r="A28" s="123" t="n">
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="B28" s="85" t="str">
-        <x:v>loc-0442</x:v>
-      </x:c>
-      <x:c r="C28" s="85" t="str">
-        <x:v>Westfield World Trade Center</x:v>
-      </x:c>
-      <x:c r="D28" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E28" s="85" t="str">
-        <x:v>loc-0037</x:v>
-      </x:c>
-      <x:c r="F28" s="85" t="str">
-        <x:v>Ocean Parkway</x:v>
-      </x:c>
-      <x:c r="G28" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H28" s="85" t="str">
-        <x:v>loc-0296</x:v>
-      </x:c>
-      <x:c r="I28" s="85" t="str">
-        <x:v>Juniper Valley Park</x:v>
-      </x:c>
-      <x:c r="J28" s="85" t="str">
+      <x:c r="B28" s="124" t="str">
+        <x:v>loc-0100</x:v>
+      </x:c>
+      <x:c r="C28" s="124" t="str">
+        <x:v>Morgan Library</x:v>
+      </x:c>
+      <x:c r="D28" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E28" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F28" s="124" t="str">
+        <x:v>loc-0056</x:v>
+      </x:c>
+      <x:c r="G28" s="124" t="str">
+        <x:v>Battery Weed</x:v>
+      </x:c>
+      <x:c r="H28" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="I28" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J28" s="124" t="str">
+        <x:v>loc-0399</x:v>
+      </x:c>
+      <x:c r="K28" s="124" t="str">
+        <x:v>34 Street-Penn Station Station</x:v>
+      </x:c>
+      <x:c r="L28" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M28" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N28" s="124" t="str">
+        <x:v>loc-0132</x:v>
+      </x:c>
+      <x:c r="O28" s="124" t="str">
+        <x:v>Fort Totten Officers' Club</x:v>
+      </x:c>
+      <x:c r="P28" s="124" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="K28" s="85" t="str">
-        <x:v>loc-0128</x:v>
-      </x:c>
-      <x:c r="L28" s="85" t="str">
-        <x:v>Eighth Regiment Armory (Kingsbridge Armory)</x:v>
-      </x:c>
-      <x:c r="M28" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="N28" s="85" t="str">
-        <x:v>loc-0135</x:v>
-      </x:c>
-      <x:c r="O28" s="85" t="str">
-        <x:v>Lent Homestead and Cemetery</x:v>
-      </x:c>
-      <x:c r="P28" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q28" s="85" t="str">
+      <x:c r="Q28" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R28" s="124" t="str">
+        <x:v>loc-0126</x:v>
+      </x:c>
+      <x:c r="S28" s="124" t="str">
+        <x:v>Duke, James B., Mansion</x:v>
+      </x:c>
+      <x:c r="T28" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U28" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V28" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R28" s="85" t="str"/>
+      <x:c r="W28" s="124" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="86" t="n">
         <x:v>46273</x:v>
       </x:c>
       <x:c r="B29" s="87" t="str">
-        <x:v>loc-0485</x:v>
+        <x:v>loc-0465</x:v>
       </x:c>
       <x:c r="C29" s="87" t="str">
-        <x:v>Starlight Park</x:v>
+        <x:v>Russ &amp; Daughters</x:v>
       </x:c>
       <x:c r="D29" s="87" t="str">
-        <x:v>Bronx</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E29" s="87" t="str">
-        <x:v>loc-0053</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F29" s="87" t="str">
-        <x:v>King Manor</x:v>
+        <x:v>loc-0487</x:v>
       </x:c>
       <x:c r="G29" s="87" t="str">
+        <x:v>Pepsi-Cola sign</x:v>
+      </x:c>
+      <x:c r="H29" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="H29" s="87" t="str">
-        <x:v>loc-0298</x:v>
-      </x:c>
       <x:c r="I29" s="87" t="str">
-        <x:v>Kissena Park</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J29" s="87" t="str">
+        <x:v>loc-0324</x:v>
+      </x:c>
+      <x:c r="K29" s="87" t="str">
+        <x:v>El Museo del Barrio</x:v>
+      </x:c>
+      <x:c r="L29" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M29" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N29" s="87" t="str">
+        <x:v>loc-0339</x:v>
+      </x:c>
+      <x:c r="O29" s="87" t="str">
+        <x:v>USS Growler</x:v>
+      </x:c>
+      <x:c r="P29" s="87" t="str">
+        <x:v>New York City</x:v>
+      </x:c>
+      <x:c r="Q29" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R29" s="87" t="str">
+        <x:v>loc-0204</x:v>
+      </x:c>
+      <x:c r="S29" s="87" t="str">
+        <x:v>Tetherball Monument</x:v>
+      </x:c>
+      <x:c r="T29" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="K29" s="87" t="str">
-        <x:v>loc-0103</x:v>
-      </x:c>
-      <x:c r="L29" s="87" t="str">
-        <x:v>Bouwerie Lane Theater</x:v>
-      </x:c>
-      <x:c r="M29" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N29" s="87" t="str">
-        <x:v>loc-0231</x:v>
-      </x:c>
-      <x:c r="O29" s="87" t="str">
-        <x:v>Fountain of the Dolphins</x:v>
-      </x:c>
-      <x:c r="P29" s="87" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="Q29" s="87" t="str">
+      <x:c r="U29" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V29" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R29" s="87" t="str"/>
+      <x:c r="W29" s="87" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="84" t="n">
+      <x:c r="A30" s="123" t="n">
         <x:v>46274</x:v>
       </x:c>
-      <x:c r="B30" s="85" t="str">
-        <x:v>loc-0252</x:v>
-      </x:c>
-      <x:c r="C30" s="85" t="str">
-        <x:v>Inwood Hill Park</x:v>
-      </x:c>
-      <x:c r="D30" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E30" s="85" t="str">
-        <x:v>loc-0325</x:v>
-      </x:c>
-      <x:c r="F30" s="85" t="str">
-        <x:v>Museum of Modern Art</x:v>
-      </x:c>
-      <x:c r="G30" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H30" s="85" t="str">
-        <x:v>loc-0426</x:v>
-      </x:c>
-      <x:c r="I30" s="85" t="str">
-        <x:v>Willoughby Plaza</x:v>
-      </x:c>
-      <x:c r="J30" s="85" t="str">
+      <x:c r="B30" s="124" t="str">
+        <x:v>loc-0451</x:v>
+      </x:c>
+      <x:c r="C30" s="124" t="str">
+        <x:v>Plaza Hotel</x:v>
+      </x:c>
+      <x:c r="D30" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E30" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F30" s="124" t="str">
+        <x:v>loc-0411</x:v>
+      </x:c>
+      <x:c r="G30" s="124" t="str">
+        <x:v>Times Square Plaza</x:v>
+      </x:c>
+      <x:c r="H30" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I30" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J30" s="124" t="str">
+        <x:v>loc-0417</x:v>
+      </x:c>
+      <x:c r="K30" s="124" t="str">
+        <x:v>Corona Plaza</x:v>
+      </x:c>
+      <x:c r="L30" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="M30" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N30" s="124" t="str">
+        <x:v>loc-0068</x:v>
+      </x:c>
+      <x:c r="O30" s="124" t="str">
+        <x:v>Litchfield Villa</x:v>
+      </x:c>
+      <x:c r="P30" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="K30" s="85" t="str">
-        <x:v>loc-0102</x:v>
-      </x:c>
-      <x:c r="L30" s="85" t="str">
-        <x:v>Jeffrey's Hook Lighthouse</x:v>
-      </x:c>
-      <x:c r="M30" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N30" s="85" t="str">
-        <x:v>loc-0192</x:v>
-      </x:c>
-      <x:c r="O30" s="85" t="str">
-        <x:v>Van Nest Memorial</x:v>
-      </x:c>
-      <x:c r="P30" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q30" s="85" t="str">
+      <x:c r="Q30" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R30" s="124" t="str">
+        <x:v>loc-0394</x:v>
+      </x:c>
+      <x:c r="S30" s="124" t="str">
+        <x:v>Broadway-Lafayette Street Station</x:v>
+      </x:c>
+      <x:c r="T30" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U30" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V30" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R30" s="85" t="str"/>
+      <x:c r="W30" s="124" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="86" t="n">
         <x:v>46275</x:v>
       </x:c>
       <x:c r="B31" s="87" t="str">
-        <x:v>loc-0001</x:v>
+        <x:v>loc-0255</x:v>
       </x:c>
       <x:c r="C31" s="87" t="str">
-        <x:v>Brooklyn Bridge</x:v>
+        <x:v>Rockaway Beach</x:v>
       </x:c>
       <x:c r="D31" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="E31" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F31" s="87" t="str">
+        <x:v>loc-0015</x:v>
+      </x:c>
+      <x:c r="G31" s="87" t="str">
+        <x:v>Guggenheim Museum</x:v>
+      </x:c>
+      <x:c r="H31" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I31" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J31" s="87" t="str">
+        <x:v>loc-0066</x:v>
+      </x:c>
+      <x:c r="K31" s="87" t="str">
+        <x:v>Garibaldi Memorial</x:v>
+      </x:c>
+      <x:c r="L31" s="87" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="M31" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N31" s="87" t="str">
+        <x:v>loc-0105</x:v>
+      </x:c>
+      <x:c r="O31" s="87" t="str">
+        <x:v>Broad Exchange Building</x:v>
+      </x:c>
+      <x:c r="P31" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q31" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R31" s="87" t="str">
+        <x:v>loc-0196</x:v>
+      </x:c>
+      <x:c r="S31" s="87" t="str">
+        <x:v>Spirit of Progress</x:v>
+      </x:c>
+      <x:c r="T31" s="87" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="U31" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V31" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W31" s="87" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="123" t="n">
+        <x:v>46276</x:v>
+      </x:c>
+      <x:c r="B32" s="124" t="str">
+        <x:v>loc-0489</x:v>
+      </x:c>
+      <x:c r="C32" s="124" t="str">
+        <x:v>Atlantic Terminal</x:v>
+      </x:c>
+      <x:c r="D32" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="E31" s="87" t="str">
-        <x:v>loc-0008</x:v>
-      </x:c>
-      <x:c r="F31" s="87" t="str">
-        <x:v>New York Botanical Garden</x:v>
-      </x:c>
-      <x:c r="G31" s="87" t="str">
+      <x:c r="E32" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F32" s="124" t="str">
+        <x:v>loc-0438</x:v>
+      </x:c>
+      <x:c r="G32" s="124" t="str">
+        <x:v>Wonder Wheel</x:v>
+      </x:c>
+      <x:c r="H32" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="I32" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J32" s="124" t="str">
+        <x:v>loc-0025</x:v>
+      </x:c>
+      <x:c r="K32" s="124" t="str">
+        <x:v>South Street Seaport</x:v>
+      </x:c>
+      <x:c r="L32" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M32" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N32" s="124" t="str">
+        <x:v>loc-0409</x:v>
+      </x:c>
+      <x:c r="O32" s="124" t="str">
+        <x:v>Marcy Avenue Station</x:v>
+      </x:c>
+      <x:c r="P32" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="Q32" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R32" s="124" t="str">
+        <x:v>loc-0309</x:v>
+      </x:c>
+      <x:c r="S32" s="124" t="str">
+        <x:v>Riverdale Park</x:v>
+      </x:c>
+      <x:c r="T32" s="124" t="str">
         <x:v>The Bronx</x:v>
       </x:c>
-      <x:c r="H31" s="87" t="str">
-        <x:v>loc-0115</x:v>
-      </x:c>
-      <x:c r="I31" s="87" t="str">
-        <x:v>Park and Tilford Building</x:v>
-      </x:c>
-      <x:c r="J31" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K31" s="87" t="str">
-        <x:v>loc-0063</x:v>
-      </x:c>
-      <x:c r="L31" s="87" t="str">
-        <x:v>Crotona Play Center</x:v>
-      </x:c>
-      <x:c r="M31" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="N31" s="87" t="str">
-        <x:v>loc-0230</x:v>
-      </x:c>
-      <x:c r="O31" s="87" t="str">
-        <x:v>Algernon Sidney Sullivan</x:v>
-      </x:c>
-      <x:c r="P31" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q31" s="87" t="str">
+      <x:c r="U32" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V32" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R31" s="87" t="str"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="84" t="n">
-        <x:v>46276</x:v>
-      </x:c>
-      <x:c r="B32" s="85" t="str">
-        <x:v>loc-0024</x:v>
-      </x:c>
-      <x:c r="C32" s="85" t="str">
-        <x:v>Stonewall Inn</x:v>
-      </x:c>
-      <x:c r="D32" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E32" s="85" t="str">
-        <x:v>loc-0472</x:v>
-      </x:c>
-      <x:c r="F32" s="85" t="str">
-        <x:v>Peter Luger Steak House</x:v>
-      </x:c>
-      <x:c r="G32" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H32" s="85" t="str">
-        <x:v>loc-0309</x:v>
-      </x:c>
-      <x:c r="I32" s="85" t="str">
-        <x:v>Riverdale Park</x:v>
-      </x:c>
-      <x:c r="J32" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="K32" s="85" t="str">
-        <x:v>loc-0371</x:v>
-      </x:c>
-      <x:c r="L32" s="85" t="str">
-        <x:v>Children's Museum of Manhattan</x:v>
-      </x:c>
-      <x:c r="M32" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N32" s="85" t="str">
-        <x:v>loc-0199</x:v>
-      </x:c>
-      <x:c r="O32" s="85" t="str">
-        <x:v>Unionport Memorial</x:v>
-      </x:c>
-      <x:c r="P32" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q32" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R32" s="85" t="str"/>
+      <x:c r="W32" s="124" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="86" t="n">
         <x:v>46277</x:v>
       </x:c>
       <x:c r="B33" s="87" t="str">
-        <x:v>loc-0437</x:v>
+        <x:v>loc-0495</x:v>
       </x:c>
       <x:c r="C33" s="87" t="str">
-        <x:v>Luna Park</x:v>
+        <x:v>Flushing Meadows Carousel</x:v>
       </x:c>
       <x:c r="D33" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="E33" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F33" s="87" t="str">
+        <x:v>loc-0460</x:v>
+      </x:c>
+      <x:c r="G33" s="87" t="str">
+        <x:v>Waldorf–Astoria</x:v>
+      </x:c>
+      <x:c r="H33" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I33" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J33" s="87" t="str">
+        <x:v>loc-0146</x:v>
+      </x:c>
+      <x:c r="K33" s="87" t="str">
+        <x:v>Unisphere and Fountain</x:v>
+      </x:c>
+      <x:c r="L33" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="M33" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N33" s="87" t="str">
+        <x:v>loc-0415</x:v>
+      </x:c>
+      <x:c r="O33" s="87" t="str">
+        <x:v>Pearl Street Plaza</x:v>
+      </x:c>
+      <x:c r="P33" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="E33" s="87" t="str">
-        <x:v>loc-0488</x:v>
-      </x:c>
-      <x:c r="F33" s="87" t="str">
-        <x:v>East River Plaza</x:v>
-      </x:c>
-      <x:c r="G33" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H33" s="87" t="str">
-        <x:v>loc-0118</x:v>
-      </x:c>
-      <x:c r="I33" s="87" t="str">
-        <x:v>Strecker Memorial Laboratory</x:v>
-      </x:c>
-      <x:c r="J33" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K33" s="87" t="str">
-        <x:v>loc-0342</x:v>
-      </x:c>
-      <x:c r="L33" s="87" t="str">
-        <x:v>Jewish Museum</x:v>
-      </x:c>
-      <x:c r="M33" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N33" s="87" t="str">
-        <x:v>loc-0195</x:v>
-      </x:c>
-      <x:c r="O33" s="87" t="str">
-        <x:v>Ridgewood Memorial</x:v>
-      </x:c>
-      <x:c r="P33" s="87" t="str">
+      <x:c r="Q33" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R33" s="87" t="str">
+        <x:v>loc-0242</x:v>
+      </x:c>
+      <x:c r="S33" s="87" t="str">
+        <x:v>College Point War Memorial</x:v>
+      </x:c>
+      <x:c r="T33" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="Q33" s="87" t="str">
+      <x:c r="U33" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V33" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R33" s="87" t="str"/>
+      <x:c r="W33" s="87" t="str"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="84" t="n">
+      <x:c r="A34" s="123" t="n">
         <x:v>46278</x:v>
       </x:c>
-      <x:c r="B34" s="85" t="str">
-        <x:v>loc-0003</x:v>
-      </x:c>
-      <x:c r="C34" s="85" t="str">
-        <x:v>Brooklyn Museum</x:v>
-      </x:c>
-      <x:c r="D34" s="85" t="str">
+      <x:c r="B34" s="124" t="str">
+        <x:v>loc-0046</x:v>
+      </x:c>
+      <x:c r="C34" s="124" t="str">
+        <x:v>Green-Wood Cemetery</x:v>
+      </x:c>
+      <x:c r="D34" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="E34" s="85" t="str">
-        <x:v>loc-0480</x:v>
-      </x:c>
-      <x:c r="F34" s="85" t="str">
-        <x:v>Etihad Park</x:v>
-      </x:c>
-      <x:c r="G34" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H34" s="85" t="str">
-        <x:v>loc-0347</x:v>
-      </x:c>
-      <x:c r="I34" s="85" t="str">
-        <x:v>Museum of the Dog</x:v>
-      </x:c>
-      <x:c r="J34" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K34" s="85" t="str">
-        <x:v>loc-0292</x:v>
-      </x:c>
-      <x:c r="L34" s="85" t="str">
-        <x:v>Highland Park</x:v>
-      </x:c>
-      <x:c r="M34" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N34" s="85" t="str">
-        <x:v>loc-0423</x:v>
-      </x:c>
-      <x:c r="O34" s="85" t="str">
-        <x:v>Plaza de Las Americas</x:v>
-      </x:c>
-      <x:c r="P34" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q34" s="85" t="str">
+      <x:c r="E34" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F34" s="124" t="str">
+        <x:v>loc-0422</x:v>
+      </x:c>
+      <x:c r="G34" s="124" t="str">
+        <x:v>Roberto Clemente Plaza</x:v>
+      </x:c>
+      <x:c r="H34" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="I34" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J34" s="124" t="str">
+        <x:v>loc-0466</x:v>
+      </x:c>
+      <x:c r="K34" s="124" t="str">
+        <x:v>Lipstick Building</x:v>
+      </x:c>
+      <x:c r="L34" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M34" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N34" s="124" t="str">
+        <x:v>loc-0492</x:v>
+      </x:c>
+      <x:c r="O34" s="124" t="str">
+        <x:v>Staten Island Mall</x:v>
+      </x:c>
+      <x:c r="P34" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="Q34" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R34" s="124" t="str">
+        <x:v>loc-0047</x:v>
+      </x:c>
+      <x:c r="S34" s="124" t="str">
+        <x:v>Bartow-Pell Mansion and Carriage House</x:v>
+      </x:c>
+      <x:c r="T34" s="124" t="str">
+        <x:v>The Bronx</x:v>
+      </x:c>
+      <x:c r="U34" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V34" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R34" s="85" t="str"/>
+      <x:c r="W34" s="124" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="86" t="n">
         <x:v>46279</x:v>
       </x:c>
       <x:c r="B35" s="87" t="str">
-        <x:v>loc-0255</x:v>
+        <x:v>loc-0007</x:v>
       </x:c>
       <x:c r="C35" s="87" t="str">
-        <x:v>Rockaway Beach</x:v>
+        <x:v>Central Park</x:v>
       </x:c>
       <x:c r="D35" s="87" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E35" s="87" t="str">
-        <x:v>loc-0088</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F35" s="87" t="str">
-        <x:v>Biltmore Theater</x:v>
+        <x:v>loc-0264</x:v>
       </x:c>
       <x:c r="G35" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Union Square Park</x:v>
       </x:c>
       <x:c r="H35" s="87" t="str">
-        <x:v>loc-0401</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I35" s="87" t="str">
-        <x:v>72 Street Station</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J35" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>loc-0482</x:v>
       </x:c>
       <x:c r="K35" s="87" t="str">
-        <x:v>loc-0095</x:v>
+        <x:v>La Marqueta</x:v>
       </x:c>
       <x:c r="L35" s="87" t="str">
-        <x:v>Riverside Park and Drive</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="M35" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N35" s="87" t="str">
-        <x:v>loc-0418</x:v>
+        <x:v>loc-0098</x:v>
       </x:c>
       <x:c r="O35" s="87" t="str">
-        <x:v>Cooper Square Plaza</x:v>
+        <x:v>Ed Sullivan Theater</x:v>
       </x:c>
       <x:c r="P35" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="Q35" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R35" s="87" t="str">
+        <x:v>loc-0145</x:v>
+      </x:c>
+      <x:c r="S35" s="87" t="str">
+        <x:v>Pupin Physics Laboratories, Columbia University</x:v>
+      </x:c>
+      <x:c r="T35" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U35" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V35" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R35" s="87" t="str"/>
+      <x:c r="W35" s="87" t="str"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="84" t="n">
+      <x:c r="A36" s="123" t="n">
         <x:v>46280</x:v>
       </x:c>
-      <x:c r="B36" s="85" t="str">
-        <x:v>loc-0025</x:v>
-      </x:c>
-      <x:c r="C36" s="85" t="str">
-        <x:v>South Street Seaport</x:v>
-      </x:c>
-      <x:c r="D36" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E36" s="85" t="str">
-        <x:v>loc-0032</x:v>
-      </x:c>
-      <x:c r="F36" s="85" t="str">
-        <x:v>Statue of Liberty and Ellis Island</x:v>
-      </x:c>
-      <x:c r="G36" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H36" s="85" t="str">
-        <x:v>loc-0137</x:v>
-      </x:c>
-      <x:c r="I36" s="85" t="str">
-        <x:v>Low Memorial Library, Columbia University</x:v>
-      </x:c>
-      <x:c r="J36" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K36" s="85" t="str">
-        <x:v>loc-0305</x:v>
-      </x:c>
-      <x:c r="L36" s="85" t="str">
-        <x:v>Powell's Cove Park</x:v>
-      </x:c>
-      <x:c r="M36" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N36" s="85" t="str">
-        <x:v>loc-0152</x:v>
-      </x:c>
-      <x:c r="O36" s="85" t="str">
-        <x:v>Bethesda Fountain</x:v>
-      </x:c>
-      <x:c r="P36" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q36" s="85" t="str">
+      <x:c r="B36" s="124" t="str">
+        <x:v>loc-0252</x:v>
+      </x:c>
+      <x:c r="C36" s="124" t="str">
+        <x:v>Inwood Hill Park</x:v>
+      </x:c>
+      <x:c r="D36" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E36" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F36" s="124" t="str">
+        <x:v>loc-0058</x:v>
+      </x:c>
+      <x:c r="G36" s="124" t="str">
+        <x:v>Conference House</x:v>
+      </x:c>
+      <x:c r="H36" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="I36" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J36" s="124" t="str">
+        <x:v>loc-0003</x:v>
+      </x:c>
+      <x:c r="K36" s="124" t="str">
+        <x:v>Brooklyn Museum</x:v>
+      </x:c>
+      <x:c r="L36" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="M36" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N36" s="124" t="str">
+        <x:v>loc-0082</x:v>
+      </x:c>
+      <x:c r="O36" s="124" t="str">
+        <x:v>U.S. Army Military Ocean Terminal</x:v>
+      </x:c>
+      <x:c r="P36" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="Q36" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R36" s="124" t="str">
+        <x:v>loc-0369</x:v>
+      </x:c>
+      <x:c r="S36" s="124" t="str">
+        <x:v>Museum of Chinese in America</x:v>
+      </x:c>
+      <x:c r="T36" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U36" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V36" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R36" s="85" t="str"/>
+      <x:c r="W36" s="124" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="86" t="n">
         <x:v>46281</x:v>
       </x:c>
       <x:c r="B37" s="87" t="str">
+        <x:v>loc-0092</x:v>
+      </x:c>
+      <x:c r="C37" s="87" t="str">
+        <x:v>Morris–Jumel Mansion</x:v>
+      </x:c>
+      <x:c r="D37" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E37" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F37" s="87" t="str">
+        <x:v>loc-0026</x:v>
+      </x:c>
+      <x:c r="G37" s="87" t="str">
+        <x:v>Woolworth Building</x:v>
+      </x:c>
+      <x:c r="H37" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I37" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J37" s="87" t="str">
+        <x:v>loc-0328</x:v>
+      </x:c>
+      <x:c r="K37" s="87" t="str">
+        <x:v>Studio Museum in Harlem</x:v>
+      </x:c>
+      <x:c r="L37" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M37" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N37" s="87" t="str">
+        <x:v>loc-0363</x:v>
+      </x:c>
+      <x:c r="O37" s="87" t="str">
+        <x:v>Enid A. Haupt Glass Garden</x:v>
+      </x:c>
+      <x:c r="P37" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q37" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R37" s="87" t="str">
+        <x:v>loc-0065</x:v>
+      </x:c>
+      <x:c r="S37" s="87" t="str">
+        <x:v>Fort Tompkins Quadrangle</x:v>
+      </x:c>
+      <x:c r="T37" s="87" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="U37" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V37" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W37" s="87" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="123" t="n">
+        <x:v>46282</x:v>
+      </x:c>
+      <x:c r="B38" s="124" t="str">
         <x:v>loc-0009</x:v>
       </x:c>
-      <x:c r="C37" s="87" t="str">
+      <x:c r="C38" s="124" t="str">
         <x:v>American Museum of Natural History</x:v>
       </x:c>
-      <x:c r="D37" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E37" s="87" t="str">
-        <x:v>loc-0436</x:v>
-      </x:c>
-      <x:c r="F37" s="87" t="str">
-        <x:v>Bronx Zoo</x:v>
-      </x:c>
-      <x:c r="G37" s="87" t="str">
-        <x:v>Bronx</x:v>
-      </x:c>
-      <x:c r="H37" s="87" t="str">
-        <x:v>loc-0052</x:v>
-      </x:c>
-      <x:c r="I37" s="87" t="str">
-        <x:v>Edgar Allan Poe Cottage</x:v>
-      </x:c>
-      <x:c r="J37" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="K37" s="87" t="str">
-        <x:v>loc-0388</x:v>
-      </x:c>
-      <x:c r="L37" s="87" t="str">
-        <x:v>Woodlawn Station</x:v>
-      </x:c>
-      <x:c r="M37" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="N37" s="87" t="str">
-        <x:v>loc-0352</x:v>
-      </x:c>
-      <x:c r="O37" s="87" t="str">
-        <x:v>Wallach Art Gallery</x:v>
-      </x:c>
-      <x:c r="P37" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q37" s="87" t="str">
+      <x:c r="D38" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E38" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F38" s="124" t="str">
+        <x:v>loc-0005</x:v>
+      </x:c>
+      <x:c r="G38" s="124" t="str">
+        <x:v>Grand Central Terminal</x:v>
+      </x:c>
+      <x:c r="H38" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I38" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J38" s="124" t="str">
+        <x:v>loc-0017</x:v>
+      </x:c>
+      <x:c r="K38" s="124" t="str">
+        <x:v>Coney Island Cyclone</x:v>
+      </x:c>
+      <x:c r="L38" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="M38" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N38" s="124" t="str">
+        <x:v>loc-0401</x:v>
+      </x:c>
+      <x:c r="O38" s="124" t="str">
+        <x:v>72 Street Station</x:v>
+      </x:c>
+      <x:c r="P38" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q38" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R38" s="124" t="str">
+        <x:v>loc-0291</x:v>
+      </x:c>
+      <x:c r="S38" s="124" t="str">
+        <x:v>High Rock Park</x:v>
+      </x:c>
+      <x:c r="T38" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="U38" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V38" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R37" s="87" t="str"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="84" t="n">
-        <x:v>46282</x:v>
-      </x:c>
-      <x:c r="B38" s="85" t="str">
-        <x:v>loc-0031</x:v>
-      </x:c>
-      <x:c r="C38" s="85" t="str">
-        <x:v>St. Patrick's Cathedral</x:v>
-      </x:c>
-      <x:c r="D38" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E38" s="85" t="str">
-        <x:v>loc-0328</x:v>
-      </x:c>
-      <x:c r="F38" s="85" t="str">
-        <x:v>Studio Museum in Harlem</x:v>
-      </x:c>
-      <x:c r="G38" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H38" s="85" t="str">
-        <x:v>loc-0381</x:v>
-      </x:c>
-      <x:c r="I38" s="85" t="str">
-        <x:v>Fulton Street Station</x:v>
-      </x:c>
-      <x:c r="J38" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K38" s="85" t="str">
-        <x:v>loc-0294</x:v>
-      </x:c>
-      <x:c r="L38" s="85" t="str">
-        <x:v>Idlewild Park</x:v>
-      </x:c>
-      <x:c r="M38" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N38" s="85" t="str">
-        <x:v>loc-0200</x:v>
-      </x:c>
-      <x:c r="O38" s="85" t="str">
-        <x:v>Von Weber Memorial</x:v>
-      </x:c>
-      <x:c r="P38" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q38" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R38" s="85" t="str"/>
+      <x:c r="W38" s="124" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="86" t="n">
         <x:v>46283</x:v>
       </x:c>
       <x:c r="B39" s="87" t="str">
-        <x:v>loc-0017</x:v>
+        <x:v>loc-0461</x:v>
       </x:c>
       <x:c r="C39" s="87" t="str">
-        <x:v>Coney Island Cyclone</x:v>
+        <x:v>Citigroup Center</x:v>
       </x:c>
       <x:c r="D39" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E39" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F39" s="87" t="str">
+        <x:v>loc-0250</x:v>
+      </x:c>
+      <x:c r="G39" s="87" t="str">
+        <x:v>Fort Tryon Park</x:v>
+      </x:c>
+      <x:c r="H39" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I39" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J39" s="87" t="str">
+        <x:v>loc-0096</x:v>
+      </x:c>
+      <x:c r="K39" s="87" t="str">
+        <x:v>The Public Theater</x:v>
+      </x:c>
+      <x:c r="L39" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M39" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N39" s="87" t="str">
+        <x:v>loc-0376</x:v>
+      </x:c>
+      <x:c r="O39" s="87" t="str">
+        <x:v>Museum of Reclaimed Urban Space</x:v>
+      </x:c>
+      <x:c r="P39" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q39" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R39" s="87" t="str">
+        <x:v>loc-0210</x:v>
+      </x:c>
+      <x:c r="S39" s="87" t="str">
+        <x:v>Carroll Park Memorial</x:v>
+      </x:c>
+      <x:c r="T39" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="E39" s="87" t="str">
-        <x:v>loc-0064</x:v>
-      </x:c>
-      <x:c r="F39" s="87" t="str">
-        <x:v>Eastern Parkway</x:v>
-      </x:c>
-      <x:c r="G39" s="87" t="str">
+      <x:c r="U39" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V39" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W39" s="87" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="123" t="n">
+        <x:v>46284</x:v>
+      </x:c>
+      <x:c r="B40" s="124" t="str">
+        <x:v>loc-0247</x:v>
+      </x:c>
+      <x:c r="C40" s="124" t="str">
+        <x:v>Coney Island Beach &amp; Boardwalk</x:v>
+      </x:c>
+      <x:c r="D40" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="H39" s="87" t="str">
-        <x:v>loc-0279</x:v>
-      </x:c>
-      <x:c r="I39" s="87" t="str">
-        <x:v>Canarsie Park</x:v>
-      </x:c>
-      <x:c r="J39" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="K39" s="87" t="str">
-        <x:v>loc-0023</x:v>
-      </x:c>
-      <x:c r="L39" s="87" t="str">
-        <x:v>Trans World Airlines Flight Center</x:v>
-      </x:c>
-      <x:c r="M39" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N39" s="87" t="str">
-        <x:v>loc-0224</x:v>
-      </x:c>
-      <x:c r="O39" s="87" t="str">
-        <x:v>Father Giorgio Memorial</x:v>
-      </x:c>
-      <x:c r="P39" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q39" s="87" t="str">
+      <x:c r="E40" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F40" s="124" t="str">
+        <x:v>loc-0449</x:v>
+      </x:c>
+      <x:c r="G40" s="124" t="str">
+        <x:v>Joe's Pizza</x:v>
+      </x:c>
+      <x:c r="H40" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I40" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J40" s="124" t="str">
+        <x:v>loc-0107</x:v>
+      </x:c>
+      <x:c r="K40" s="124" t="str">
+        <x:v>Columbus Monument</x:v>
+      </x:c>
+      <x:c r="L40" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M40" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N40" s="124" t="str">
+        <x:v>loc-0400</x:v>
+      </x:c>
+      <x:c r="O40" s="124" t="str">
+        <x:v>49 Street Station</x:v>
+      </x:c>
+      <x:c r="P40" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q40" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R40" s="124" t="str">
+        <x:v>loc-0274</x:v>
+      </x:c>
+      <x:c r="S40" s="124" t="str">
+        <x:v>Blue Heron Park</x:v>
+      </x:c>
+      <x:c r="T40" s="124" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="U40" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V40" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R39" s="87" t="str"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="84" t="n">
-        <x:v>46284</x:v>
-      </x:c>
-      <x:c r="B40" s="85" t="str">
-        <x:v>loc-0438</x:v>
-      </x:c>
-      <x:c r="C40" s="85" t="str">
-        <x:v>Wonder Wheel</x:v>
-      </x:c>
-      <x:c r="D40" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="E40" s="85" t="str">
-        <x:v>loc-0002</x:v>
-      </x:c>
-      <x:c r="F40" s="85" t="str">
-        <x:v>Prospect Park</x:v>
-      </x:c>
-      <x:c r="G40" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H40" s="85" t="str">
-        <x:v>loc-0367</x:v>
-      </x:c>
-      <x:c r="I40" s="85" t="str">
-        <x:v>Leslie-Lohman Museum of Art</x:v>
-      </x:c>
-      <x:c r="J40" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K40" s="85" t="str">
-        <x:v>loc-0284</x:v>
-      </x:c>
-      <x:c r="L40" s="85" t="str">
-        <x:v>Fort Totten Park</x:v>
-      </x:c>
-      <x:c r="M40" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N40" s="85" t="str">
-        <x:v>loc-0163</x:v>
-      </x:c>
-      <x:c r="O40" s="85" t="str">
-        <x:v>Balto</x:v>
-      </x:c>
-      <x:c r="P40" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q40" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R40" s="85" t="str"/>
+      <x:c r="W40" s="124" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="86" t="n">
         <x:v>46285</x:v>
       </x:c>
       <x:c r="B41" s="87" t="str">
-        <x:v>loc-0097</x:v>
+        <x:v>loc-0099</x:v>
       </x:c>
       <x:c r="C41" s="87" t="str">
-        <x:v>Whitney Museum of American Art</x:v>
+        <x:v>Gracie Mansion</x:v>
       </x:c>
       <x:c r="D41" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E41" s="87" t="str">
-        <x:v>loc-0269</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F41" s="87" t="str">
-        <x:v>Pelham Bay Park</x:v>
+        <x:v>loc-0081</x:v>
       </x:c>
       <x:c r="G41" s="87" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>Staten Island Ferry Terminal</x:v>
       </x:c>
       <x:c r="H41" s="87" t="str">
+        <x:v>Staten Island</x:v>
+      </x:c>
+      <x:c r="I41" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J41" s="87" t="str">
+        <x:v>loc-0440</x:v>
+      </x:c>
+      <x:c r="K41" s="87" t="str">
+        <x:v>Chelsea Market</x:v>
+      </x:c>
+      <x:c r="L41" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M41" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N41" s="87" t="str">
+        <x:v>loc-0121</x:v>
+      </x:c>
+      <x:c r="O41" s="87" t="str">
+        <x:v>BOHEMIAN HALL AND PARK</x:v>
+      </x:c>
+      <x:c r="P41" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="Q41" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R41" s="87" t="str">
+        <x:v>loc-0049</x:v>
+      </x:c>
+      <x:c r="S41" s="87" t="str">
+        <x:v>Flushing Town Hall</x:v>
+      </x:c>
+      <x:c r="T41" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="U41" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V41" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W41" s="87" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="123" t="n">
+        <x:v>46286</x:v>
+      </x:c>
+      <x:c r="B42" s="124" t="str">
+        <x:v>loc-0332</x:v>
+      </x:c>
+      <x:c r="C42" s="124" t="str">
+        <x:v>Cooper Hewitt, Smithsonian Design Museum</x:v>
+      </x:c>
+      <x:c r="D42" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E42" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F42" s="124" t="str">
+        <x:v>loc-0326</x:v>
+      </x:c>
+      <x:c r="G42" s="124" t="str">
+        <x:v>The Frick Collection</x:v>
+      </x:c>
+      <x:c r="H42" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I42" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J42" s="124" t="str">
+        <x:v>loc-0481</x:v>
+      </x:c>
+      <x:c r="K42" s="124" t="str">
+        <x:v>Kings Plaza</x:v>
+      </x:c>
+      <x:c r="L42" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="M42" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N42" s="124" t="str">
         <x:v>loc-0406</x:v>
       </x:c>
-      <x:c r="I41" s="87" t="str">
+      <x:c r="O42" s="124" t="str">
         <x:v>DeKalb Avenue Station</x:v>
       </x:c>
-      <x:c r="J41" s="87" t="str">
+      <x:c r="P42" s="124" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="K41" s="87" t="str">
-        <x:v>loc-0429</x:v>
-      </x:c>
-      <x:c r="L41" s="87" t="str">
-        <x:v>34th Avenue Plaza</x:v>
-      </x:c>
-      <x:c r="M41" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N41" s="87" t="str">
-        <x:v>loc-0357</x:v>
-      </x:c>
-      <x:c r="O41" s="87" t="str">
-        <x:v>Society of Illustrators</x:v>
-      </x:c>
-      <x:c r="P41" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q41" s="87" t="str">
+      <x:c r="Q42" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R42" s="124" t="str">
+        <x:v>loc-0070</x:v>
+      </x:c>
+      <x:c r="S42" s="124" t="str">
+        <x:v>Loew's King Theatre</x:v>
+      </x:c>
+      <x:c r="T42" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="U42" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V42" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R41" s="87" t="str"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="84" t="n">
-        <x:v>46286</x:v>
-      </x:c>
-      <x:c r="B42" s="85" t="str">
-        <x:v>loc-0066</x:v>
-      </x:c>
-      <x:c r="C42" s="85" t="str">
-        <x:v>Garibaldi Memorial</x:v>
-      </x:c>
-      <x:c r="D42" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="E42" s="85" t="str">
-        <x:v>loc-0391</x:v>
-      </x:c>
-      <x:c r="F42" s="85" t="str">
-        <x:v>34 Street-Herald Square Station</x:v>
-      </x:c>
-      <x:c r="G42" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H42" s="85" t="str">
-        <x:v>loc-0409</x:v>
-      </x:c>
-      <x:c r="I42" s="85" t="str">
-        <x:v>Marcy Avenue Station</x:v>
-      </x:c>
-      <x:c r="J42" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="K42" s="85" t="str">
-        <x:v>loc-0331</x:v>
-      </x:c>
-      <x:c r="L42" s="85" t="str">
-        <x:v>International Center of Photography</x:v>
-      </x:c>
-      <x:c r="M42" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N42" s="85" t="str">
-        <x:v>loc-0215</x:v>
-      </x:c>
-      <x:c r="O42" s="85" t="str">
-        <x:v>Triumph of Government</x:v>
-      </x:c>
-      <x:c r="P42" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q42" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R42" s="85" t="str"/>
+      <x:c r="W42" s="124" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="86" t="n">
         <x:v>46287</x:v>
       </x:c>
       <x:c r="B43" s="87" t="str">
-        <x:v>loc-0447</x:v>
+        <x:v>loc-0462</x:v>
       </x:c>
       <x:c r="C43" s="87" t="str">
-        <x:v>Film Forum</x:v>
+        <x:v>Keens Steakhouse</x:v>
       </x:c>
       <x:c r="D43" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E43" s="87" t="str">
-        <x:v>loc-0061</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F43" s="87" t="str">
-        <x:v>Alice Austen House</x:v>
+        <x:v>loc-0032</x:v>
       </x:c>
       <x:c r="G43" s="87" t="str">
-        <x:v>Staten Island</x:v>
+        <x:v>Statue of Liberty and Ellis Island</x:v>
       </x:c>
       <x:c r="H43" s="87" t="str">
-        <x:v>loc-0443</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="I43" s="87" t="str">
-        <x:v>Per Se</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J43" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>loc-0008</x:v>
       </x:c>
       <x:c r="K43" s="87" t="str">
-        <x:v>loc-0070</x:v>
+        <x:v>New York Botanical Garden</x:v>
       </x:c>
       <x:c r="L43" s="87" t="str">
-        <x:v>Loew's King Theatre</x:v>
+        <x:v>The Bronx</x:v>
       </x:c>
       <x:c r="M43" s="87" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N43" s="87" t="str">
-        <x:v>loc-0161</x:v>
+        <x:v>loc-0059</x:v>
       </x:c>
       <x:c r="O43" s="87" t="str">
-        <x:v>George Washington as Master Mason</x:v>
+        <x:v>Trinity Church and Graveyard</x:v>
       </x:c>
       <x:c r="P43" s="87" t="str">
-        <x:v>Queens</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="Q43" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R43" s="87" t="str">
+        <x:v>loc-0423</x:v>
+      </x:c>
+      <x:c r="S43" s="87" t="str">
+        <x:v>Plaza de Las Americas</x:v>
+      </x:c>
+      <x:c r="T43" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U43" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V43" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R43" s="87" t="str"/>
+      <x:c r="W43" s="87" t="str"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="84" t="n">
+      <x:c r="A44" s="123" t="n">
         <x:v>46288</x:v>
       </x:c>
-      <x:c r="B44" s="85" t="str">
-        <x:v>loc-0481</x:v>
-      </x:c>
-      <x:c r="C44" s="85" t="str">
-        <x:v>Kings Plaza</x:v>
-      </x:c>
-      <x:c r="D44" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="E44" s="85" t="str">
-        <x:v>loc-0465</x:v>
-      </x:c>
-      <x:c r="F44" s="85" t="str">
-        <x:v>Russ &amp; Daughters</x:v>
-      </x:c>
-      <x:c r="G44" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H44" s="85" t="str">
-        <x:v>loc-0259</x:v>
-      </x:c>
-      <x:c r="I44" s="85" t="str">
-        <x:v>Fort Greene Park</x:v>
-      </x:c>
-      <x:c r="J44" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="K44" s="85" t="str">
+      <x:c r="B44" s="124" t="str">
+        <x:v>loc-0088</x:v>
+      </x:c>
+      <x:c r="C44" s="124" t="str">
+        <x:v>Biltmore Theater</x:v>
+      </x:c>
+      <x:c r="D44" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E44" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F44" s="124" t="str">
+        <x:v>loc-0398</x:v>
+      </x:c>
+      <x:c r="G44" s="124" t="str">
+        <x:v>Times Square-42 Street Station</x:v>
+      </x:c>
+      <x:c r="H44" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I44" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J44" s="124" t="str">
+        <x:v>loc-0390</x:v>
+      </x:c>
+      <x:c r="K44" s="124" t="str">
+        <x:v>14 Street-Union Square Station</x:v>
+      </x:c>
+      <x:c r="L44" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M44" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N44" s="124" t="str">
         <x:v>loc-0471</x:v>
       </x:c>
-      <x:c r="L44" s="85" t="str">
+      <x:c r="O44" s="124" t="str">
         <x:v>New York Times Building</x:v>
       </x:c>
-      <x:c r="M44" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N44" s="85" t="str">
-        <x:v>loc-0304</x:v>
-      </x:c>
-      <x:c r="O44" s="85" t="str">
-        <x:v>Paerdegat Basin Park</x:v>
-      </x:c>
-      <x:c r="P44" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q44" s="85" t="str">
+      <x:c r="P44" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q44" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R44" s="124" t="str">
+        <x:v>loc-0375</x:v>
+      </x:c>
+      <x:c r="S44" s="124" t="str">
+        <x:v>Museum of Comic and Cartoon Art</x:v>
+      </x:c>
+      <x:c r="T44" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U44" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V44" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R44" s="85" t="str"/>
+      <x:c r="W44" s="124" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="86" t="n">
         <x:v>46289</x:v>
       </x:c>
       <x:c r="B45" s="87" t="str">
-        <x:v>loc-0146</x:v>
+        <x:v>loc-0455</x:v>
       </x:c>
       <x:c r="C45" s="87" t="str">
-        <x:v>Unisphere and Fountain</x:v>
+        <x:v>Le Bernardin</x:v>
       </x:c>
       <x:c r="D45" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E45" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F45" s="87" t="str">
+        <x:v>loc-0249</x:v>
+      </x:c>
+      <x:c r="G45" s="87" t="str">
+        <x:v>Flushing Meadows Corona Park</x:v>
+      </x:c>
+      <x:c r="H45" s="87" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="E45" s="87" t="str">
-        <x:v>loc-0081</x:v>
-      </x:c>
-      <x:c r="F45" s="87" t="str">
-        <x:v>Staten Island Ferry Terminal</x:v>
-      </x:c>
-      <x:c r="G45" s="87" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="H45" s="87" t="str">
-        <x:v>loc-0258</x:v>
-      </x:c>
       <x:c r="I45" s="87" t="str">
-        <x:v>McCarren Park</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J45" s="87" t="str">
-        <x:v>Brooklyn</x:v>
+        <x:v>loc-0321</x:v>
       </x:c>
       <x:c r="K45" s="87" t="str">
-        <x:v>loc-0275</x:v>
+        <x:v>New Museum</x:v>
       </x:c>
       <x:c r="L45" s="87" t="str">
-        <x:v>Bronx Park</x:v>
+        <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="M45" s="87" t="str">
-        <x:v>The Bronx</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="N45" s="87" t="str">
-        <x:v>loc-0222</x:v>
+        <x:v>loc-0259</x:v>
       </x:c>
       <x:c r="O45" s="87" t="str">
-        <x:v>Antonio Meucci Memorial</x:v>
+        <x:v>Fort Greene Park</x:v>
       </x:c>
       <x:c r="P45" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
       <x:c r="Q45" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R45" s="87" t="str">
+        <x:v>loc-0062</x:v>
+      </x:c>
+      <x:c r="S45" s="87" t="str">
+        <x:v>B &amp; B Carousell</x:v>
+      </x:c>
+      <x:c r="T45" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="U45" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V45" s="87" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R45" s="87" t="str"/>
+      <x:c r="W45" s="87" t="str"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="84" t="n">
+      <x:c r="A46" s="123" t="n">
         <x:v>46290</x:v>
       </x:c>
-      <x:c r="B46" s="85" t="str">
-        <x:v>loc-0336</x:v>
-      </x:c>
-      <x:c r="C46" s="85" t="str">
-        <x:v>Village Vanguard</x:v>
-      </x:c>
-      <x:c r="D46" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E46" s="85" t="str">
-        <x:v>loc-0028</x:v>
-      </x:c>
-      <x:c r="F46" s="85" t="str">
-        <x:v>Grant’s Tomb</x:v>
-      </x:c>
-      <x:c r="G46" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H46" s="85" t="str">
-        <x:v>loc-0358</x:v>
-      </x:c>
-      <x:c r="I46" s="85" t="str">
-        <x:v>American Folk Art Museum</x:v>
-      </x:c>
-      <x:c r="J46" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K46" s="85" t="str">
-        <x:v>loc-0375</x:v>
-      </x:c>
-      <x:c r="L46" s="85" t="str">
-        <x:v>Museum of Comic and Cartoon Art</x:v>
-      </x:c>
-      <x:c r="M46" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N46" s="85" t="str">
-        <x:v>loc-0077</x:v>
-      </x:c>
-      <x:c r="O46" s="85" t="str">
-        <x:v>Rainey Memorial Gates</x:v>
-      </x:c>
-      <x:c r="P46" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q46" s="85" t="str">
+      <x:c r="B46" s="124" t="str">
+        <x:v>loc-0011</x:v>
+      </x:c>
+      <x:c r="C46" s="124" t="str">
+        <x:v>New York Public Library and Bryant Park</x:v>
+      </x:c>
+      <x:c r="D46" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E46" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F46" s="124" t="str">
+        <x:v>loc-0001</x:v>
+      </x:c>
+      <x:c r="G46" s="124" t="str">
+        <x:v>Brooklyn Bridge</x:v>
+      </x:c>
+      <x:c r="H46" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="I46" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J46" s="124" t="str">
+        <x:v>loc-0109</x:v>
+      </x:c>
+      <x:c r="K46" s="124" t="str">
+        <x:v>Fort Jay</x:v>
+      </x:c>
+      <x:c r="L46" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M46" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N46" s="124" t="str">
+        <x:v>loc-0036</x:v>
+      </x:c>
+      <x:c r="O46" s="124" t="str">
+        <x:v>Floyd Bennett Field</x:v>
+      </x:c>
+      <x:c r="P46" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="Q46" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R46" s="124" t="str">
+        <x:v>loc-0285</x:v>
+      </x:c>
+      <x:c r="S46" s="124" t="str">
+        <x:v>Fort Washington Park</x:v>
+      </x:c>
+      <x:c r="T46" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U46" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V46" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R46" s="85" t="str"/>
+      <x:c r="W46" s="124" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="86" t="n">
         <x:v>46291</x:v>
       </x:c>
       <x:c r="B47" s="87" t="str">
-        <x:v>loc-0446</x:v>
+        <x:v>loc-0485</x:v>
       </x:c>
       <x:c r="C47" s="87" t="str">
-        <x:v>Dirt Candy</x:v>
+        <x:v>Starlight Park</x:v>
       </x:c>
       <x:c r="D47" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Bronx</x:v>
       </x:c>
       <x:c r="E47" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F47" s="87" t="str">
+        <x:v>loc-0013</x:v>
+      </x:c>
+      <x:c r="G47" s="87" t="str">
+        <x:v>Apollo Theater</x:v>
+      </x:c>
+      <x:c r="H47" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I47" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J47" s="87" t="str">
+        <x:v>loc-0097</x:v>
+      </x:c>
+      <x:c r="K47" s="87" t="str">
+        <x:v>Whitney Museum of American Art</x:v>
+      </x:c>
+      <x:c r="L47" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M47" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N47" s="87" t="str">
+        <x:v>loc-0453</x:v>
+      </x:c>
+      <x:c r="O47" s="87" t="str">
+        <x:v>Via 57 West</x:v>
+      </x:c>
+      <x:c r="P47" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q47" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R47" s="87" t="str">
+        <x:v>loc-0197</x:v>
+      </x:c>
+      <x:c r="S47" s="87" t="str">
+        <x:v>Sunnyside Memorial</x:v>
+      </x:c>
+      <x:c r="T47" s="87" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="U47" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V47" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W47" s="87" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="123" t="n">
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="B48" s="124" t="str">
+        <x:v>loc-0027</x:v>
+      </x:c>
+      <x:c r="C48" s="124" t="str">
+        <x:v>Cooper Union</x:v>
+      </x:c>
+      <x:c r="D48" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E48" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F48" s="124" t="str">
         <x:v>loc-0382</x:v>
       </x:c>
-      <x:c r="F47" s="87" t="str">
+      <x:c r="G48" s="124" t="str">
         <x:v>Queensboro Plaza Station</x:v>
       </x:c>
-      <x:c r="G47" s="87" t="str">
+      <x:c r="H48" s="124" t="str">
         <x:v>Queens</x:v>
       </x:c>
-      <x:c r="H47" s="87" t="str">
-        <x:v>loc-0067</x:v>
-      </x:c>
-      <x:c r="I47" s="87" t="str">
-        <x:v>High Bridge Aqueduct and Water Tower</x:v>
-      </x:c>
-      <x:c r="J47" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="K47" s="87" t="str">
-        <x:v>loc-0364</x:v>
-      </x:c>
-      <x:c r="L47" s="87" t="str">
-        <x:v>Museum of American Finance</x:v>
-      </x:c>
-      <x:c r="M47" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N47" s="87" t="str">
-        <x:v>loc-0244</x:v>
-      </x:c>
-      <x:c r="O47" s="87" t="str">
-        <x:v>Midland Beach War Memorial</x:v>
-      </x:c>
-      <x:c r="P47" s="87" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="Q47" s="87" t="str">
+      <x:c r="I48" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J48" s="124" t="str">
+        <x:v>loc-0064</x:v>
+      </x:c>
+      <x:c r="K48" s="124" t="str">
+        <x:v>Eastern Parkway</x:v>
+      </x:c>
+      <x:c r="L48" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="M48" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N48" s="124" t="str">
+        <x:v>loc-0450</x:v>
+      </x:c>
+      <x:c r="O48" s="124" t="str">
+        <x:v>Papaya King</x:v>
+      </x:c>
+      <x:c r="P48" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q48" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R48" s="124" t="str">
+        <x:v>loc-0137</x:v>
+      </x:c>
+      <x:c r="S48" s="124" t="str">
+        <x:v>Low Memorial Library, Columbia University</x:v>
+      </x:c>
+      <x:c r="T48" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U48" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V48" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R47" s="87" t="str"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="84" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="B48" s="85" t="str">
-        <x:v>loc-0056</x:v>
-      </x:c>
-      <x:c r="C48" s="85" t="str">
-        <x:v>Battery Weed</x:v>
-      </x:c>
-      <x:c r="D48" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="E48" s="85" t="str">
-        <x:v>loc-0397</x:v>
-      </x:c>
-      <x:c r="F48" s="85" t="str">
-        <x:v>Jackson Heights-Roosevelt Avenue Station</x:v>
-      </x:c>
-      <x:c r="G48" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H48" s="85" t="str">
-        <x:v>loc-0273</x:v>
-      </x:c>
-      <x:c r="I48" s="85" t="str">
-        <x:v>Bloomingdale Park</x:v>
-      </x:c>
-      <x:c r="J48" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="K48" s="85" t="str">
-        <x:v>loc-0069</x:v>
-      </x:c>
-      <x:c r="L48" s="85" t="str">
-        <x:v>Loew's Kameo Theater</x:v>
-      </x:c>
-      <x:c r="M48" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N48" s="85" t="str">
-        <x:v>loc-0120</x:v>
-      </x:c>
-      <x:c r="O48" s="85" t="str">
-        <x:v>Beth Olam Cemetery</x:v>
-      </x:c>
-      <x:c r="P48" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q48" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R48" s="85" t="str"/>
+      <x:c r="W48" s="124" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="86" t="n">
         <x:v>46293</x:v>
       </x:c>
       <x:c r="B49" s="87" t="str">
-        <x:v>loc-0460</x:v>
+        <x:v>loc-0029</x:v>
       </x:c>
       <x:c r="C49" s="87" t="str">
-        <x:v>Waldorf–Astoria</x:v>
+        <x:v>The Met Cloisters</x:v>
       </x:c>
       <x:c r="D49" s="87" t="str">
         <x:v>Manhattan</x:v>
       </x:c>
       <x:c r="E49" s="87" t="str">
-        <x:v>loc-0005</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="F49" s="87" t="str">
-        <x:v>Grand Central Terminal</x:v>
+        <x:v>loc-0483</x:v>
       </x:c>
       <x:c r="G49" s="87" t="str">
-        <x:v>Manhattan</x:v>
+        <x:v>Empire Outlets</x:v>
       </x:c>
       <x:c r="H49" s="87" t="str">
-        <x:v>loc-0129</x:v>
+        <x:v>Staten Island</x:v>
       </x:c>
       <x:c r="I49" s="87" t="str">
-        <x:v>Erasmus Hall Academy</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="J49" s="87" t="str">
+        <x:v>loc-0002</x:v>
+      </x:c>
+      <x:c r="K49" s="87" t="str">
+        <x:v>Prospect Park</x:v>
+      </x:c>
+      <x:c r="L49" s="87" t="str">
         <x:v>Brooklyn</x:v>
       </x:c>
-      <x:c r="K49" s="87" t="str">
+      <x:c r="M49" s="87" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N49" s="87" t="str">
+        <x:v>loc-0119</x:v>
+      </x:c>
+      <x:c r="O49" s="87" t="str">
+        <x:v>Yiddish Art Theatre</x:v>
+      </x:c>
+      <x:c r="P49" s="87" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q49" s="87" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R49" s="87" t="str">
+        <x:v>loc-0208</x:v>
+      </x:c>
+      <x:c r="S49" s="87" t="str">
+        <x:v>Brooklyn War Memorial</x:v>
+      </x:c>
+      <x:c r="T49" s="87" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="U49" s="87" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V49" s="87" t="str">
+        <x:v>scheduled</x:v>
+      </x:c>
+      <x:c r="W49" s="87" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="123" t="n">
+        <x:v>46294</x:v>
+      </x:c>
+      <x:c r="B50" s="124" t="str">
+        <x:v>loc-0437</x:v>
+      </x:c>
+      <x:c r="C50" s="124" t="str">
+        <x:v>Luna Park</x:v>
+      </x:c>
+      <x:c r="D50" s="124" t="str">
+        <x:v>Brooklyn</x:v>
+      </x:c>
+      <x:c r="E50" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F50" s="124" t="str">
+        <x:v>loc-0441</x:v>
+      </x:c>
+      <x:c r="G50" s="124" t="str">
+        <x:v>Arthur Ashe Stadium</x:v>
+      </x:c>
+      <x:c r="H50" s="124" t="str">
+        <x:v>Queens</x:v>
+      </x:c>
+      <x:c r="I50" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J50" s="124" t="str">
+        <x:v>loc-0488</x:v>
+      </x:c>
+      <x:c r="K50" s="124" t="str">
+        <x:v>East River Plaza</x:v>
+      </x:c>
+      <x:c r="L50" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="M50" s="124" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N50" s="124" t="str">
         <x:v>loc-0306</x:v>
       </x:c>
-      <x:c r="L49" s="87" t="str">
+      <x:c r="O50" s="124" t="str">
         <x:v>Pralls Island</x:v>
       </x:c>
-      <x:c r="M49" s="87" t="str">
+      <x:c r="P50" s="124" t="str">
         <x:v>Staten Island</x:v>
       </x:c>
-      <x:c r="N49" s="87" t="str">
-        <x:v>loc-0191</x:v>
-      </x:c>
-      <x:c r="O49" s="87" t="str">
-        <x:v>Tortoise and Hare</x:v>
-      </x:c>
-      <x:c r="P49" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q49" s="87" t="str">
+      <x:c r="Q50" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R50" s="124" t="str">
+        <x:v>loc-0124</x:v>
+      </x:c>
+      <x:c r="S50" s="124" t="str">
+        <x:v>Carnegie, Andrew, Mansion</x:v>
+      </x:c>
+      <x:c r="T50" s="124" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U50" s="124" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="V50" s="124" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R49" s="87" t="str"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="84" t="n">
-        <x:v>46294</x:v>
-      </x:c>
-      <x:c r="B50" s="85" t="str">
-        <x:v>loc-0487</x:v>
-      </x:c>
-      <x:c r="C50" s="85" t="str">
-        <x:v>Pepsi-Cola sign</x:v>
-      </x:c>
-      <x:c r="D50" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="E50" s="85" t="str">
-        <x:v>loc-0337</x:v>
-      </x:c>
-      <x:c r="F50" s="85" t="str">
-        <x:v>Blue Note Jazz Club</x:v>
-      </x:c>
-      <x:c r="G50" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H50" s="85" t="str">
-        <x:v>loc-0450</x:v>
-      </x:c>
-      <x:c r="I50" s="85" t="str">
-        <x:v>Papaya King</x:v>
-      </x:c>
-      <x:c r="J50" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K50" s="85" t="str">
-        <x:v>loc-0119</x:v>
-      </x:c>
-      <x:c r="L50" s="85" t="str">
-        <x:v>Yiddish Art Theatre</x:v>
-      </x:c>
-      <x:c r="M50" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N50" s="85" t="str">
-        <x:v>loc-0271</x:v>
-      </x:c>
-      <x:c r="O50" s="85" t="str">
-        <x:v>Alley Pond Park</x:v>
-      </x:c>
-      <x:c r="P50" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q50" s="85" t="str">
+      <x:c r="W50" s="124" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="125" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B51" s="126" t="str">
+        <x:v>loc-0413</x:v>
+      </x:c>
+      <x:c r="C51" s="126" t="str">
+        <x:v>Flatiron Plaza</x:v>
+      </x:c>
+      <x:c r="D51" s="126" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="E51" s="126" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="F51" s="126" t="str">
+        <x:v>loc-0479</x:v>
+      </x:c>
+      <x:c r="G51" s="126" t="str">
+        <x:v>Madison Square Garden</x:v>
+      </x:c>
+      <x:c r="H51" s="126" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="I51" s="126" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="J51" s="126" t="str">
+        <x:v>loc-0378</x:v>
+      </x:c>
+      <x:c r="K51" s="126" t="str">
+        <x:v>Intrepid Sea, Air &amp; Space Museum</x:v>
+      </x:c>
+      <x:c r="L51" s="126" t="str">
+        <x:v>New York City</x:v>
+      </x:c>
+      <x:c r="M51" s="126" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="N51" s="126" t="str">
+        <x:v>loc-0353</x:v>
+      </x:c>
+      <x:c r="O51" s="126" t="str">
+        <x:v>Henry Clay Frick House</x:v>
+      </x:c>
+      <x:c r="P51" s="126" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="Q51" s="126" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="R51" s="126" t="str">
+        <x:v>loc-0427</x:v>
+      </x:c>
+      <x:c r="S51" s="126" t="str">
+        <x:v>Hudson Square Plaza</x:v>
+      </x:c>
+      <x:c r="T51" s="126" t="str">
+        <x:v>Manhattan</x:v>
+      </x:c>
+      <x:c r="U51" s="126" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="V51" s="126" t="str">
         <x:v>scheduled</x:v>
       </x:c>
-      <x:c r="R50" s="85" t="str"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="86" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="B51" s="87" t="str">
-        <x:v>loc-0112</x:v>
-      </x:c>
-      <x:c r="C51" s="87" t="str">
-        <x:v>Hudson Theater</x:v>
-      </x:c>
-      <x:c r="D51" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E51" s="87" t="str">
-        <x:v>loc-0012</x:v>
-      </x:c>
-      <x:c r="F51" s="87" t="str">
-        <x:v>New York Stock Exchange</x:v>
-      </x:c>
-      <x:c r="G51" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H51" s="87" t="str">
-        <x:v>loc-0114</x:v>
-      </x:c>
-      <x:c r="I51" s="87" t="str">
-        <x:v>Mary McLeod Bethune Gardens</x:v>
-      </x:c>
-      <x:c r="J51" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K51" s="87" t="str">
-        <x:v>loc-0054</x:v>
-      </x:c>
-      <x:c r="L51" s="87" t="str">
-        <x:v>Theodore Roosevelt Birthplace</x:v>
-      </x:c>
-      <x:c r="M51" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N51" s="87" t="str">
-        <x:v>loc-0136</x:v>
-      </x:c>
-      <x:c r="O51" s="87" t="str">
-        <x:v>Long Island City Courthouse Complex</x:v>
-      </x:c>
-      <x:c r="P51" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q51" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R51" s="87" t="str"/>
+      <x:c r="W51" s="126" t="str"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="84" t="n">
-        <x:v>46296</x:v>
-      </x:c>
-      <x:c r="B52" s="85" t="str">
-        <x:v>loc-0482</x:v>
-      </x:c>
-      <x:c r="C52" s="85" t="str">
-        <x:v>La Marqueta</x:v>
-      </x:c>
-      <x:c r="D52" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E52" s="85" t="str">
-        <x:v>loc-0326</x:v>
-      </x:c>
-      <x:c r="F52" s="85" t="str">
-        <x:v>The Frick Collection</x:v>
-      </x:c>
-      <x:c r="G52" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H52" s="85" t="str">
-        <x:v>loc-0314</x:v>
-      </x:c>
-      <x:c r="I52" s="85" t="str">
-        <x:v>Willowbrook Park</x:v>
-      </x:c>
-      <x:c r="J52" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="K52" s="85" t="str">
-        <x:v>loc-0464</x:v>
-      </x:c>
-      <x:c r="L52" s="85" t="str">
-        <x:v>One Court Square</x:v>
-      </x:c>
-      <x:c r="M52" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N52" s="85" t="str">
-        <x:v>loc-0359</x:v>
-      </x:c>
-      <x:c r="O52" s="85" t="str">
-        <x:v>Madame Tussauds New York</x:v>
-      </x:c>
-      <x:c r="P52" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q52" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R52" s="85" t="str"/>
+      <x:c r="A52"/>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
+      <x:c r="I52"/>
+      <x:c r="J52"/>
+      <x:c r="K52"/>
+      <x:c r="L52"/>
+      <x:c r="M52"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="86" t="n">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="B53" s="87" t="str">
-        <x:v>loc-0495</x:v>
-      </x:c>
-      <x:c r="C53" s="87" t="str">
-        <x:v>Flushing Meadows Carousel</x:v>
-      </x:c>
-      <x:c r="D53" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="E53" s="87" t="str">
-        <x:v>loc-0026</x:v>
-      </x:c>
-      <x:c r="F53" s="87" t="str">
-        <x:v>Woolworth Building</x:v>
-      </x:c>
-      <x:c r="G53" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H53" s="87" t="str">
-        <x:v>loc-0348</x:v>
-      </x:c>
-      <x:c r="I53" s="87" t="str">
-        <x:v>Skyscraper Museum</x:v>
-      </x:c>
-      <x:c r="J53" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K53" s="87" t="str">
-        <x:v>loc-0419</x:v>
-      </x:c>
-      <x:c r="L53" s="87" t="str">
-        <x:v>Albee Square Plaza</x:v>
-      </x:c>
-      <x:c r="M53" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N53" s="87" t="str">
-        <x:v>loc-0236</x:v>
-      </x:c>
-      <x:c r="O53" s="87" t="str">
-        <x:v>Astoria Park War Memorial</x:v>
-      </x:c>
-      <x:c r="P53" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q53" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R53" s="87" t="str"/>
+      <x:c r="A53"/>
+      <x:c r="B53"/>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
+      <x:c r="E53"/>
+      <x:c r="F53"/>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+      <x:c r="I53"/>
+      <x:c r="J53"/>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
+      <x:c r="M53"/>
+      <x:c r="N53"/>
+      <x:c r="O53"/>
+      <x:c r="P53"/>
+      <x:c r="Q53"/>
+      <x:c r="R53"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="84" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="B54" s="85" t="str">
-        <x:v>loc-0107</x:v>
-      </x:c>
-      <x:c r="C54" s="85" t="str">
-        <x:v>Columbus Monument</x:v>
-      </x:c>
-      <x:c r="D54" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E54" s="85" t="str">
-        <x:v>loc-0058</x:v>
-      </x:c>
-      <x:c r="F54" s="85" t="str">
-        <x:v>Conference House</x:v>
-      </x:c>
-      <x:c r="G54" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="H54" s="85" t="str">
-        <x:v>loc-0124</x:v>
-      </x:c>
-      <x:c r="I54" s="85" t="str">
-        <x:v>Carnegie, Andrew, Mansion</x:v>
-      </x:c>
-      <x:c r="J54" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K54" s="85" t="str">
-        <x:v>loc-0274</x:v>
-      </x:c>
-      <x:c r="L54" s="85" t="str">
-        <x:v>Blue Heron Park</x:v>
-      </x:c>
-      <x:c r="M54" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="N54" s="85" t="str">
-        <x:v>loc-0039</x:v>
-      </x:c>
-      <x:c r="O54" s="85" t="str">
-        <x:v>Jerome Park Reservoir</x:v>
-      </x:c>
-      <x:c r="P54" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q54" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R54" s="85" t="str"/>
+      <x:c r="A54"/>
+      <x:c r="B54"/>
+      <x:c r="C54"/>
+      <x:c r="D54"/>
+      <x:c r="E54"/>
+      <x:c r="F54"/>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
+      <x:c r="I54"/>
+      <x:c r="J54"/>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
+      <x:c r="M54"/>
+      <x:c r="N54"/>
+      <x:c r="O54"/>
+      <x:c r="P54"/>
+      <x:c r="Q54"/>
+      <x:c r="R54"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="86" t="n">
-        <x:v>46299</x:v>
-      </x:c>
-      <x:c r="B55" s="87" t="str">
-        <x:v>loc-0321</x:v>
-      </x:c>
-      <x:c r="C55" s="87" t="str">
-        <x:v>New Museum</x:v>
-      </x:c>
-      <x:c r="D55" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E55" s="87" t="str">
-        <x:v>loc-0075</x:v>
-      </x:c>
-      <x:c r="F55" s="87" t="str">
-        <x:v>Parkway Village</x:v>
-      </x:c>
-      <x:c r="G55" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H55" s="87" t="str">
-        <x:v>loc-0396</x:v>
-      </x:c>
-      <x:c r="I55" s="87" t="str">
-        <x:v>Forest Hills-71 Avenue Station</x:v>
-      </x:c>
-      <x:c r="J55" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="K55" s="87" t="str">
-        <x:v>loc-0047</x:v>
-      </x:c>
-      <x:c r="L55" s="87" t="str">
-        <x:v>Bartow-Pell Mansion and Carriage House</x:v>
-      </x:c>
-      <x:c r="M55" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="N55" s="87" t="str">
-        <x:v>loc-0345</x:v>
-      </x:c>
-      <x:c r="O55" s="87" t="str">
-        <x:v>Mishkin Gallery</x:v>
-      </x:c>
-      <x:c r="P55" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q55" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R55" s="87" t="str"/>
+      <x:c r="A55"/>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
+      <x:c r="E55"/>
+      <x:c r="F55"/>
+      <x:c r="G55"/>
+      <x:c r="H55"/>
+      <x:c r="I55"/>
+      <x:c r="J55"/>
+      <x:c r="K55"/>
+      <x:c r="L55"/>
+      <x:c r="M55"/>
+      <x:c r="N55"/>
+      <x:c r="O55"/>
+      <x:c r="P55"/>
+      <x:c r="Q55"/>
+      <x:c r="R55"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="84" t="n">
-        <x:v>46300</x:v>
-      </x:c>
-      <x:c r="B56" s="85" t="str">
-        <x:v>loc-0327</x:v>
-      </x:c>
-      <x:c r="C56" s="85" t="str">
-        <x:v>New York Transit Museum</x:v>
-      </x:c>
-      <x:c r="D56" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="E56" s="85" t="str">
-        <x:v>loc-0051</x:v>
-      </x:c>
-      <x:c r="F56" s="85" t="str">
-        <x:v>Wave Hill</x:v>
-      </x:c>
-      <x:c r="G56" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="H56" s="85" t="str">
-        <x:v>loc-0040</x:v>
-      </x:c>
-      <x:c r="I56" s="85" t="str">
-        <x:v>Washington Bridge</x:v>
-      </x:c>
-      <x:c r="J56" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="K56" s="85" t="str">
-        <x:v>loc-0459</x:v>
-      </x:c>
-      <x:c r="L56" s="85" t="str">
-        <x:v>Nitehawk Cinema</x:v>
-      </x:c>
-      <x:c r="M56" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N56" s="85" t="str">
-        <x:v>loc-0176</x:v>
-      </x:c>
-      <x:c r="O56" s="85" t="str">
-        <x:v>Call of the Sea</x:v>
-      </x:c>
-      <x:c r="P56" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q56" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R56" s="85" t="str"/>
+      <x:c r="A56"/>
+      <x:c r="B56"/>
+      <x:c r="C56"/>
+      <x:c r="D56"/>
+      <x:c r="E56"/>
+      <x:c r="F56"/>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
+      <x:c r="I56"/>
+      <x:c r="J56"/>
+      <x:c r="K56"/>
+      <x:c r="L56"/>
+      <x:c r="M56"/>
+      <x:c r="N56"/>
+      <x:c r="O56"/>
+      <x:c r="P56"/>
+      <x:c r="Q56"/>
+      <x:c r="R56"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="86" t="n">
-        <x:v>46301</x:v>
-      </x:c>
-      <x:c r="B57" s="87" t="str">
-        <x:v>loc-0013</x:v>
-      </x:c>
-      <x:c r="C57" s="87" t="str">
-        <x:v>Apollo Theater</x:v>
-      </x:c>
-      <x:c r="D57" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E57" s="87" t="str">
-        <x:v>loc-0014</x:v>
-      </x:c>
-      <x:c r="F57" s="87" t="str">
-        <x:v>Fraunces Tavern</x:v>
-      </x:c>
-      <x:c r="G57" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H57" s="87" t="str">
-        <x:v>loc-0402</x:v>
-      </x:c>
-      <x:c r="I57" s="87" t="str">
-        <x:v>86 Street Station</x:v>
-      </x:c>
-      <x:c r="J57" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K57" s="87" t="str">
-        <x:v>loc-0290</x:v>
-      </x:c>
-      <x:c r="L57" s="87" t="str">
-        <x:v>Hart Island</x:v>
-      </x:c>
-      <x:c r="M57" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="N57" s="87" t="str">
-        <x:v>loc-0168</x:v>
-      </x:c>
-      <x:c r="O57" s="87" t="str">
-        <x:v>George Washington Accompanied by Fame and Valor</x:v>
-      </x:c>
-      <x:c r="P57" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q57" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R57" s="87" t="str"/>
+      <x:c r="A57"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
+      <x:c r="E57"/>
+      <x:c r="F57"/>
+      <x:c r="G57"/>
+      <x:c r="H57"/>
+      <x:c r="I57"/>
+      <x:c r="J57"/>
+      <x:c r="K57"/>
+      <x:c r="L57"/>
+      <x:c r="M57"/>
+      <x:c r="N57"/>
+      <x:c r="O57"/>
+      <x:c r="P57"/>
+      <x:c r="Q57"/>
+      <x:c r="R57"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="84" t="n">
-        <x:v>46302</x:v>
-      </x:c>
-      <x:c r="B58" s="85" t="str">
-        <x:v>loc-0407</x:v>
-      </x:c>
-      <x:c r="C58" s="85" t="str">
-        <x:v>Grand Central-42 Street Station</x:v>
-      </x:c>
-      <x:c r="D58" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E58" s="85" t="str">
-        <x:v>loc-0247</x:v>
-      </x:c>
-      <x:c r="F58" s="85" t="str">
-        <x:v>Coney Island Beach &amp; Boardwalk</x:v>
-      </x:c>
-      <x:c r="G58" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H58" s="85" t="str">
-        <x:v>loc-0059</x:v>
-      </x:c>
-      <x:c r="I58" s="85" t="str">
-        <x:v>Trinity Church and Graveyard</x:v>
-      </x:c>
-      <x:c r="J58" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K58" s="85" t="str">
-        <x:v>loc-0318</x:v>
-      </x:c>
-      <x:c r="L58" s="85" t="str">
-        <x:v>John V. Lindsay East River Park</x:v>
-      </x:c>
-      <x:c r="M58" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N58" s="85" t="str">
-        <x:v>loc-0233</x:v>
-      </x:c>
-      <x:c r="O58" s="85" t="str">
-        <x:v>John F. Kennedy Memorial</x:v>
-      </x:c>
-      <x:c r="P58" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q58" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R58" s="85" t="str"/>
+      <x:c r="A58"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
+      <x:c r="E58"/>
+      <x:c r="F58"/>
+      <x:c r="G58"/>
+      <x:c r="H58"/>
+      <x:c r="I58"/>
+      <x:c r="J58"/>
+      <x:c r="K58"/>
+      <x:c r="L58"/>
+      <x:c r="M58"/>
+      <x:c r="N58"/>
+      <x:c r="O58"/>
+      <x:c r="P58"/>
+      <x:c r="Q58"/>
+      <x:c r="R58"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="86" t="n">
-        <x:v>46303</x:v>
-      </x:c>
-      <x:c r="B59" s="87" t="str">
-        <x:v>loc-0456</x:v>
-      </x:c>
-      <x:c r="C59" s="87" t="str">
-        <x:v>One Vanderbilt</x:v>
-      </x:c>
-      <x:c r="D59" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E59" s="87" t="str">
-        <x:v>loc-0489</x:v>
-      </x:c>
-      <x:c r="F59" s="87" t="str">
-        <x:v>Atlantic Terminal</x:v>
-      </x:c>
-      <x:c r="G59" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H59" s="87" t="str">
-        <x:v>loc-0335</x:v>
-      </x:c>
-      <x:c r="I59" s="87" t="str">
-        <x:v>Bowery Ballroom</x:v>
-      </x:c>
-      <x:c r="J59" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K59" s="87" t="str">
-        <x:v>loc-0076</x:v>
-      </x:c>
-      <x:c r="L59" s="87" t="str">
-        <x:v>Port Morris Ferry Bridges</x:v>
-      </x:c>
-      <x:c r="M59" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="N59" s="87" t="str">
-        <x:v>loc-0333</x:v>
-      </x:c>
-      <x:c r="O59" s="87" t="str">
-        <x:v>National Museum of the American Indian George Gustav Heye Center</x:v>
-      </x:c>
-      <x:c r="P59" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q59" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R59" s="87" t="str"/>
+      <x:c r="A59"/>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
+      <x:c r="E59"/>
+      <x:c r="F59"/>
+      <x:c r="G59"/>
+      <x:c r="H59"/>
+      <x:c r="I59"/>
+      <x:c r="J59"/>
+      <x:c r="K59"/>
+      <x:c r="L59"/>
+      <x:c r="M59"/>
+      <x:c r="N59"/>
+      <x:c r="O59"/>
+      <x:c r="P59"/>
+      <x:c r="Q59"/>
+      <x:c r="R59"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="84" t="n">
-        <x:v>46304</x:v>
-      </x:c>
-      <x:c r="B60" s="85" t="str">
-        <x:v>loc-0020</x:v>
-      </x:c>
-      <x:c r="C60" s="85" t="str">
-        <x:v>Rockefeller Center</x:v>
-      </x:c>
-      <x:c r="D60" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E60" s="85" t="str">
-        <x:v>loc-0479</x:v>
-      </x:c>
-      <x:c r="F60" s="85" t="str">
-        <x:v>Madison Square Garden</x:v>
-      </x:c>
-      <x:c r="G60" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H60" s="85" t="str">
-        <x:v>loc-0313</x:v>
-      </x:c>
-      <x:c r="I60" s="85" t="str">
-        <x:v>Wards Island Park</x:v>
-      </x:c>
-      <x:c r="J60" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K60" s="85" t="str">
-        <x:v>loc-0082</x:v>
-      </x:c>
-      <x:c r="L60" s="85" t="str">
-        <x:v>U.S. Army Military Ocean Terminal</x:v>
-      </x:c>
-      <x:c r="M60" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="N60" s="85" t="str">
-        <x:v>loc-0157</x:v>
-      </x:c>
-      <x:c r="O60" s="85" t="str">
-        <x:v>Harriet Tubman Memorial</x:v>
-      </x:c>
-      <x:c r="P60" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q60" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R60" s="85" t="str"/>
+      <x:c r="A60"/>
+      <x:c r="B60"/>
+      <x:c r="C60"/>
+      <x:c r="D60"/>
+      <x:c r="E60"/>
+      <x:c r="F60"/>
+      <x:c r="G60"/>
+      <x:c r="H60"/>
+      <x:c r="I60"/>
+      <x:c r="J60"/>
+      <x:c r="K60"/>
+      <x:c r="L60"/>
+      <x:c r="M60"/>
+      <x:c r="N60"/>
+      <x:c r="O60"/>
+      <x:c r="P60"/>
+      <x:c r="Q60"/>
+      <x:c r="R60"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="86" t="n">
-        <x:v>46305</x:v>
-      </x:c>
-      <x:c r="B61" s="87" t="str">
-        <x:v>loc-0413</x:v>
-      </x:c>
-      <x:c r="C61" s="87" t="str">
-        <x:v>Flatiron Plaza</x:v>
-      </x:c>
-      <x:c r="D61" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E61" s="87" t="str">
-        <x:v>loc-0315</x:v>
-      </x:c>
-      <x:c r="F61" s="87" t="str">
-        <x:v>Brooklyn Botanic Garden</x:v>
-      </x:c>
-      <x:c r="G61" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H61" s="87" t="str">
-        <x:v>loc-0415</x:v>
-      </x:c>
-      <x:c r="I61" s="87" t="str">
-        <x:v>Pearl Street Plaza</x:v>
-      </x:c>
-      <x:c r="J61" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="K61" s="87" t="str">
-        <x:v>loc-0363</x:v>
-      </x:c>
-      <x:c r="L61" s="87" t="str">
-        <x:v>Enid A. Haupt Glass Garden</x:v>
-      </x:c>
-      <x:c r="M61" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N61" s="87" t="str">
-        <x:v>loc-0170</x:v>
-      </x:c>
-      <x:c r="O61" s="87" t="str">
-        <x:v>Para Roberto</x:v>
-      </x:c>
-      <x:c r="P61" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="Q61" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R61" s="87" t="str"/>
+      <x:c r="A61"/>
+      <x:c r="B61"/>
+      <x:c r="C61"/>
+      <x:c r="D61"/>
+      <x:c r="E61"/>
+      <x:c r="F61"/>
+      <x:c r="G61"/>
+      <x:c r="H61"/>
+      <x:c r="I61"/>
+      <x:c r="J61"/>
+      <x:c r="K61"/>
+      <x:c r="L61"/>
+      <x:c r="M61"/>
+      <x:c r="N61"/>
+      <x:c r="O61"/>
+      <x:c r="P61"/>
+      <x:c r="Q61"/>
+      <x:c r="R61"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="84" t="n">
-        <x:v>46306</x:v>
-      </x:c>
-      <x:c r="B62" s="85" t="str">
-        <x:v>loc-0109</x:v>
-      </x:c>
-      <x:c r="C62" s="85" t="str">
-        <x:v>Fort Jay</x:v>
-      </x:c>
-      <x:c r="D62" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E62" s="85" t="str">
-        <x:v>loc-0205</x:v>
-      </x:c>
-      <x:c r="F62" s="85" t="str">
-        <x:v>Rockefeller Fountain</x:v>
-      </x:c>
-      <x:c r="G62" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="H62" s="85" t="str">
-        <x:v>loc-0355</x:v>
-      </x:c>
-      <x:c r="I62" s="85" t="str">
-        <x:v>Merchant's House Museum</x:v>
-      </x:c>
-      <x:c r="J62" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K62" s="85" t="str">
-        <x:v>loc-0291</x:v>
-      </x:c>
-      <x:c r="L62" s="85" t="str">
-        <x:v>High Rock Park</x:v>
-      </x:c>
-      <x:c r="M62" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="N62" s="85" t="str">
-        <x:v>loc-0203</x:v>
-      </x:c>
-      <x:c r="O62" s="85" t="str">
-        <x:v>Korean War Memorial</x:v>
-      </x:c>
-      <x:c r="P62" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q62" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R62" s="85" t="str"/>
+      <x:c r="A62"/>
+      <x:c r="B62"/>
+      <x:c r="C62"/>
+      <x:c r="D62"/>
+      <x:c r="E62"/>
+      <x:c r="F62"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+      <x:c r="I62"/>
+      <x:c r="J62"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
+      <x:c r="M62"/>
+      <x:c r="N62"/>
+      <x:c r="O62"/>
+      <x:c r="P62"/>
+      <x:c r="Q62"/>
+      <x:c r="R62"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="86" t="n">
-        <x:v>46307</x:v>
-      </x:c>
-      <x:c r="B63" s="87" t="str">
-        <x:v>loc-0093</x:v>
-      </x:c>
-      <x:c r="C63" s="87" t="str">
-        <x:v>New Amsterdam Theater</x:v>
-      </x:c>
-      <x:c r="D63" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E63" s="87" t="str">
-        <x:v>loc-0398</x:v>
-      </x:c>
-      <x:c r="F63" s="87" t="str">
-        <x:v>Times Square-42 Street Station</x:v>
-      </x:c>
-      <x:c r="G63" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H63" s="87" t="str">
-        <x:v>loc-0369</x:v>
-      </x:c>
-      <x:c r="I63" s="87" t="str">
-        <x:v>Museum of Chinese in America</x:v>
-      </x:c>
-      <x:c r="J63" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K63" s="87" t="str">
-        <x:v>loc-0089</x:v>
-      </x:c>
-      <x:c r="L63" s="87" t="str">
-        <x:v>Castle Clinton National Monument</x:v>
-      </x:c>
-      <x:c r="M63" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N63" s="87" t="str">
-        <x:v>loc-0071</x:v>
-      </x:c>
-      <x:c r="O63" s="87" t="str">
-        <x:v>Long Island Motor Parkway</x:v>
-      </x:c>
-      <x:c r="P63" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q63" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R63" s="87" t="str"/>
+      <x:c r="A63"/>
+      <x:c r="B63"/>
+      <x:c r="C63"/>
+      <x:c r="D63"/>
+      <x:c r="E63"/>
+      <x:c r="F63"/>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+      <x:c r="I63"/>
+      <x:c r="J63"/>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
+      <x:c r="M63"/>
+      <x:c r="N63"/>
+      <x:c r="O63"/>
+      <x:c r="P63"/>
+      <x:c r="Q63"/>
+      <x:c r="R63"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="84" t="n">
-        <x:v>46308</x:v>
-      </x:c>
-      <x:c r="B64" s="85" t="str">
-        <x:v>loc-0408</x:v>
-      </x:c>
-      <x:c r="C64" s="85" t="str">
-        <x:v>Jamaica Center-Parsons/Archer Station</x:v>
-      </x:c>
-      <x:c r="D64" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="E64" s="85" t="str">
-        <x:v>loc-0038</x:v>
-      </x:c>
-      <x:c r="F64" s="85" t="str">
-        <x:v>Fort Schuyler</x:v>
-      </x:c>
-      <x:c r="G64" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="H64" s="85" t="str">
-        <x:v>loc-0094</x:v>
-      </x:c>
-      <x:c r="I64" s="85" t="str">
-        <x:v>Queensboro Bridge</x:v>
-      </x:c>
-      <x:c r="J64" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K64" s="85" t="str">
-        <x:v>loc-0377</x:v>
-      </x:c>
-      <x:c r="L64" s="85" t="str">
-        <x:v>Museum of the American Gangster</x:v>
-      </x:c>
-      <x:c r="M64" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N64" s="85" t="str">
-        <x:v>loc-0302</x:v>
-      </x:c>
-      <x:c r="O64" s="85" t="str">
-        <x:v>Mariners Marsh Park</x:v>
-      </x:c>
-      <x:c r="P64" s="85" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="Q64" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R64" s="85" t="str"/>
+      <x:c r="A64"/>
+      <x:c r="B64"/>
+      <x:c r="C64"/>
+      <x:c r="D64"/>
+      <x:c r="E64"/>
+      <x:c r="F64"/>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+      <x:c r="I64"/>
+      <x:c r="J64"/>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
+      <x:c r="M64"/>
+      <x:c r="N64"/>
+      <x:c r="O64"/>
+      <x:c r="P64"/>
+      <x:c r="Q64"/>
+      <x:c r="R64"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="86" t="n">
-        <x:v>46309</x:v>
-      </x:c>
-      <x:c r="B65" s="87" t="str">
-        <x:v>loc-0108</x:v>
-      </x:c>
-      <x:c r="C65" s="87" t="str">
-        <x:v>DeLamar Mansion</x:v>
-      </x:c>
-      <x:c r="D65" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E65" s="87" t="str">
-        <x:v>loc-0010</x:v>
-      </x:c>
-      <x:c r="F65" s="87" t="str">
-        <x:v>The Metropolitan Museum of Art</x:v>
-      </x:c>
-      <x:c r="G65" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H65" s="87" t="str">
-        <x:v>loc-0475</x:v>
-      </x:c>
-      <x:c r="I65" s="87" t="str">
-        <x:v>Manhattan Municipal Building</x:v>
-      </x:c>
-      <x:c r="J65" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K65" s="87" t="str">
-        <x:v>loc-0303</x:v>
-      </x:c>
-      <x:c r="L65" s="87" t="str">
-        <x:v>Ocean Breeze Park</x:v>
-      </x:c>
-      <x:c r="M65" s="87" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="N65" s="87" t="str">
-        <x:v>loc-0188</x:v>
-      </x:c>
-      <x:c r="O65" s="87" t="str">
-        <x:v>Flushing Memorial</x:v>
-      </x:c>
-      <x:c r="P65" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q65" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R65" s="87" t="str"/>
+      <x:c r="A65"/>
+      <x:c r="B65"/>
+      <x:c r="C65"/>
+      <x:c r="D65"/>
+      <x:c r="E65"/>
+      <x:c r="F65"/>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
+      <x:c r="I65"/>
+      <x:c r="J65"/>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
+      <x:c r="M65"/>
+      <x:c r="N65"/>
+      <x:c r="O65"/>
+      <x:c r="P65"/>
+      <x:c r="Q65"/>
+      <x:c r="R65"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="84" t="n">
-        <x:v>46310</x:v>
-      </x:c>
-      <x:c r="B66" s="85" t="str">
-        <x:v>loc-0422</x:v>
-      </x:c>
-      <x:c r="C66" s="85" t="str">
-        <x:v>Roberto Clemente Plaza</x:v>
-      </x:c>
-      <x:c r="D66" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="E66" s="85" t="str">
-        <x:v>loc-0057</x:v>
-      </x:c>
-      <x:c r="F66" s="85" t="str">
-        <x:v>Steinway House</x:v>
-      </x:c>
-      <x:c r="G66" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H66" s="85" t="str">
-        <x:v>loc-0379</x:v>
-      </x:c>
-      <x:c r="I66" s="85" t="str">
-        <x:v>Eyebeam Art and Technology Center</x:v>
-      </x:c>
-      <x:c r="J66" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K66" s="85" t="str">
-        <x:v>loc-0322</x:v>
-      </x:c>
-      <x:c r="L66" s="85" t="str">
-        <x:v>Neue Galerie</x:v>
-      </x:c>
-      <x:c r="M66" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N66" s="85" t="str">
-        <x:v>loc-0144</x:v>
-      </x:c>
-      <x:c r="O66" s="85" t="str">
-        <x:v>Prospect Cemetery</x:v>
-      </x:c>
-      <x:c r="P66" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q66" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R66" s="85" t="str"/>
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
+      <x:c r="J66"/>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
+      <x:c r="P66"/>
+      <x:c r="Q66"/>
+      <x:c r="R66"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="86" t="n">
-        <x:v>46311</x:v>
-      </x:c>
-      <x:c r="B67" s="87" t="str">
-        <x:v>loc-0007</x:v>
-      </x:c>
-      <x:c r="C67" s="87" t="str">
-        <x:v>Central Park</x:v>
-      </x:c>
-      <x:c r="D67" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E67" s="87" t="str">
-        <x:v>loc-0015</x:v>
-      </x:c>
-      <x:c r="F67" s="87" t="str">
-        <x:v>Guggenheim Museum</x:v>
-      </x:c>
-      <x:c r="G67" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H67" s="87" t="str">
-        <x:v>loc-0311</x:v>
-      </x:c>
-      <x:c r="I67" s="87" t="str">
-        <x:v>Soundview Park</x:v>
-      </x:c>
-      <x:c r="J67" s="87" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="K67" s="87" t="str">
-        <x:v>loc-0467</x:v>
-      </x:c>
-      <x:c r="L67" s="87" t="str">
-        <x:v>Eleven Madison Park</x:v>
-      </x:c>
-      <x:c r="M67" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N67" s="87" t="str">
-        <x:v>loc-0164</x:v>
-      </x:c>
-      <x:c r="O67" s="87" t="str">
-        <x:v>Mohandas Gandhi</x:v>
-      </x:c>
-      <x:c r="P67" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q67" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R67" s="87" t="str"/>
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
+      <x:c r="J67"/>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
+      <x:c r="M67"/>
+      <x:c r="N67"/>
+      <x:c r="O67"/>
+      <x:c r="P67"/>
+      <x:c r="Q67"/>
+      <x:c r="R67"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="84" t="n">
-        <x:v>46312</x:v>
-      </x:c>
-      <x:c r="B68" s="85" t="str">
-        <x:v>loc-0027</x:v>
-      </x:c>
-      <x:c r="C68" s="85" t="str">
-        <x:v>Cooper Union</x:v>
-      </x:c>
-      <x:c r="D68" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E68" s="85" t="str">
-        <x:v>loc-0022</x:v>
-      </x:c>
-      <x:c r="F68" s="85" t="str">
-        <x:v>Flatiron Building</x:v>
-      </x:c>
-      <x:c r="G68" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H68" s="85" t="str">
-        <x:v>loc-0341</x:v>
-      </x:c>
-      <x:c r="I68" s="85" t="str">
-        <x:v>Icahn Stadium</x:v>
-      </x:c>
-      <x:c r="J68" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K68" s="85" t="str">
-        <x:v>loc-0428</x:v>
-      </x:c>
-      <x:c r="L68" s="85" t="str">
-        <x:v>Municipal Plaza</x:v>
-      </x:c>
-      <x:c r="M68" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N68" s="85" t="str">
-        <x:v>loc-0350</x:v>
-      </x:c>
-      <x:c r="O68" s="85" t="str">
-        <x:v>Microscope Gallery</x:v>
-      </x:c>
-      <x:c r="P68" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q68" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R68" s="85" t="str"/>
+      <x:c r="A68"/>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
+      <x:c r="E68"/>
+      <x:c r="F68"/>
+      <x:c r="G68"/>
+      <x:c r="H68"/>
+      <x:c r="I68"/>
+      <x:c r="J68"/>
+      <x:c r="K68"/>
+      <x:c r="L68"/>
+      <x:c r="M68"/>
+      <x:c r="N68"/>
+      <x:c r="O68"/>
+      <x:c r="P68"/>
+      <x:c r="Q68"/>
+      <x:c r="R68"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="86" t="n">
-        <x:v>46313</x:v>
-      </x:c>
-      <x:c r="B69" s="87" t="str">
-        <x:v>loc-0042</x:v>
-      </x:c>
-      <x:c r="C69" s="87" t="str">
-        <x:v>Fort Wadsworth</x:v>
-      </x:c>
-      <x:c r="D69" s="87" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="E69" s="87" t="str">
-        <x:v>loc-0441</x:v>
-      </x:c>
-      <x:c r="F69" s="87" t="str">
-        <x:v>Arthur Ashe Stadium</x:v>
-      </x:c>
-      <x:c r="G69" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="H69" s="87" t="str">
-        <x:v>loc-0360</x:v>
-      </x:c>
-      <x:c r="I69" s="87" t="str">
-        <x:v>Museum of Food and Drink</x:v>
-      </x:c>
-      <x:c r="J69" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="K69" s="87" t="str">
-        <x:v>loc-0349</x:v>
-      </x:c>
-      <x:c r="L69" s="87" t="str">
-        <x:v>The Africa Center</x:v>
-      </x:c>
-      <x:c r="M69" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="N69" s="87" t="str">
-        <x:v>loc-0184</x:v>
-      </x:c>
-      <x:c r="O69" s="87" t="str">
-        <x:v>Maspeth Memorial</x:v>
-      </x:c>
-      <x:c r="P69" s="87" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q69" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R69" s="87" t="str"/>
+      <x:c r="A69"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69"/>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
+      <x:c r="I69"/>
+      <x:c r="J69"/>
+      <x:c r="K69"/>
+      <x:c r="L69"/>
+      <x:c r="M69"/>
+      <x:c r="N69"/>
+      <x:c r="O69"/>
+      <x:c r="P69"/>
+      <x:c r="Q69"/>
+      <x:c r="R69"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="84" t="n">
-        <x:v>46314</x:v>
-      </x:c>
-      <x:c r="B70" s="85" t="str">
-        <x:v>loc-0466</x:v>
-      </x:c>
-      <x:c r="C70" s="85" t="str">
-        <x:v>Lipstick Building</x:v>
-      </x:c>
-      <x:c r="D70" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E70" s="85" t="str">
-        <x:v>loc-0457</x:v>
-      </x:c>
-      <x:c r="F70" s="85" t="str">
-        <x:v>Algonquin Hotel</x:v>
-      </x:c>
-      <x:c r="G70" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H70" s="85" t="str">
-        <x:v>loc-0281</x:v>
-      </x:c>
-      <x:c r="I70" s="85" t="str">
-        <x:v>Cunningham Park</x:v>
-      </x:c>
-      <x:c r="J70" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="K70" s="85" t="str">
-        <x:v>loc-0405</x:v>
-      </x:c>
-      <x:c r="L70" s="85" t="str">
-        <x:v>Chambers Street Station</x:v>
-      </x:c>
-      <x:c r="M70" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N70" s="85" t="str">
-        <x:v>loc-0174</x:v>
-      </x:c>
-      <x:c r="O70" s="85" t="str">
-        <x:v>Rocket Thrower</x:v>
-      </x:c>
-      <x:c r="P70" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q70" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R70" s="85" t="str"/>
+      <x:c r="A70"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+      <x:c r="J70"/>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
+      <x:c r="M70"/>
+      <x:c r="N70"/>
+      <x:c r="O70"/>
+      <x:c r="P70"/>
+      <x:c r="Q70"/>
+      <x:c r="R70"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="86" t="n">
-        <x:v>46315</x:v>
-      </x:c>
-      <x:c r="B71" s="87" t="str">
-        <x:v>loc-0110</x:v>
-      </x:c>
-      <x:c r="C71" s="87" t="str">
-        <x:v>Greenacre Park</x:v>
-      </x:c>
-      <x:c r="D71" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E71" s="87" t="str">
-        <x:v>loc-0478</x:v>
-      </x:c>
-      <x:c r="F71" s="87" t="str">
-        <x:v>Yankee Stadium</x:v>
-      </x:c>
-      <x:c r="G71" s="87" t="str">
-        <x:v>Bronx</x:v>
-      </x:c>
-      <x:c r="H71" s="87" t="str">
-        <x:v>loc-0400</x:v>
-      </x:c>
-      <x:c r="I71" s="87" t="str">
-        <x:v>49 Street Station</x:v>
-      </x:c>
-      <x:c r="J71" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K71" s="87" t="str">
-        <x:v>loc-0256</x:v>
-      </x:c>
-      <x:c r="L71" s="87" t="str">
-        <x:v>Silver Lake Park</x:v>
-      </x:c>
-      <x:c r="M71" s="87" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="N71" s="87" t="str">
-        <x:v>loc-0062</x:v>
-      </x:c>
-      <x:c r="O71" s="87" t="str">
-        <x:v>B &amp; B Carousell</x:v>
-      </x:c>
-      <x:c r="P71" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q71" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R71" s="87" t="str"/>
+      <x:c r="A71"/>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
+      <x:c r="J71"/>
+      <x:c r="K71"/>
+      <x:c r="L71"/>
+      <x:c r="M71"/>
+      <x:c r="N71"/>
+      <x:c r="O71"/>
+      <x:c r="P71"/>
+      <x:c r="Q71"/>
+      <x:c r="R71"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="84" t="n">
-        <x:v>46316</x:v>
-      </x:c>
-      <x:c r="B72" s="85" t="str">
-        <x:v>loc-0451</x:v>
-      </x:c>
-      <x:c r="C72" s="85" t="str">
-        <x:v>Plaza Hotel</x:v>
-      </x:c>
-      <x:c r="D72" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E72" s="85" t="str">
-        <x:v>loc-0412</x:v>
-      </x:c>
-      <x:c r="F72" s="85" t="str">
-        <x:v>Fordham Plaza</x:v>
-      </x:c>
-      <x:c r="G72" s="85" t="str">
-        <x:v>The Bronx</x:v>
-      </x:c>
-      <x:c r="H72" s="85" t="str">
-        <x:v>loc-0090</x:v>
-      </x:c>
-      <x:c r="I72" s="85" t="str">
-        <x:v>College of the City of New York</x:v>
-      </x:c>
-      <x:c r="J72" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K72" s="85" t="str">
-        <x:v>loc-0101</x:v>
-      </x:c>
-      <x:c r="L72" s="85" t="str">
-        <x:v>Federal Hall National Memorial</x:v>
-      </x:c>
-      <x:c r="M72" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N72" s="85" t="str">
-        <x:v>loc-0368</x:v>
-      </x:c>
-      <x:c r="O72" s="85" t="str">
-        <x:v>New York City Police Museum</x:v>
-      </x:c>
-      <x:c r="P72" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q72" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R72" s="85" t="str"/>
+      <x:c r="A72"/>
+      <x:c r="B72"/>
+      <x:c r="C72"/>
+      <x:c r="D72"/>
+      <x:c r="E72"/>
+      <x:c r="F72"/>
+      <x:c r="G72"/>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
+      <x:c r="J72"/>
+      <x:c r="K72"/>
+      <x:c r="L72"/>
+      <x:c r="M72"/>
+      <x:c r="N72"/>
+      <x:c r="O72"/>
+      <x:c r="P72"/>
+      <x:c r="Q72"/>
+      <x:c r="R72"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="86" t="n">
-        <x:v>46317</x:v>
-      </x:c>
-      <x:c r="B73" s="87" t="str">
-        <x:v>loc-0046</x:v>
-      </x:c>
-      <x:c r="C73" s="87" t="str">
-        <x:v>Green-Wood Cemetery</x:v>
-      </x:c>
-      <x:c r="D73" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="E73" s="87" t="str">
-        <x:v>loc-0029</x:v>
-      </x:c>
-      <x:c r="F73" s="87" t="str">
-        <x:v>The Met Cloisters</x:v>
-      </x:c>
-      <x:c r="G73" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H73" s="87" t="str">
-        <x:v>loc-0343</x:v>
-      </x:c>
-      <x:c r="I73" s="87" t="str">
-        <x:v>Museum of Sex</x:v>
-      </x:c>
-      <x:c r="J73" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K73" s="87" t="str">
-        <x:v>loc-0393</x:v>
-      </x:c>
-      <x:c r="L73" s="87" t="str">
-        <x:v>59 Street-Columbus Circle Station</x:v>
-      </x:c>
-      <x:c r="M73" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N73" s="87" t="str">
-        <x:v>loc-0213</x:v>
-      </x:c>
-      <x:c r="O73" s="87" t="str">
-        <x:v>Edvard Grieg Memorial</x:v>
-      </x:c>
-      <x:c r="P73" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q73" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R73" s="87" t="str"/>
+      <x:c r="A73"/>
+      <x:c r="B73"/>
+      <x:c r="C73"/>
+      <x:c r="D73"/>
+      <x:c r="E73"/>
+      <x:c r="F73"/>
+      <x:c r="G73"/>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
+      <x:c r="J73"/>
+      <x:c r="K73"/>
+      <x:c r="L73"/>
+      <x:c r="M73"/>
+      <x:c r="N73"/>
+      <x:c r="O73"/>
+      <x:c r="P73"/>
+      <x:c r="Q73"/>
+      <x:c r="R73"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="84" t="n">
-        <x:v>46318</x:v>
-      </x:c>
-      <x:c r="B74" s="85" t="str">
-        <x:v>loc-0404</x:v>
-      </x:c>
-      <x:c r="C74" s="85" t="str">
-        <x:v>Atlantic Avenue-Barclays Center Station</x:v>
-      </x:c>
-      <x:c r="D74" s="85" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="E74" s="85" t="str">
-        <x:v>loc-0463</x:v>
-      </x:c>
-      <x:c r="F74" s="85" t="str">
-        <x:v>MetLife Building</x:v>
-      </x:c>
-      <x:c r="G74" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H74" s="85" t="str">
-        <x:v>loc-0297</x:v>
-      </x:c>
-      <x:c r="I74" s="85" t="str">
-        <x:v>Kissena Corridor Park</x:v>
-      </x:c>
-      <x:c r="J74" s="85" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="K74" s="85" t="str">
-        <x:v>loc-0494</x:v>
-      </x:c>
-      <x:c r="L74" s="85" t="str">
-        <x:v>Bay Plaza Shopping Center</x:v>
-      </x:c>
-      <x:c r="M74" s="85" t="str">
-        <x:v>Bronx</x:v>
-      </x:c>
-      <x:c r="N74" s="85" t="str">
-        <x:v>loc-0165</x:v>
-      </x:c>
-      <x:c r="O74" s="85" t="str">
-        <x:v>Giuseppe Garibaldi</x:v>
-      </x:c>
-      <x:c r="P74" s="85" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="Q74" s="85" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R74" s="85" t="str"/>
+      <x:c r="A74"/>
+      <x:c r="B74"/>
+      <x:c r="C74"/>
+      <x:c r="D74"/>
+      <x:c r="E74"/>
+      <x:c r="F74"/>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
+      <x:c r="J74"/>
+      <x:c r="K74"/>
+      <x:c r="L74"/>
+      <x:c r="M74"/>
+      <x:c r="N74"/>
+      <x:c r="O74"/>
+      <x:c r="P74"/>
+      <x:c r="Q74"/>
+      <x:c r="R74"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="86" t="n">
-        <x:v>46319</x:v>
-      </x:c>
-      <x:c r="B75" s="87" t="str">
-        <x:v>loc-0330</x:v>
-      </x:c>
-      <x:c r="C75" s="87" t="str">
-        <x:v>Museum of the City of New York</x:v>
-      </x:c>
-      <x:c r="D75" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E75" s="87" t="str">
-        <x:v>loc-0033</x:v>
-      </x:c>
-      <x:c r="F75" s="87" t="str">
-        <x:v>Carnegie Hall</x:v>
-      </x:c>
-      <x:c r="G75" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="H75" s="87" t="str">
-        <x:v>loc-0266</x:v>
-      </x:c>
-      <x:c r="I75" s="87" t="str">
-        <x:v>Battery Park City</x:v>
-      </x:c>
-      <x:c r="J75" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="K75" s="87" t="str">
-        <x:v>loc-0434</x:v>
-      </x:c>
-      <x:c r="L75" s="87" t="str">
-        <x:v>185th Street Plaza</x:v>
-      </x:c>
-      <x:c r="M75" s="87" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N75" s="87" t="str">
-        <x:v>loc-0130</x:v>
-      </x:c>
-      <x:c r="O75" s="87" t="str">
-        <x:v>Evergreens Cemetery</x:v>
-      </x:c>
-      <x:c r="P75" s="87" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="Q75" s="87" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R75" s="87" t="str"/>
+      <x:c r="A75"/>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
+      <x:c r="I75"/>
+      <x:c r="J75"/>
+      <x:c r="K75"/>
+      <x:c r="L75"/>
+      <x:c r="M75"/>
+      <x:c r="N75"/>
+      <x:c r="O75"/>
+      <x:c r="P75"/>
+      <x:c r="Q75"/>
+      <x:c r="R75"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="88" t="n">
-        <x:v>46320</x:v>
-      </x:c>
-      <x:c r="B76" s="89" t="str">
-        <x:v>loc-0116</x:v>
-      </x:c>
-      <x:c r="C76" s="89" t="str">
-        <x:v>Park Row Building</x:v>
-      </x:c>
-      <x:c r="D76" s="89" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="E76" s="89" t="str">
-        <x:v>loc-0004</x:v>
-      </x:c>
-      <x:c r="F76" s="89" t="str">
-        <x:v>Brooklyn Academy of Music</x:v>
-      </x:c>
-      <x:c r="G76" s="89" t="str">
-        <x:v>Brooklyn</x:v>
-      </x:c>
-      <x:c r="H76" s="89" t="str">
-        <x:v>loc-0276</x:v>
-      </x:c>
-      <x:c r="I76" s="89" t="str">
-        <x:v>Brookfield Park</x:v>
-      </x:c>
-      <x:c r="J76" s="89" t="str">
-        <x:v>Staten Island</x:v>
-      </x:c>
-      <x:c r="K76" s="89" t="str">
-        <x:v>loc-0394</x:v>
-      </x:c>
-      <x:c r="L76" s="89" t="str">
-        <x:v>Broadway-Lafayette Street Station</x:v>
-      </x:c>
-      <x:c r="M76" s="89" t="str">
-        <x:v>Manhattan</x:v>
-      </x:c>
-      <x:c r="N76" s="89" t="str">
-        <x:v>loc-0190</x:v>
-      </x:c>
-      <x:c r="O76" s="89" t="str">
-        <x:v>Soldiers Monument</x:v>
-      </x:c>
-      <x:c r="P76" s="89" t="str">
-        <x:v>Queens</x:v>
-      </x:c>
-      <x:c r="Q76" s="89" t="str">
-        <x:v>scheduled</x:v>
-      </x:c>
-      <x:c r="R76" s="89" t="str"/>
+      <x:c r="A76"/>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+      <x:c r="H76"/>
+      <x:c r="I76"/>
+      <x:c r="J76"/>
+      <x:c r="K76"/>
+      <x:c r="L76"/>
+      <x:c r="M76"/>
+      <x:c r="N76"/>
+      <x:c r="O76"/>
+      <x:c r="P76"/>
+      <x:c r="Q76"/>
+      <x:c r="R76"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55fe259df43046df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R200143af5c6f4f51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23803,7 +23784,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1792a3ebb2734274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refd706937a5540db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23835,10 +23816,10 @@
       <x:c r="H1" s="31"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="113" t="str">
+      <x:c r="A3" s="139" t="str">
         <x:v>Catalog metric</x:v>
       </x:c>
-      <x:c r="B3" s="114" t="str">
+      <x:c r="B3" s="140" t="str">
         <x:v>Count</x:v>
       </x:c>
       <x:c r="C3" s="33"/>
@@ -23849,10 +23830,10 @@
       <x:c r="H3" s="33"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="104" t="str">
+      <x:c r="A4" s="130" t="str">
         <x:v>Active locations</x:v>
       </x:c>
-      <x:c r="B4" s="105" t="n">
+      <x:c r="B4" s="131" t="n">
         <x:f>COUNTA('All Locations'!$A$2:$A$496)</x:f>
         <x:v>495</x:v>
       </x:c>
@@ -23864,10 +23845,10 @@
       <x:c r="H4" s="33"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="106" t="str">
+      <x:c r="A5" s="132" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="B5" s="107" t="n">
+      <x:c r="B5" s="133" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="33"/>
@@ -23878,10 +23859,10 @@
       <x:c r="H5" s="33"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="108" t="str">
+      <x:c r="A6" s="134" t="str">
         <x:v>Nearby distinct pairs flagged</x:v>
       </x:c>
-      <x:c r="B6" s="109" t="n">
+      <x:c r="B6" s="135" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C6" s="33"/>
@@ -23892,12 +23873,12 @@
       <x:c r="H6" s="33"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="106" t="str">
+      <x:c r="A7" s="132" t="str">
         <x:v>Repeat-free scheduled days</x:v>
       </x:c>
-      <x:c r="B7" s="110" t="n">
-        <x:f>COUNTA('Daily Games'!$A$2:$A$76)</x:f>
-        <x:v>75</x:v>
+      <x:c r="B7" s="136" t="n">
+        <x:f>COUNTA('Daily Games'!$A$2:$A$51)</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="33"/>
       <x:c r="D7" s="33"/>
@@ -23907,12 +23888,12 @@
       <x:c r="H7" s="33"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="115" t="str">
+      <x:c r="A8" s="141" t="str">
         <x:v>Scheduled through</x:v>
       </x:c>
-      <x:c r="B8" s="116" t="n">
-        <x:f>MAX('Daily Games'!$A$2:$A$76)</x:f>
-        <x:v>46320</x:v>
+      <x:c r="B8" s="142" t="n">
+        <x:f>MAX('Daily Games'!$A$2:$A$51)</x:f>
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="C8" s="33"/>
       <x:c r="D8" s="33"/>
@@ -27445,7 +27426,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66f6f4c860574a05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dbe65d41a8e4e0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>